--- a/templates/postateynyy-faktornyy-analiz.xlsx
+++ b/templates/postateynyy-faktornyy-analiz.xlsx
@@ -12,11 +12,12 @@
     <sheet name="Шаблон" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Условный пример" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Калькулятор позиции" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Индекс" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Производные затраты" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Риск" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Реестр документов" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Контроль" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Ориентировочный бюджет" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Индекс" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Производные затраты" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Риск" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Реестр документов" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Контроль" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Как пользоваться'!$1:$2</definedName>
@@ -27,8 +28,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Условный пример'!$A$4:$N$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Условный пример'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Калькулятор позиции'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Реестр документов'!$A$4:$E$48</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Реестр документов'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Ориентировочный бюджет'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Реестр документов'!$A$4:$E$54</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Реестр документов'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
@@ -210,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -308,6 +310,18 @@
     <xf numFmtId="164" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -317,16 +331,10 @@
     <xf numFmtId="10" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -343,9 +351,6 @@
     </xf>
     <xf numFmtId="2" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -787,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -885,7 +890,7 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>11. Класс надежности: А — первичные объемы, цены и индексы; Б — параметрический расчет; В — экспертный остаток.</t>
+          <t>11. Класс надежности: А — первичные объемы, цены и индексы; Б — параметрический расчет; В — экспертный остаток. Для ориентировочного бюджета до рабочей документации класс А по строительной статье не ставится.</t>
         </is>
       </c>
     </row>
@@ -893,6 +898,13 @@
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>12. Полные правила, запрет двойного счета и реестр доказательств — в текстовой методике.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>13. Если в базовом бюджете не было смет и рабочей документации, статья считается на листе «Ориентировочный бюджет»: инфляция начисляется на удельную ставку, а первый обсчет той же программы раскрывается внутри иных причин.</t>
         </is>
       </c>
     </row>
@@ -998,12 +1010,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Индекс</t>
+          <t>Ориентировочный бюджет</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Сборка коэффициента инфляции из весов ресурсов</t>
+          <t>Удельная ставка до рабочей документации: инфляция, отступление от паспорта и уточнение</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -1014,12 +1026,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Производные затраты</t>
+          <t>Индекс</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Процент генподряда, содержание команды и учебный график процентов</t>
+          <t>Сборка коэффициента инфляции из весов ресурсов</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
@@ -1030,12 +1042,12 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Риск</t>
+          <t>Производные затраты</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Шкала баллов до ввода в эксплуатацию</t>
+          <t>Процент генподряда, содержание команды и учебный график процентов</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
@@ -1046,12 +1058,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Реестр документов</t>
+          <t>Риск</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Минимальный комплект доказательств по факторам</t>
+          <t>Шкала баллов до ввода в эксплуатацию</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
@@ -1062,12 +1074,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Реестр документов</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Сверка итога условного примера</t>
+          <t>Минимальный комплект доказательств по факторам</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -1075,8 +1087,25 @@
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="9" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Сверка итога условного примера</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="B22:F22"/>
@@ -1088,6 +1117,7 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B29:F29"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="B28:F28"/>
@@ -1109,11 +1139,1429 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Минимальный реестр документов для подтверждения факторов</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Класс А не присваивается по объяснительной записке. Если документа из минимума нет, сумма не получает имя соответствующего фактора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Документ</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Какой фактор закрывает</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Что сверяется</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Если документа нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Сквозные</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Протокол утверждения базового бюджета, модель и макродопущения T0</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Все</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Какой файл является базой и какие дефляторы утверждены</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>База не идентифицирована, расчет не начинается</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Сквозные</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Файл откорректированного бюджета T1 и пояснения застройщика</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Все</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>От какой версии отстраивается анализ</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
+        <is>
+          <t>Нет предмета анализа</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Сквозные</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Реестр промежуточных версий бюджета</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Все</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Что промежуточная версия не подменила T0</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="inlineStr">
+        <is>
+          <t>Риск подмены базы раскрывается как оговорка</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Сквозные</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Модели T0 и T1 с формулами</t>
+        </is>
+      </c>
+      <c r="C8" s="57" t="inlineStr">
+        <is>
+          <t>F1, проценты</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Ряды дефляторов, график, ставка, НДС</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>F1 не выше класса В</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Сквозные</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Письма Минстроя, выгрузка ФГИС ЦС, публикация Росстата на кварталы периода</t>
+        </is>
+      </c>
+      <c r="C9" s="57" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Отношение индексов, а не индекс к базе 2001 года</t>
+        </is>
+      </c>
+      <c r="E9" s="55" t="inlineStr">
+        <is>
+          <t>Называть сумму инфляцией нельзя</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Сквозные</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Графики T0 и T1, критический путь, справка о причинах сдвига</t>
+        </is>
+      </c>
+      <c r="C10" s="57" t="inlineStr">
+        <is>
+          <t>F1 против F3, реклассификация в F2</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Какие месяцы относятся к сроку, а не к индексу</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
+        <is>
+          <t>Сдвиг сроков остается неразделенным</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Сквозные</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Поквартальный поток затрат без процентов и отдельно проценты</t>
+        </is>
+      </c>
+      <c r="C11" s="57" t="inlineStr">
+        <is>
+          <t>F1, F3</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Веса кварталов и сценарии долга</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
+        <is>
+          <t>Допустим только средний индекс с оговоркой</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Сквозные</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Учетная политика по НДС, капитализации процентов и претензиям</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Чтобы одна сумма не попала в два режима</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>Оговорка о возможном двойном счете</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Сквозные</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Справка о периметре: очереди, выбытия, затраты вне бюджета</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>До факторов</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Сопоставимость итогов</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>Факторы могут объяснять чужой объект</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Сквозные</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Регистр фактических затрат на дату T1 против бюджета</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>Все</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Связь бюджета с фактом</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>Бюджет T1 может быть декларацией</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Ориентировочный бюджет</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Модель T0 с формулой удельной ставки, составом включенных затрат, датой цен и дефлятором</t>
+        </is>
+      </c>
+      <c r="C15" s="57" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Ставка a0 и измеритель Q0, от которых считается инфляция</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>Инфляцию начислять не на что</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Ориентировочный бюджет</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Лист ТЭП и задание на проектирование редакции T0</t>
+        </is>
+      </c>
+      <c r="C16" s="58" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Паспорт программы, от которой считается отступление</t>
+        </is>
+      </c>
+      <c r="E16" s="55" t="inlineStr">
+        <is>
+          <t>Первый обсчет нельзя отделить от изменения проекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Ориентировочный бюджет</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Концепция или стадия П с пометкой, была ли она основанием бюджета</t>
+        </is>
+      </c>
+      <c r="C17" s="58" t="inlineStr">
+        <is>
+          <t>F2 против F3d</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Названные решения отделены от решений, которых в основании не было</t>
+        </is>
+      </c>
+      <c r="E17" s="55" t="inlineStr">
+        <is>
+          <t>Любая рабочая документация выглядит как изменение</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Ориентировочный бюджет</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Расчет аналога с долями конструктива, фасада и инженерных систем</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>U и F1</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Доля замененного решения и структура индекса, утвержденная до сметы T1</t>
+        </is>
+      </c>
+      <c r="E18" s="55" t="inlineStr">
+        <is>
+          <t>Доля замены назначается произвольно, класс В</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Ориентировочный бюджет</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Перечень исключений из удельной ставки и резерв на недопроектированность</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>F3d</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Что ставка не обещала и какой резерв это покрывал</t>
+        </is>
+      </c>
+      <c r="E19" s="55" t="inlineStr">
+        <is>
+          <t>Уточнение смешивается с пропуском периметра</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Ориентировочный бюджет</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Рабочая документация и сметы T1 плюс таблица исключенных отступлений от паспорта</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>S и F3d</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Стоимость той же программы в ценах T1</t>
+        </is>
+      </c>
+      <c r="E20" s="55" t="inlineStr">
+        <is>
+          <t>F3d становится остатком без доказательства</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Договоры, дополнительные соглашения, протоколы цены и ведомости расценок</t>
+        </is>
+      </c>
+      <c r="C21" s="57" t="inlineStr">
+        <is>
+          <t>F1, F3</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Исходная и новая цена, формула эскалации</t>
+        </is>
+      </c>
+      <c r="E21" s="55" t="inlineStr">
+        <is>
+          <t>Нет класса А по цене</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Калькуляция расценки или ресурсная ведомость</t>
+        </is>
+      </c>
+      <c r="C22" s="57" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Веса материалов, машин и оплаты труда</t>
+        </is>
+      </c>
+      <c r="E22" s="55" t="inlineStr">
+        <is>
+          <t>Индекс статьи становится среднеотраслевым, класс Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Локальные сметы и сводный сметный расчет с указанием базы и квартала цен</t>
+        </is>
+      </c>
+      <c r="C23" s="57" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>К какой базе применяется отношение индексов</t>
+        </is>
+      </c>
+      <c r="E23" s="55" t="inlineStr">
+        <is>
+          <t>Индекс легко применить не к той базе</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Расчет скользящей цены подрядчика и его первичные индексы</t>
+        </is>
+      </c>
+      <c r="C24" s="57" t="inlineStr">
+        <is>
+          <t>F1 и F3</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Разница экономической инфляции и договорной эскалации</t>
+        </is>
+      </c>
+      <c r="E24" s="55" t="inlineStr">
+        <is>
+          <t>Договорная эскалация может быть принята за дефлятор</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Счета и УПД на основные материалы, спецификации поставки</t>
+        </is>
+      </c>
+      <c r="C25" s="57" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Фактическая цена освоенного объема</t>
+        </is>
+      </c>
+      <c r="E25" s="55" t="inlineStr">
+        <is>
+          <t>F1a не подтвержден</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Не менее двух сопоставимых предложений на незакупленный остаток</t>
+        </is>
+      </c>
+      <c r="C26" s="57" t="inlineStr">
+        <is>
+          <t>F1b, pref</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Прогноз и рыночная цена нового решения</t>
+        </is>
+      </c>
+      <c r="E26" s="55" t="inlineStr">
+        <is>
+          <t>Остаток получает класс В</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Проект и рабочая документация обеих ревизий, заключения экспертизы</t>
+        </is>
+      </c>
+      <c r="C27" s="58" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Что именно изменилось в решениях</t>
+        </is>
+      </c>
+      <c r="E27" s="55" t="inlineStr">
+        <is>
+          <t>F2 не подтверждается</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Реестр измов с причиной и сопоставительная ведомость объемов</t>
+        </is>
+      </c>
+      <c r="C28" s="58" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Дельта количества со ссылкой на лист</t>
+        </is>
+      </c>
+      <c r="E28" s="55" t="inlineStr">
+        <is>
+          <t>Объемное отклонение остается классом В</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Спецификации оборудования и ведомости отделки обеих ревизий</t>
+        </is>
+      </c>
+      <c r="C29" s="58" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Смена класса внутри того же шифра работы</t>
+        </is>
+      </c>
+      <c r="E29" s="55" t="inlineStr">
+        <is>
+          <t>Смена класса смешивается с инфляцией</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Технические условия и расчет платы за присоединение обеих редакций</t>
+        </is>
+      </c>
+      <c r="C30" s="57" t="inlineStr">
+        <is>
+          <t>F1, F2, F3</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Мощность, тариф и навязанная трасса по отдельности</t>
+        </is>
+      </c>
+      <c r="E30" s="55" t="inlineStr">
+        <is>
+          <t>Сети не раскладываются</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Акты выполненных работ, справки о стоимости, накопительные ведомости, исполнительные схемы</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>Все по закрытому объему</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Факт объема и цены</t>
+        </is>
+      </c>
+      <c r="E31" s="55" t="inlineStr">
+        <is>
+          <t>Закрытый объем не отделен от прогноза</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Журнал работ, акты простоя, подтверждение форс-мажора, реестр претензий</t>
+        </is>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Иные причины по существу, а не остатком</t>
+        </is>
+      </c>
+      <c r="E32" s="55" t="inlineStr">
+        <is>
+          <t>Остаток F3 ограничивается классом В</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Реестр давальческих материалов заказчика</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Запрет двойного счета</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Материал не сидит и у заказчика, и у подрядчика</t>
+        </is>
+      </c>
+      <c r="E33" s="55" t="inlineStr">
+        <is>
+          <t>Риск двойного счета в заключении</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>СМР, вариант Б</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Тендерная расшифровка твердой цены, допущения и протокол конкурса</t>
+        </is>
+      </c>
+      <c r="C34" s="57" t="inlineStr">
+        <is>
+          <t>F1, F3</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Структура твердой цены и коммерческий результат</t>
+        </is>
+      </c>
+      <c r="E34" s="55" t="inlineStr">
+        <is>
+          <t>Остается параметрический мост класса Б или В</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>СМР, вариант В</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Реестр пакетов, матрица разграничения, схема временных зданий</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Запрет двойного счета</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Сумма пакетов равна статьям СМР, стыки не задвоены</t>
+        </is>
+      </c>
+      <c r="E35" s="55" t="inlineStr">
+        <is>
+          <t>Невязка блокирует вывод по статье</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>ПИР</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Договоры на изыскания, стадии П и Р, авторский надзор</t>
+        </is>
+      </c>
+      <c r="C36" s="57" t="inlineStr">
+        <is>
+          <t>F1, F2, F3</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Цена этапа и предмет</t>
+        </is>
+      </c>
+      <c r="E36" s="55" t="inlineStr">
+        <is>
+          <t>Нет базы для ставки</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>ПИР</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Оба задания на проектирование</t>
+        </is>
+      </c>
+      <c r="C37" s="58" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Какие разделы добавлены</t>
+        </is>
+      </c>
+      <c r="E37" s="55" t="inlineStr">
+        <is>
+          <t>Переработка не отличима от инфляции ставок</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>ПИР</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Акты сдачи комплектов и программа дополнительных изысканий</t>
+        </is>
+      </c>
+      <c r="C38" s="58" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Связь допизысканий с новым решением</t>
+        </is>
+      </c>
+      <c r="E38" s="55" t="inlineStr">
+        <is>
+          <t>Допизыскания остаются в F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>ПИР</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Ведомость переработанных разделов с причиной</t>
+        </is>
+      </c>
+      <c r="C39" s="58" t="inlineStr">
+        <is>
+          <t>F2 против F3</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Смена ТЭП отделена от ошибки проектировщика</t>
+        </is>
+      </c>
+      <c r="E39" s="55" t="inlineStr">
+        <is>
+          <t>Вся переработка падает в один фактор</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>ПИР</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>График выпуска рабочей документации и журнал авторского надзора</t>
+        </is>
+      </c>
+      <c r="C40" s="58" t="inlineStr">
+        <is>
+          <t>F2, F3</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Выезд привязан к разделу или к лишнему месяцу</t>
+        </is>
+      </c>
+      <c r="E40" s="55" t="inlineStr">
+        <is>
+          <t>Пролонгация надзора не доказывается</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>ПИР</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Платежные документы экспертизы с составом поданной документации</t>
+        </is>
+      </c>
+      <c r="C41" s="58" t="inlineStr">
+        <is>
+          <t>F2, F1</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Повторная экспертиза против тарифного индекса</t>
+        </is>
+      </c>
+      <c r="E41" s="55" t="inlineStr">
+        <is>
+          <t>Экспертиза не раскладывается</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Управление</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Договоры заказчика, генподряда, управления, стройконтроля и охраны</t>
+        </is>
+      </c>
+      <c r="C42" s="57" t="inlineStr">
+        <is>
+          <t>F1, F2, F3</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Процент, база процента и возмещаемые затраты</t>
+        </is>
+      </c>
+      <c r="E42" s="55" t="inlineStr">
+        <is>
+          <t>Процент может задвоить ФОТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Управление</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Калькуляция базы процента генподряда</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Наследование факторов</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>В базу не входят затраты, возмещаемые отдельно</t>
+        </is>
+      </c>
+      <c r="E43" s="55" t="inlineStr">
+        <is>
+          <t>Двойной счет управления</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Управление</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Штатное расписание и помесячная стоимость команды без персональных данных в отчете</t>
+        </is>
+      </c>
+      <c r="C44" s="57" t="inlineStr">
+        <is>
+          <t>F1, F3</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Индексация исходных месяцев и лишние месяцы</t>
+        </is>
+      </c>
+      <c r="E44" s="55" t="inlineStr">
+        <is>
+          <t>Рост содержания не раскладывается</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Управление</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Приказы об изменении численности с указанием функции</t>
+        </is>
+      </c>
+      <c r="C45" s="58" t="inlineStr">
+        <is>
+          <t>F2 против F3</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Новые разделы проекта против удержания срока</t>
+        </is>
+      </c>
+      <c r="E45" s="55" t="inlineStr">
+        <is>
+          <t>Прирост людей остается в F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Управление</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Счета общеплощадочных расходов по месяцам</t>
+        </is>
+      </c>
+      <c r="C46" s="55" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Месяц затраты совпадает с месяцем пролонгации</t>
+        </is>
+      </c>
+      <c r="E46" s="55" t="inlineStr">
+        <is>
+          <t>Справка о проценте роста недостаточна</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Коммерция</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Маркетинговые бюджеты, медиаплан и договоры размещений</t>
+        </is>
+      </c>
+      <c r="C47" s="57" t="inlineStr">
+        <is>
+          <t>F1, F3</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Цена исходного размещения и новые каналы</t>
+        </is>
+      </c>
+      <c r="E47" s="55" t="inlineStr">
+        <is>
+          <t>Медиаинфляция не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Коммерция</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Договоры брокеров и отчет о продажах: площадь, цена, канал</t>
+        </is>
+      </c>
+      <c r="C48" s="58" t="inlineStr">
+        <is>
+          <t>F2, F3</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Площадь из-за ТЭП отделена от цены прайса и ставки</t>
+        </is>
+      </c>
+      <c r="E48" s="55" t="inlineStr">
+        <is>
+          <t>Комиссия не раскладывается</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Коммерция</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Смета шоурума с указанием статьи, где сидит стройка</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Запрет двойного счета</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Отделка не включена и в СМР, и в коммерцию</t>
+        </is>
+      </c>
+      <c r="E49" s="55" t="inlineStr">
+        <is>
+          <t>Двойной счет шоурума</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Финансы</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Кредитный договор, соглашения о ставке и сроке, модель банка T0 и T1</t>
+        </is>
+      </c>
+      <c r="C50" s="57" t="inlineStr">
+        <is>
+          <t>F1, F2, F3</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Сценарии тела, ставки и срока</t>
+        </is>
+      </c>
+      <c r="E50" s="55" t="inlineStr">
+        <is>
+          <t>Проценты нельзя наследовать от капитальных затрат reliable</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Финансы</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Регистр начисленных и капитализированных процентов</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Запрет двойного счета</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Проценты не капитализированы второй раз внутри СМР</t>
+        </is>
+      </c>
+      <c r="E51" s="55" t="inlineStr">
+        <is>
+          <t>Риск двойной капитализации</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Финансы</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Полисы и расчеты премий</t>
+        </is>
+      </c>
+      <c r="C52" s="57" t="inlineStr">
+        <is>
+          <t>F1, F2, F3</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Тариф, страховая сумма и срок полиса</t>
+        </is>
+      </c>
+      <c r="E52" s="55" t="inlineStr">
+        <is>
+          <t>Страхование остается котловой суммой</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Финансы</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Положение о резерве и регистр использования каждого существенного транша</t>
+        </is>
+      </c>
+      <c r="C53" s="55" t="inlineStr">
+        <is>
+          <t>F3 и перенос в статьи</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Куда ушел резерв и не снят ли он второй раз</t>
+        </is>
+      </c>
+      <c r="E53" s="55" t="inlineStr">
+        <is>
+          <t>Отрицательный резерв можно принять за экономию</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Финансы</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Договоры гарантий и расчет земельных платежей периода строительства</t>
+        </is>
+      </c>
+      <c r="C54" s="55" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Пролонгация и новые обязательные платежи</t>
+        </is>
+      </c>
+      <c r="E54" s="55" t="inlineStr">
+        <is>
+          <t>Строка 06.04 не раскрыта</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E54"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1152,7 +2600,7 @@
           <t>Ожидание</t>
         </is>
       </c>
-      <c r="D4" s="58" t="inlineStr">
+      <c r="D4" s="59" t="inlineStr">
         <is>
           <t>Сошлось</t>
         </is>
@@ -1164,14 +2612,14 @@
           <t>Базовый бюджет, руб.</t>
         </is>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="37">
         <f>'Условный пример'!C51</f>
         <v/>
       </c>
-      <c r="C5" s="59" t="n">
+      <c r="C5" s="60" t="n">
         <v>8000000000</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="61">
         <f>ABS(B5-C5)&lt;0.001</f>
         <v/>
       </c>
@@ -1182,14 +2630,14 @@
           <t>Откорректированный бюджет, руб.</t>
         </is>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="37">
         <f>'Условный пример'!D51</f>
         <v/>
       </c>
-      <c r="C6" s="59" t="n">
+      <c r="C6" s="60" t="n">
         <v>9200000000</v>
       </c>
-      <c r="D6" s="60">
+      <c r="D6" s="61">
         <f>ABS(B6-C6)&lt;0.001</f>
         <v/>
       </c>
@@ -1200,14 +2648,14 @@
           <t>Отклонение, руб.</t>
         </is>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="37">
         <f>'Условный пример'!E51</f>
         <v/>
       </c>
-      <c r="C7" s="59" t="n">
+      <c r="C7" s="60" t="n">
         <v>1200000000</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="61">
         <f>ABS(B7-C7)&lt;0.001</f>
         <v/>
       </c>
@@ -1218,14 +2666,14 @@
           <t>Фактор 1, руб.</t>
         </is>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="37">
         <f>'Условный пример'!G51</f>
         <v/>
       </c>
-      <c r="C8" s="59" t="n">
+      <c r="C8" s="60" t="n">
         <v>550000000</v>
       </c>
-      <c r="D8" s="60">
+      <c r="D8" s="61">
         <f>ABS(B8-C8)&lt;0.001</f>
         <v/>
       </c>
@@ -1236,14 +2684,14 @@
           <t>Фактор 2, руб.</t>
         </is>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="37">
         <f>'Условный пример'!H51</f>
         <v/>
       </c>
-      <c r="C9" s="59" t="n">
+      <c r="C9" s="60" t="n">
         <v>458000000</v>
       </c>
-      <c r="D9" s="60">
+      <c r="D9" s="61">
         <f>ABS(B9-C9)&lt;0.001</f>
         <v/>
       </c>
@@ -1254,14 +2702,14 @@
           <t>Фактор 3, руб.</t>
         </is>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="37">
         <f>'Условный пример'!I51</f>
         <v/>
       </c>
-      <c r="C10" s="59" t="n">
+      <c r="C10" s="60" t="n">
         <v>192000000</v>
       </c>
-      <c r="D10" s="60">
+      <c r="D10" s="61">
         <f>ABS(B10-C10)&lt;0.001</f>
         <v/>
       </c>
@@ -1272,14 +2720,14 @@
           <t>Контроль тождества, руб.</t>
         </is>
       </c>
-      <c r="B11" s="43">
+      <c r="B11" s="37">
         <f>'Условный пример'!J51</f>
         <v/>
       </c>
-      <c r="C11" s="59" t="n">
+      <c r="C11" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="61">
         <f>ABS(B11-C11)&lt;0.001</f>
         <v/>
       </c>
@@ -1290,14 +2738,14 @@
           <t>Отклонение к базе</t>
         </is>
       </c>
-      <c r="B12" s="61">
+      <c r="B12" s="62">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C12" s="62" t="n">
+      <c r="C12" s="63" t="n">
         <v>0.15</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="61">
         <f>ABS(B12-C12)&lt;0.001</f>
         <v/>
       </c>
@@ -1308,14 +2756,14 @@
           <t>Доля инфляции в приросте</t>
         </is>
       </c>
-      <c r="B13" s="61">
+      <c r="B13" s="62">
         <f>B8/B7</f>
         <v/>
       </c>
-      <c r="C13" s="62" t="n">
+      <c r="C13" s="63" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="61">
         <f>ABS(B13-C13)&lt;0.001</f>
         <v/>
       </c>
@@ -1326,14 +2774,14 @@
           <t>Доля ПСД в приросте</t>
         </is>
       </c>
-      <c r="B14" s="61">
+      <c r="B14" s="62">
         <f>B9/B7</f>
         <v/>
       </c>
-      <c r="C14" s="62" t="n">
+      <c r="C14" s="63" t="n">
         <v>0.3816666666666667</v>
       </c>
-      <c r="D14" s="60">
+      <c r="D14" s="61">
         <f>ABS(B14-C14)&lt;0.001</f>
         <v/>
       </c>
@@ -1344,14 +2792,14 @@
           <t>Доля иных причин в приросте</t>
         </is>
       </c>
-      <c r="B15" s="61">
+      <c r="B15" s="62">
         <f>B10/B7</f>
         <v/>
       </c>
-      <c r="C15" s="62" t="n">
+      <c r="C15" s="63" t="n">
         <v>0.16</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D15" s="61">
         <f>ABS(B15-C15)&lt;0.001</f>
         <v/>
       </c>
@@ -1362,7 +2810,7 @@
           <t>Позиция монолита, контроль калькулятора, руб.</t>
         </is>
       </c>
-      <c r="B17" s="48">
+      <c r="B17" s="50">
         <f>'Калькулятор позиции'!B18</f>
         <v/>
       </c>
@@ -1373,7 +2821,7 @@
           <t>Замена фасада, контроль калькулятора, руб.</t>
         </is>
       </c>
-      <c r="B18" s="48">
+      <c r="B18" s="50">
         <f>'Калькулятор позиции'!B35</f>
         <v/>
       </c>
@@ -1384,7 +2832,7 @@
           <t>Контроль производного вознаграждения, руб.</t>
         </is>
       </c>
-      <c r="B19" s="48">
+      <c r="B19" s="50">
         <f>'Производные затраты'!B26</f>
         <v/>
       </c>
@@ -1395,8 +2843,30 @@
           <t>Контроль учебного графика процентов, млн руб.</t>
         </is>
       </c>
-      <c r="B20" s="48">
+      <c r="B20" s="50">
         <f>'Производные затраты'!B51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Контроль ориентировочного бюджета, руб.</t>
+        </is>
+      </c>
+      <c r="B21" s="50">
+        <f>'Ориентировочный бюджет'!B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Контроль состава ориентировочного бюджета, руб.</t>
+        </is>
+      </c>
+      <c r="B22" s="50">
+        <f>'Ориентировочный бюджет'!B29</f>
         <v/>
       </c>
     </row>
@@ -7832,6 +9302,396 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ориентировочный бюджет до рабочей документации</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Исходного сметного объема нет. Инфляция считается на удельную ставку паспорта. К изменениям проекта относятся площадь и замена названного решения. Первый обсчет той же программы раскрывается внутри иных причин как F3d и вторым фактором не становится.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Паспорт и инфляция</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Исходный измеритель Q0</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>м² общей площади, как в модели T0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Удельная ставка a0</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>руб. без НДС за единицу измерителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Коэффициент Iex</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>дефлятор паспорта, не веса новой сметы</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Базовый бюджет B0</t>
+        </is>
+      </c>
+      <c r="B8" s="37">
+        <f>B5*B6</f>
+        <v/>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>a0 × Q0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Фактор 1. Инфляция</t>
+        </is>
+      </c>
+      <c r="B9" s="37">
+        <f>B8*(B7-1)</f>
+        <v/>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>только на сумму паспорта</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Проиндексированный паспорт</t>
+        </is>
+      </c>
+      <c r="B10" s="37">
+        <f>B8*B7</f>
+        <v/>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>B0 × Iex</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Отступление от паспорта</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Измеритель T1, Q1</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="n">
+        <v>52000</v>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>новый ТЭП той же единицы измерения</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Стоимость той же программы S</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n">
+        <v>7750000000</v>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>рабочая документация и цены T1 без лишней площади и без замененного решения</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Удельная стоимость той же программы</t>
+        </is>
+      </c>
+      <c r="B15" s="38">
+        <f>IF(B5=0,"",B14/B5)</f>
+        <v/>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>S / Q0, руб. за единицу</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Фактор 2 по измерителю</t>
+        </is>
+      </c>
+      <c r="B16" s="21">
+        <f>(B13-B5)*B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>приростная площадь в текущей полноте исходного стандарта</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Стоимость нового решения на Q0</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n">
+        <v>1400000000</v>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>замена решения, названного в паспорте</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Доля замененного решения в ставке T0</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>Allowance0 из паспорта или аналога</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>U, чистая замена</t>
+        </is>
+      </c>
+      <c r="B19" s="37">
+        <f>B17-B18*B7</f>
+        <v/>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>Cost1 − Allowance0 × Iex</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Фактор 2. Изменения ПСД</t>
+        </is>
+      </c>
+      <c r="B20" s="37">
+        <f>B16+B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>площадь и замена; детализация сюда не входит</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Факт, уточнение и прочие иные причины</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Откорректированный бюджет B1</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>8560000000</v>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>статья T1, тот же периметр</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Фактор 3. Иные причины</t>
+        </is>
+      </c>
+      <c r="B24" s="37">
+        <f>B23-B8-B9-B20</f>
+        <v/>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>остаток после инфляции и отступлений от паспорта</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>В том числе F3d, уточнение по РД</t>
+        </is>
+      </c>
+      <c r="B25" s="34">
+        <f>B14-B10</f>
+        <v/>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>S − проиндексированный паспорт; это не изменение проекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>В том числе прочие иные причины</t>
+        </is>
+      </c>
+      <c r="B26" s="21">
+        <f>B24-B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>срок, закупка, форс-мажор и налог</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Отклонение</t>
+        </is>
+      </c>
+      <c r="B27" s="37">
+        <f>B23-B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>Контроль тождества</t>
+        </is>
+      </c>
+      <c r="B28" s="34">
+        <f>B9+B20+B24-B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>F1 + F2 + F3 − отклонение, должно быть 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>Контроль состава B1</t>
+        </is>
+      </c>
+      <c r="B29" s="34">
+        <f>B14+B20+B26-B23</f>
+        <v/>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>S + F2 + прочие иные − B1, должно быть 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Числа листа — учебный пример раздела 5.10: 6,00 млрд руб. становятся 8,56 млрд руб. Из отклонения 2,56 млрд руб. инфляция паспорта составляет 1,50 млрд, изменения площади и фасада — 0,71 млрд, уточнение по рабочей документации — 0,25 млрд, прочие иные причины — 0,10 млрд.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="008064A2"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -7887,13 +9747,13 @@
           <t>Материалы</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="41" t="n">
         <v>0.62</v>
       </c>
       <c r="C5" s="31" t="n">
         <v>1.19</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="42">
         <f>B5*C5</f>
         <v/>
       </c>
@@ -7904,13 +9764,13 @@
           <t>Машины и механизмы</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="41" t="n">
         <v>0.11</v>
       </c>
       <c r="C6" s="31" t="n">
         <v>1.14</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="42">
         <f>B6*C6</f>
         <v/>
       </c>
@@ -7921,13 +9781,13 @@
           <t>Оплата труда</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="41" t="n">
         <v>0.27</v>
       </c>
       <c r="C7" s="31" t="n">
         <v>1.16</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="42">
         <f>B7*C7</f>
         <v/>
       </c>
@@ -7938,13 +9798,13 @@
           <t>Перевозка, если выделена отдельно</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="42">
         <f>B8*C8</f>
         <v/>
       </c>
@@ -7955,7 +9815,7 @@
           <t>Сумма весов</t>
         </is>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="43">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
@@ -7966,12 +9826,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Iex позиции</t>
         </is>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="44">
         <f>IF(ABS(B9-1)&gt;0.000001,"проверьте веса",SUM(D5:D8))</f>
         <v/>
       </c>
@@ -8006,7 +9866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C0C"/>
@@ -8052,7 +9912,7 @@
           <t>База T0, руб.</t>
         </is>
       </c>
-      <c r="B5" s="42" t="n">
+      <c r="B5" s="45" t="n">
         <v>3100000000</v>
       </c>
     </row>
@@ -8062,7 +9922,7 @@
           <t>Фактор 1 базы, руб.</t>
         </is>
       </c>
-      <c r="B6" s="42" t="n">
+      <c r="B6" s="45" t="n">
         <v>280000000</v>
       </c>
     </row>
@@ -8072,7 +9932,7 @@
           <t>Фактор 2 базы, руб.</t>
         </is>
       </c>
-      <c r="B7" s="42" t="n">
+      <c r="B7" s="45" t="n">
         <v>190000000</v>
       </c>
     </row>
@@ -8082,7 +9942,7 @@
           <t>Фактор 3 базы, руб.</t>
         </is>
       </c>
-      <c r="B8" s="42" t="n">
+      <c r="B8" s="45" t="n">
         <v>30000000</v>
       </c>
     </row>
@@ -8092,7 +9952,7 @@
           <t>Ставка процента T0</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="41" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -8102,7 +9962,7 @@
           <t>Ставка процента T1</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="41" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -8112,7 +9972,7 @@
           <t>Исходная численность, чел.</t>
         </is>
       </c>
-      <c r="B11" s="42" t="n">
+      <c r="B11" s="45" t="n">
         <v>12</v>
       </c>
     </row>
@@ -8122,7 +9982,7 @@
           <t>Дополнительная численность из-за ПСД, чел.</t>
         </is>
       </c>
-      <c r="B12" s="42" t="n">
+      <c r="B12" s="45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8132,7 +9992,7 @@
           <t>Исходный срок, мес.</t>
         </is>
       </c>
-      <c r="B13" s="42" t="n">
+      <c r="B13" s="45" t="n">
         <v>36</v>
       </c>
     </row>
@@ -8142,7 +10002,7 @@
           <t>Срок T1, мес.</t>
         </is>
       </c>
-      <c r="B14" s="42" t="n">
+      <c r="B14" s="45" t="n">
         <v>43</v>
       </c>
     </row>
@@ -8152,7 +10012,7 @@
           <t>Стоимость человека в месяц T0, руб.</t>
         </is>
       </c>
-      <c r="B15" s="42" t="n">
+      <c r="B15" s="45" t="n">
         <v>350000</v>
       </c>
     </row>
@@ -8172,7 +10032,7 @@
           <t>Фактическая стоимость человека в месяц T1, руб.</t>
         </is>
       </c>
-      <c r="B17" s="42" t="n">
+      <c r="B17" s="45" t="n">
         <v>410000</v>
       </c>
     </row>
@@ -8215,7 +10075,7 @@
           <t>Отклонение</t>
         </is>
       </c>
-      <c r="B22" s="43">
+      <c r="B22" s="37">
         <f>B21-B20</f>
         <v/>
       </c>
@@ -8321,20 +10181,20 @@
           <t>Выборка BASE</t>
         </is>
       </c>
-      <c r="B32" s="44" t="n">
+      <c r="B32" s="46" t="n">
         <v>100</v>
       </c>
-      <c r="C32" s="44" t="n">
+      <c r="C32" s="46" t="n">
         <v>100</v>
       </c>
-      <c r="D32" s="44" t="n">
+      <c r="D32" s="46" t="n">
         <v>100</v>
       </c>
-      <c r="E32" s="44" t="n">
+      <c r="E32" s="46" t="n">
         <v>100</v>
       </c>
-      <c r="F32" s="44" t="n"/>
-      <c r="G32" s="45">
+      <c r="F32" s="46" t="n"/>
+      <c r="G32" s="47">
         <f>SUM(B32:F32)</f>
         <v/>
       </c>
@@ -8345,20 +10205,20 @@
           <t>Выборка INF</t>
         </is>
       </c>
-      <c r="B33" s="44" t="n">
+      <c r="B33" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="C33" s="44" t="n">
+      <c r="C33" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="D33" s="44" t="n">
+      <c r="D33" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="E33" s="44" t="n">
+      <c r="E33" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="F33" s="44" t="n"/>
-      <c r="G33" s="45">
+      <c r="F33" s="46" t="n"/>
+      <c r="G33" s="47">
         <f>SUM(B33:F33)</f>
         <v/>
       </c>
@@ -8369,20 +10229,20 @@
           <t>Выборка PSD</t>
         </is>
       </c>
-      <c r="B34" s="44" t="n">
+      <c r="B34" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="C34" s="44" t="n">
+      <c r="C34" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="D34" s="44" t="n">
+      <c r="D34" s="46" t="n">
         <v>150</v>
       </c>
-      <c r="E34" s="44" t="n">
+      <c r="E34" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="F34" s="44" t="n"/>
-      <c r="G34" s="45">
+      <c r="F34" s="46" t="n"/>
+      <c r="G34" s="47">
         <f>SUM(B34:F34)</f>
         <v/>
       </c>
@@ -8393,22 +10253,22 @@
           <t>Выборка ACT</t>
         </is>
       </c>
-      <c r="B35" s="44" t="n">
+      <c r="B35" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="C35" s="44" t="n">
+      <c r="C35" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="D35" s="44" t="n">
+      <c r="D35" s="46" t="n">
         <v>150</v>
       </c>
-      <c r="E35" s="44" t="n">
+      <c r="E35" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="F35" s="44" t="n">
+      <c r="F35" s="46" t="n">
         <v>40</v>
       </c>
-      <c r="G35" s="45">
+      <c r="G35" s="47">
         <f>SUM(B35:F35)</f>
         <v/>
       </c>
@@ -8419,7 +10279,7 @@
           <t>Ставка за квартал BASE / INF / PSD</t>
         </is>
       </c>
-      <c r="B36" s="37" t="n">
+      <c r="B36" s="41" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -8429,7 +10289,7 @@
           <t>Ставка за квартал ACT</t>
         </is>
       </c>
-      <c r="B37" s="37" t="n">
+      <c r="B37" s="41" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -8439,22 +10299,22 @@
           <t>Долг на начало, BASE</t>
         </is>
       </c>
-      <c r="B39" s="45" t="n">
+      <c r="B39" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="45">
+      <c r="C39" s="47">
         <f>IF(C32="","",B39+B32)</f>
         <v/>
       </c>
-      <c r="D39" s="45">
+      <c r="D39" s="47">
         <f>IF(D32="","",C39+C32)</f>
         <v/>
       </c>
-      <c r="E39" s="45">
+      <c r="E39" s="47">
         <f>IF(E32="","",D39+D32)</f>
         <v/>
       </c>
-      <c r="F39" s="45">
+      <c r="F39" s="47">
         <f>IF(F32="","",E39+E32)</f>
         <v/>
       </c>
@@ -8465,27 +10325,27 @@
           <t>Проценты, BASE</t>
         </is>
       </c>
-      <c r="B40" s="46">
+      <c r="B40" s="48">
         <f>IF(OR(B32="",B39=""),"",B39*$B$36)</f>
         <v/>
       </c>
-      <c r="C40" s="46">
+      <c r="C40" s="48">
         <f>IF(OR(C32="",C39=""),"",C39*$B$36)</f>
         <v/>
       </c>
-      <c r="D40" s="46">
+      <c r="D40" s="48">
         <f>IF(OR(D32="",D39=""),"",D39*$B$36)</f>
         <v/>
       </c>
-      <c r="E40" s="46">
+      <c r="E40" s="48">
         <f>IF(OR(E32="",E39=""),"",E39*$B$36)</f>
         <v/>
       </c>
-      <c r="F40" s="46">
+      <c r="F40" s="48">
         <f>IF(OR(F32="",F39=""),"",F39*$B$36)</f>
         <v/>
       </c>
-      <c r="G40" s="47">
+      <c r="G40" s="49">
         <f>SUM(B40:F40)</f>
         <v/>
       </c>
@@ -8496,22 +10356,22 @@
           <t>Долг на начало, INF</t>
         </is>
       </c>
-      <c r="B41" s="45" t="n">
+      <c r="B41" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="45">
+      <c r="C41" s="47">
         <f>IF(C33="","",B41+B33)</f>
         <v/>
       </c>
-      <c r="D41" s="45">
+      <c r="D41" s="47">
         <f>IF(D33="","",C41+C33)</f>
         <v/>
       </c>
-      <c r="E41" s="45">
+      <c r="E41" s="47">
         <f>IF(E33="","",D41+D33)</f>
         <v/>
       </c>
-      <c r="F41" s="45">
+      <c r="F41" s="47">
         <f>IF(F33="","",E41+E33)</f>
         <v/>
       </c>
@@ -8522,27 +10382,27 @@
           <t>Проценты, INF</t>
         </is>
       </c>
-      <c r="B42" s="46">
+      <c r="B42" s="48">
         <f>IF(OR(B33="",B41=""),"",B41*$B$36)</f>
         <v/>
       </c>
-      <c r="C42" s="46">
+      <c r="C42" s="48">
         <f>IF(OR(C33="",C41=""),"",C41*$B$36)</f>
         <v/>
       </c>
-      <c r="D42" s="46">
+      <c r="D42" s="48">
         <f>IF(OR(D33="",D41=""),"",D41*$B$36)</f>
         <v/>
       </c>
-      <c r="E42" s="46">
+      <c r="E42" s="48">
         <f>IF(OR(E33="",E41=""),"",E41*$B$36)</f>
         <v/>
       </c>
-      <c r="F42" s="46">
+      <c r="F42" s="48">
         <f>IF(OR(F33="",F41=""),"",F41*$B$36)</f>
         <v/>
       </c>
-      <c r="G42" s="47">
+      <c r="G42" s="49">
         <f>SUM(B42:F42)</f>
         <v/>
       </c>
@@ -8553,22 +10413,22 @@
           <t>Долг на начало, PSD</t>
         </is>
       </c>
-      <c r="B43" s="45" t="n">
+      <c r="B43" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="C43" s="45">
+      <c r="C43" s="47">
         <f>IF(C34="","",B43+B34)</f>
         <v/>
       </c>
-      <c r="D43" s="45">
+      <c r="D43" s="47">
         <f>IF(D34="","",C43+C34)</f>
         <v/>
       </c>
-      <c r="E43" s="45">
+      <c r="E43" s="47">
         <f>IF(E34="","",D43+D34)</f>
         <v/>
       </c>
-      <c r="F43" s="45">
+      <c r="F43" s="47">
         <f>IF(F34="","",E43+E34)</f>
         <v/>
       </c>
@@ -8579,27 +10439,27 @@
           <t>Проценты, PSD</t>
         </is>
       </c>
-      <c r="B44" s="46">
+      <c r="B44" s="48">
         <f>IF(OR(B34="",B43=""),"",B43*$B$36)</f>
         <v/>
       </c>
-      <c r="C44" s="46">
+      <c r="C44" s="48">
         <f>IF(OR(C34="",C43=""),"",C43*$B$36)</f>
         <v/>
       </c>
-      <c r="D44" s="46">
+      <c r="D44" s="48">
         <f>IF(OR(D34="",D43=""),"",D43*$B$36)</f>
         <v/>
       </c>
-      <c r="E44" s="46">
+      <c r="E44" s="48">
         <f>IF(OR(E34="",E43=""),"",E43*$B$36)</f>
         <v/>
       </c>
-      <c r="F44" s="46">
+      <c r="F44" s="48">
         <f>IF(OR(F34="",F43=""),"",F43*$B$36)</f>
         <v/>
       </c>
-      <c r="G44" s="47">
+      <c r="G44" s="49">
         <f>SUM(B44:F44)</f>
         <v/>
       </c>
@@ -8610,22 +10470,22 @@
           <t>Долг на начало, ACT</t>
         </is>
       </c>
-      <c r="B45" s="45" t="n">
+      <c r="B45" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="C45" s="45">
+      <c r="C45" s="47">
         <f>IF(C35="","",B45+B35)</f>
         <v/>
       </c>
-      <c r="D45" s="45">
+      <c r="D45" s="47">
         <f>IF(D35="","",C45+C35)</f>
         <v/>
       </c>
-      <c r="E45" s="45">
+      <c r="E45" s="47">
         <f>IF(E35="","",D45+D35)</f>
         <v/>
       </c>
-      <c r="F45" s="45">
+      <c r="F45" s="47">
         <f>IF(F35="","",E45+E35)</f>
         <v/>
       </c>
@@ -8636,27 +10496,27 @@
           <t>Проценты, ACT</t>
         </is>
       </c>
-      <c r="B46" s="46">
+      <c r="B46" s="48">
         <f>IF(OR(B35="",B45=""),"",B45*$B$37)</f>
         <v/>
       </c>
-      <c r="C46" s="46">
+      <c r="C46" s="48">
         <f>IF(OR(C35="",C45=""),"",C45*$B$37)</f>
         <v/>
       </c>
-      <c r="D46" s="46">
+      <c r="D46" s="48">
         <f>IF(OR(D35="",D45=""),"",D45*$B$37)</f>
         <v/>
       </c>
-      <c r="E46" s="46">
+      <c r="E46" s="48">
         <f>IF(OR(E35="",E45=""),"",E45*$B$37)</f>
         <v/>
       </c>
-      <c r="F46" s="46">
+      <c r="F46" s="48">
         <f>IF(OR(F35="",F45=""),"",F45*$B$37)</f>
         <v/>
       </c>
-      <c r="G46" s="47">
+      <c r="G46" s="49">
         <f>SUM(B46:F46)</f>
         <v/>
       </c>
@@ -8667,7 +10527,7 @@
           <t>Фактор 1 процентов</t>
         </is>
       </c>
-      <c r="B48" s="48">
+      <c r="B48" s="50">
         <f>G42-G40</f>
         <v/>
       </c>
@@ -8683,7 +10543,7 @@
           <t>Фактор 2 процентов</t>
         </is>
       </c>
-      <c r="B49" s="48">
+      <c r="B49" s="50">
         <f>G44-G42</f>
         <v/>
       </c>
@@ -8694,18 +10554,18 @@
           <t>Фактор 3 процентов</t>
         </is>
       </c>
-      <c r="B50" s="48">
+      <c r="B50" s="50">
         <f>G46-G44</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="40" t="inlineStr">
+      <c r="A51" s="39" t="inlineStr">
         <is>
           <t>Контроль процентов</t>
         </is>
       </c>
-      <c r="B51" s="47">
+      <c r="B51" s="49">
         <f>B48+B49+B50-(G46-G40)</f>
         <v/>
       </c>
@@ -8720,7 +10580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -8788,22 +10648,22 @@
           <t>Доля строки без подписанного договора</t>
         </is>
       </c>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>менее 15%</t>
         </is>
       </c>
-      <c r="C5" s="50" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>от 15% до 40%</t>
         </is>
       </c>
-      <c r="D5" s="51" t="inlineStr">
+      <c r="D5" s="52" t="inlineStr">
         <is>
           <t>более 40%</t>
         </is>
       </c>
-      <c r="E5" s="52" t="n">
+      <c r="E5" s="53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8813,22 +10673,22 @@
           <t>Тип цены подписанного объема</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>твердая цена без эскалации</t>
         </is>
       </c>
-      <c r="C6" s="50" t="inlineStr">
+      <c r="C6" s="51" t="inlineStr">
         <is>
           <t>единичные расценки</t>
         </is>
       </c>
-      <c r="D6" s="51" t="inlineStr">
+      <c r="D6" s="52" t="inlineStr">
         <is>
           <t>открытая цена или договор не подписан</t>
         </is>
       </c>
-      <c r="E6" s="52" t="n">
+      <c r="E6" s="53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8838,22 +10698,22 @@
           <t>Зрелость рабочей документации</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>заморожена не менее чем на 90%</t>
         </is>
       </c>
-      <c r="C7" s="50" t="inlineStr">
+      <c r="C7" s="51" t="inlineStr">
         <is>
           <t>от 60% до 90%</t>
         </is>
       </c>
-      <c r="D7" s="51" t="inlineStr">
+      <c r="D7" s="52" t="inlineStr">
         <is>
           <t>менее 60%</t>
         </is>
       </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8863,22 +10723,22 @@
           <t>Резерв против ожидаемой стоимости названных рисков</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>резерв покрывает не менее 100%</t>
         </is>
       </c>
-      <c r="C8" s="50" t="inlineStr">
+      <c r="C8" s="51" t="inlineStr">
         <is>
           <t>покрытие от 50% до 100%</t>
         </is>
       </c>
-      <c r="D8" s="51" t="inlineStr">
+      <c r="D8" s="52" t="inlineStr">
         <is>
           <t>покрытие менее 50%</t>
         </is>
       </c>
-      <c r="E8" s="52" t="n">
+      <c r="E8" s="53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8888,22 +10748,22 @@
           <t>Срок</t>
         </is>
       </c>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>есть резерв времени</t>
         </is>
       </c>
-      <c r="C9" s="50" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
         <is>
           <t>резерв выбран или задержка меньше 3 месяцев</t>
         </is>
       </c>
-      <c r="D9" s="51" t="inlineStr">
+      <c r="D9" s="52" t="inlineStr">
         <is>
           <t>задержка от 3 месяцев или вероятна претензия на срок</t>
         </is>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8913,22 +10773,22 @@
           <t>Несогласованные изменения и претензии</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>менее 1% строки</t>
         </is>
       </c>
-      <c r="C10" s="50" t="inlineStr">
+      <c r="C10" s="51" t="inlineStr">
         <is>
           <t>от 1% до 3%</t>
         </is>
       </c>
-      <c r="D10" s="51" t="inlineStr">
+      <c r="D10" s="52" t="inlineStr">
         <is>
           <t>более 3%</t>
         </is>
       </c>
-      <c r="E10" s="52" t="n">
+      <c r="E10" s="53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8938,13 +10798,13 @@
           <t>Сумма баллов</t>
         </is>
       </c>
-      <c r="E11" s="53">
+      <c r="E11" s="54">
         <f>SUM(E5:E10)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="54" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>Принудительное повышение: нет ТУ, отрицательная экспертиза, обременение или неизвестная плата за присоединение</t>
         </is>
@@ -8952,7 +10812,7 @@
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="9" t="n"/>
-      <c r="E12" s="52" t="n">
+      <c r="E12" s="53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8962,7 +10822,7 @@
           <t>Оценка</t>
         </is>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="56">
         <f>IF(E12&gt;=2,"Высокий",IF(AND(E12=1,E11&lt;=3),"Средний",IF(E11&lt;=3,"Низкий",IF(E11&lt;=7,"Средний","Высокий"))))</f>
         <v/>
       </c>
@@ -8991,1260 +10851,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F4E79"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Минимальный реестр документов для подтверждения факторов</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Класс А не присваивается по объяснительной записке. Если документа из минимума нет, сумма не получает имя соответствующего фактора.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Группа</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Документ</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Какой фактор закрывает</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Что сверяется</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Если документа нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Сквозные</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Протокол утверждения базового бюджета, модель и макродопущения T0</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>Все</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Какой файл является базой и какие дефляторы утверждены</t>
-        </is>
-      </c>
-      <c r="E5" s="54" t="inlineStr">
-        <is>
-          <t>База не идентифицирована, расчет не начинается</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Сквозные</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Файл откорректированного бюджета T1 и пояснения застройщика</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>Все</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>От какой версии отстраивается анализ</t>
-        </is>
-      </c>
-      <c r="E6" s="54" t="inlineStr">
-        <is>
-          <t>Нет предмета анализа</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Сквозные</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Реестр промежуточных версий бюджета</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>Все</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Что промежуточная версия не подменила T0</t>
-        </is>
-      </c>
-      <c r="E7" s="54" t="inlineStr">
-        <is>
-          <t>Риск подмены базы раскрывается как оговорка</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Сквозные</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Модели T0 и T1 с формулами</t>
-        </is>
-      </c>
-      <c r="C8" s="56" t="inlineStr">
-        <is>
-          <t>F1, проценты</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Ряды дефляторов, график, ставка, НДС</t>
-        </is>
-      </c>
-      <c r="E8" s="54" t="inlineStr">
-        <is>
-          <t>F1 не выше класса В</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Сквозные</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Письма Минстроя, выгрузка ФГИС ЦС, публикация Росстата на кварталы периода</t>
-        </is>
-      </c>
-      <c r="C9" s="56" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Отношение индексов, а не индекс к базе 2001 года</t>
-        </is>
-      </c>
-      <c r="E9" s="54" t="inlineStr">
-        <is>
-          <t>Называть сумму инфляцией нельзя</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Сквозные</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Графики T0 и T1, критический путь, справка о причинах сдвига</t>
-        </is>
-      </c>
-      <c r="C10" s="56" t="inlineStr">
-        <is>
-          <t>F1 против F3, реклассификация в F2</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Какие месяцы относятся к сроку, а не к индексу</t>
-        </is>
-      </c>
-      <c r="E10" s="54" t="inlineStr">
-        <is>
-          <t>Сдвиг сроков остается неразделенным</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Сквозные</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Поквартальный поток затрат без процентов и отдельно проценты</t>
-        </is>
-      </c>
-      <c r="C11" s="56" t="inlineStr">
-        <is>
-          <t>F1, F3</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Веса кварталов и сценарии долга</t>
-        </is>
-      </c>
-      <c r="E11" s="54" t="inlineStr">
-        <is>
-          <t>Допустим только средний индекс с оговоркой</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Сквозные</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Учетная политика по НДС, капитализации процентов и претензиям</t>
-        </is>
-      </c>
-      <c r="C12" s="54" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Чтобы одна сумма не попала в два режима</t>
-        </is>
-      </c>
-      <c r="E12" s="54" t="inlineStr">
-        <is>
-          <t>Оговорка о возможном двойном счете</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Сквозные</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Справка о периметре: очереди, выбытия, затраты вне бюджета</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>До факторов</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Сопоставимость итогов</t>
-        </is>
-      </c>
-      <c r="E13" s="54" t="inlineStr">
-        <is>
-          <t>Факторы могут объяснять чужой объект</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Сквозные</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Регистр фактических затрат на дату T1 против бюджета</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>Все</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Связь бюджета с фактом</t>
-        </is>
-      </c>
-      <c r="E14" s="54" t="inlineStr">
-        <is>
-          <t>Бюджет T1 может быть декларацией</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Договоры, дополнительные соглашения, протоколы цены и ведомости расценок</t>
-        </is>
-      </c>
-      <c r="C15" s="56" t="inlineStr">
-        <is>
-          <t>F1, F3</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Исходная и новая цена, формула эскалации</t>
-        </is>
-      </c>
-      <c r="E15" s="54" t="inlineStr">
-        <is>
-          <t>Нет класса А по цене</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Калькуляция расценки или ресурсная ведомость</t>
-        </is>
-      </c>
-      <c r="C16" s="56" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Веса материалов, машин и оплаты труда</t>
-        </is>
-      </c>
-      <c r="E16" s="54" t="inlineStr">
-        <is>
-          <t>Индекс статьи становится среднеотраслевым, класс Б</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Локальные сметы и сводный сметный расчет с указанием базы и квартала цен</t>
-        </is>
-      </c>
-      <c r="C17" s="56" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>К какой базе применяется отношение индексов</t>
-        </is>
-      </c>
-      <c r="E17" s="54" t="inlineStr">
-        <is>
-          <t>Индекс легко применить не к той базе</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Расчет скользящей цены подрядчика и его первичные индексы</t>
-        </is>
-      </c>
-      <c r="C18" s="56" t="inlineStr">
-        <is>
-          <t>F1 и F3</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Разница экономической инфляции и договорной эскалации</t>
-        </is>
-      </c>
-      <c r="E18" s="54" t="inlineStr">
-        <is>
-          <t>Договорная эскалация может быть принята за дефлятор</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Счета и УПД на основные материалы, спецификации поставки</t>
-        </is>
-      </c>
-      <c r="C19" s="56" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Фактическая цена освоенного объема</t>
-        </is>
-      </c>
-      <c r="E19" s="54" t="inlineStr">
-        <is>
-          <t>F1a не подтвержден</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Не менее двух сопоставимых предложений на незакупленный остаток</t>
-        </is>
-      </c>
-      <c r="C20" s="56" t="inlineStr">
-        <is>
-          <t>F1b, pref</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Прогноз и рыночная цена нового решения</t>
-        </is>
-      </c>
-      <c r="E20" s="54" t="inlineStr">
-        <is>
-          <t>Остаток получает класс В</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Проект и рабочая документация обеих ревизий, заключения экспертизы</t>
-        </is>
-      </c>
-      <c r="C21" s="57" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Что именно изменилось в решениях</t>
-        </is>
-      </c>
-      <c r="E21" s="54" t="inlineStr">
-        <is>
-          <t>F2 не подтверждается</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Реестр измов с причиной и сопоставительная ведомость объемов</t>
-        </is>
-      </c>
-      <c r="C22" s="57" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Дельта количества со ссылкой на лист</t>
-        </is>
-      </c>
-      <c r="E22" s="54" t="inlineStr">
-        <is>
-          <t>Объемное отклонение остается классом В</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Спецификации оборудования и ведомости отделки обеих ревизий</t>
-        </is>
-      </c>
-      <c r="C23" s="57" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Смена класса внутри того же шифра работы</t>
-        </is>
-      </c>
-      <c r="E23" s="54" t="inlineStr">
-        <is>
-          <t>Смена класса смешивается с инфляцией</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Технические условия и расчет платы за присоединение обеих редакций</t>
-        </is>
-      </c>
-      <c r="C24" s="56" t="inlineStr">
-        <is>
-          <t>F1, F2, F3</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Мощность, тариф и навязанная трасса по отдельности</t>
-        </is>
-      </c>
-      <c r="E24" s="54" t="inlineStr">
-        <is>
-          <t>Сети не раскладываются</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Акты выполненных работ, справки о стоимости, накопительные ведомости, исполнительные схемы</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>Все по закрытому объему</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Факт объема и цены</t>
-        </is>
-      </c>
-      <c r="E25" s="54" t="inlineStr">
-        <is>
-          <t>Закрытый объем не отделен от прогноза</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Журнал работ, акты простоя, подтверждение форс-мажора, реестр претензий</t>
-        </is>
-      </c>
-      <c r="C26" s="54" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Иные причины по существу, а не остатком</t>
-        </is>
-      </c>
-      <c r="E26" s="54" t="inlineStr">
-        <is>
-          <t>Остаток F3 ограничивается классом В</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Реестр давальческих материалов заказчика</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Запрет двойного счета</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Материал не сидит и у заказчика, и у подрядчика</t>
-        </is>
-      </c>
-      <c r="E27" s="54" t="inlineStr">
-        <is>
-          <t>Риск двойного счета в заключении</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>СМР, вариант Б</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Тендерная расшифровка твердой цены, допущения и протокол конкурса</t>
-        </is>
-      </c>
-      <c r="C28" s="56" t="inlineStr">
-        <is>
-          <t>F1, F3</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Структура твердой цены и коммерческий результат</t>
-        </is>
-      </c>
-      <c r="E28" s="54" t="inlineStr">
-        <is>
-          <t>Остается параметрический мост класса Б или В</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>СМР, вариант В</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Реестр пакетов, матрица разграничения, схема временных зданий</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Запрет двойного счета</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Сумма пакетов равна статьям СМР, стыки не задвоены</t>
-        </is>
-      </c>
-      <c r="E29" s="54" t="inlineStr">
-        <is>
-          <t>Невязка блокирует вывод по статье</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Договоры на изыскания, стадии П и Р, авторский надзор</t>
-        </is>
-      </c>
-      <c r="C30" s="56" t="inlineStr">
-        <is>
-          <t>F1, F2, F3</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Цена этапа и предмет</t>
-        </is>
-      </c>
-      <c r="E30" s="54" t="inlineStr">
-        <is>
-          <t>Нет базы для ставки</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Оба задания на проектирование</t>
-        </is>
-      </c>
-      <c r="C31" s="57" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Какие разделы добавлены</t>
-        </is>
-      </c>
-      <c r="E31" s="54" t="inlineStr">
-        <is>
-          <t>Переработка не отличима от инфляции ставок</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Акты сдачи комплектов и программа дополнительных изысканий</t>
-        </is>
-      </c>
-      <c r="C32" s="57" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Связь допизысканий с новым решением</t>
-        </is>
-      </c>
-      <c r="E32" s="54" t="inlineStr">
-        <is>
-          <t>Допизыскания остаются в F3</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Ведомость переработанных разделов с причиной</t>
-        </is>
-      </c>
-      <c r="C33" s="57" t="inlineStr">
-        <is>
-          <t>F2 против F3</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Смена ТЭП отделена от ошибки проектировщика</t>
-        </is>
-      </c>
-      <c r="E33" s="54" t="inlineStr">
-        <is>
-          <t>Вся переработка падает в один фактор</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>График выпуска рабочей документации и журнал авторского надзора</t>
-        </is>
-      </c>
-      <c r="C34" s="57" t="inlineStr">
-        <is>
-          <t>F2, F3</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Выезд привязан к разделу или к лишнему месяцу</t>
-        </is>
-      </c>
-      <c r="E34" s="54" t="inlineStr">
-        <is>
-          <t>Пролонгация надзора не доказывается</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Платежные документы экспертизы с составом поданной документации</t>
-        </is>
-      </c>
-      <c r="C35" s="57" t="inlineStr">
-        <is>
-          <t>F2, F1</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Повторная экспертиза против тарифного индекса</t>
-        </is>
-      </c>
-      <c r="E35" s="54" t="inlineStr">
-        <is>
-          <t>Экспертиза не раскладывается</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Договоры заказчика, генподряда, управления, стройконтроля и охраны</t>
-        </is>
-      </c>
-      <c r="C36" s="56" t="inlineStr">
-        <is>
-          <t>F1, F2, F3</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Процент, база процента и возмещаемые затраты</t>
-        </is>
-      </c>
-      <c r="E36" s="54" t="inlineStr">
-        <is>
-          <t>Процент может задвоить ФОТ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Калькуляция базы процента генподряда</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Наследование факторов</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>В базу не входят затраты, возмещаемые отдельно</t>
-        </is>
-      </c>
-      <c r="E37" s="54" t="inlineStr">
-        <is>
-          <t>Двойной счет управления</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Штатное расписание и помесячная стоимость команды без персональных данных в отчете</t>
-        </is>
-      </c>
-      <c r="C38" s="56" t="inlineStr">
-        <is>
-          <t>F1, F3</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Индексация исходных месяцев и лишние месяцы</t>
-        </is>
-      </c>
-      <c r="E38" s="54" t="inlineStr">
-        <is>
-          <t>Рост содержания не раскладывается</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Приказы об изменении численности с указанием функции</t>
-        </is>
-      </c>
-      <c r="C39" s="57" t="inlineStr">
-        <is>
-          <t>F2 против F3</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Новые разделы проекта против удержания срока</t>
-        </is>
-      </c>
-      <c r="E39" s="54" t="inlineStr">
-        <is>
-          <t>Прирост людей остается в F3</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Счета общеплощадочных расходов по месяцам</t>
-        </is>
-      </c>
-      <c r="C40" s="54" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Месяц затраты совпадает с месяцем пролонгации</t>
-        </is>
-      </c>
-      <c r="E40" s="54" t="inlineStr">
-        <is>
-          <t>Справка о проценте роста недостаточна</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Коммерция</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Маркетинговые бюджеты, медиаплан и договоры размещений</t>
-        </is>
-      </c>
-      <c r="C41" s="56" t="inlineStr">
-        <is>
-          <t>F1, F3</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Цена исходного размещения и новые каналы</t>
-        </is>
-      </c>
-      <c r="E41" s="54" t="inlineStr">
-        <is>
-          <t>Медиаинфляция не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Коммерция</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Договоры брокеров и отчет о продажах: площадь, цена, канал</t>
-        </is>
-      </c>
-      <c r="C42" s="57" t="inlineStr">
-        <is>
-          <t>F2, F3</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Площадь из-за ТЭП отделена от цены прайса и ставки</t>
-        </is>
-      </c>
-      <c r="E42" s="54" t="inlineStr">
-        <is>
-          <t>Комиссия не раскладывается</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Коммерция</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Смета шоурума с указанием статьи, где сидит стройка</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Запрет двойного счета</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Отделка не включена и в СМР, и в коммерцию</t>
-        </is>
-      </c>
-      <c r="E43" s="54" t="inlineStr">
-        <is>
-          <t>Двойной счет шоурума</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Кредитный договор, соглашения о ставке и сроке, модель банка T0 и T1</t>
-        </is>
-      </c>
-      <c r="C44" s="56" t="inlineStr">
-        <is>
-          <t>F1, F2, F3</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Сценарии тела, ставки и срока</t>
-        </is>
-      </c>
-      <c r="E44" s="54" t="inlineStr">
-        <is>
-          <t>Проценты нельзя наследовать от капитальных затрат reliable</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Регистр начисленных и капитализированных процентов</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Запрет двойного счета</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Проценты не капитализированы второй раз внутри СМР</t>
-        </is>
-      </c>
-      <c r="E45" s="54" t="inlineStr">
-        <is>
-          <t>Риск двойной капитализации</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Полисы и расчеты премий</t>
-        </is>
-      </c>
-      <c r="C46" s="56" t="inlineStr">
-        <is>
-          <t>F1, F2, F3</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Тариф, страховая сумма и срок полиса</t>
-        </is>
-      </c>
-      <c r="E46" s="54" t="inlineStr">
-        <is>
-          <t>Страхование остается котловой суммой</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Положение о резерве и регистр использования каждого существенного транша</t>
-        </is>
-      </c>
-      <c r="C47" s="54" t="inlineStr">
-        <is>
-          <t>F3 и перенос в статьи</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Куда ушел резерв и не снят ли он второй раз</t>
-        </is>
-      </c>
-      <c r="E47" s="54" t="inlineStr">
-        <is>
-          <t>Отрицательный резерв можно принять за экономию</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Договоры гарантий и расчет земельных платежей периода строительства</t>
-        </is>
-      </c>
-      <c r="C48" s="54" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Пролонгация и новые обязательные платежи</t>
-        </is>
-      </c>
-      <c r="E48" s="54" t="inlineStr">
-        <is>
-          <t>Строка 06.04 не раскрыта</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:E48"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/templates/postateynyy-faktornyy-analiz.xlsx
+++ b/templates/postateynyy-faktornyy-analiz.xlsx
@@ -1,36 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Как пользоваться" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Классификатор" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Шаблон" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Условный пример" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Калькулятор позиции" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ориентировочный бюджет" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Индекс" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Производные затраты" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Риск" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Реестр документов" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Контроль" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как пользоваться" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Классификатор" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблон" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Условный пример" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Укрупненный анализ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калькулятор позиции" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ориентировочный бюджет" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Индекс" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Производные затраты" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Риск" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр документов" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Контроль" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Как пользоваться'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Классификатор'!$A$4:$E$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Классификатор'!$A$4:$E$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Классификатор'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Шаблон'!$A$4:$N$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Шаблон'!$A$4:$O$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Шаблон'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Условный пример'!$A$4:$N$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Условный пример'!$A$4:$O$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Условный пример'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Калькулятор позиции'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Ориентировочный бюджет'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Реестр документов'!$A$4:$E$54</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Реестр документов'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Укрупненный анализ'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Калькулятор позиции'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Ориентировочный бюджет'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Реестр документов'!$A$4:$E$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Реестр документов'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,12 +40,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0;&quot;—&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red]-0.0%;&quot;—&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -212,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -285,23 +286,47 @@
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -310,17 +335,8 @@
     <xf numFmtId="164" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -335,21 +351,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -385,10 +386,13 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -792,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -862,7 +866,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>7. Проценты, страхование и процент генподряда считаются после разложения своей базы. Калькулятор — на листе «Производные затраты».</t>
+          <t>7. Страхование и процент генподряда считаются после разложения своей базы. Проценты по кредиту в бюджет проекта не входят и в факторы не ставятся. Калькулятор процента генподряда — на листе «Производные затраты».</t>
         </is>
       </c>
     </row>
@@ -876,14 +880,14 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>9. Риск до ввода — это риск нового роста сверх откорректированного бюджета, а не объяснение уже включенного отклонения.</t>
+          <t>9. Риск до ввода — это риск нового роста сверх откорректированного бюджета. Качественная оценка стоит в колонке «Риск до ввода», величина в рублях — в колонке «Сумма риска». В тождество факторов сумма риска не входит.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>10. Лист «Условный пример» содержит учебный проект с ростом бюджета на 15%. Это не заключение по реальному объекту.</t>
+          <t>10. Лист «Условный пример» — постатейная таблица. Под ней упрощенные формулы сумм факторов. Лист «Укрупненный анализ» сводит те же цифры в пять групп. Это не заключение по реальному объекту.</t>
         </is>
       </c>
     </row>
@@ -967,7 +971,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Пустая рабочая таблица с формулами</t>
+          <t>Пустая постатейная таблица с формулами</t>
         </is>
       </c>
       <c r="C21" s="8" t="n"/>
@@ -983,7 +987,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Заполненный пример: 8,0 млрд руб. → 9,2 млрд руб.</t>
+          <t>Постатейный пример без процентов по кредиту: 7,02 млрд руб. → 8,175 млрд руб.</t>
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
@@ -994,12 +998,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Калькулятор позиции</t>
+          <t>Укрупненный анализ</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Формула трех факторов для одной работы</t>
+          <t>Пять групп: СМР, ПИР, наружные сети и ТУ, коммерческие, административные</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
@@ -1010,12 +1014,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Ориентировочный бюджет</t>
+          <t>Калькулятор позиции</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Удельная ставка до рабочей документации: инфляция, отступление от паспорта и уточнение</t>
+          <t>Формула трех факторов для одной работы</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
@@ -1026,12 +1030,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Индекс</t>
+          <t>Ориентировочный бюджет</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Сборка коэффициента инфляции из весов ресурсов</t>
+          <t>Удельная ставка до рабочей документации: инфляция, отступление от паспорта и уточнение</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
@@ -1042,12 +1046,12 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Производные затраты</t>
+          <t>Индекс</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Процент генподряда, содержание команды и учебный график процентов</t>
+          <t>Сборка коэффициента инфляции из весов ресурсов</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
@@ -1058,12 +1062,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Риск</t>
+          <t>Производные затраты</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Шкала баллов до ввода в эксплуатацию</t>
+          <t>Процент генподряда и содержание команды. Процентов по кредиту на листе нет</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
@@ -1074,12 +1078,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Реестр документов</t>
+          <t>Риск</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Минимальный комплект доказательств по факторам</t>
+          <t>Шкала баллов до ввода в эксплуатацию</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -1090,12 +1094,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Контроль</t>
+          <t>Реестр документов</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Сверка итога условного примера</t>
+          <t>Минимальный комплект доказательств по факторам</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
@@ -1103,8 +1107,24 @@
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="9" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Контроль</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Сверка итога условного примера</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="A12:F12"/>
@@ -1124,6 +1144,7 @@
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B20:F20"/>
@@ -1139,11 +1160,284 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Оценка риска дальнейшего роста бюджета до ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Шкала оценивает новое отклонение сверх откорректированного бюджета. Она не переразлагает уже учтенные факторы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Признак</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>0 баллов</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>1 балл</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2 балла</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Балл строки</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Доля строки без подписанного договора</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>менее 15%</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>от 15% до 40%</t>
+        </is>
+      </c>
+      <c r="D5" s="52" t="inlineStr">
+        <is>
+          <t>более 40%</t>
+        </is>
+      </c>
+      <c r="E5" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Тип цены подписанного объема</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>твердая цена без эскалации</t>
+        </is>
+      </c>
+      <c r="C6" s="51" t="inlineStr">
+        <is>
+          <t>единичные расценки</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>открытая цена или договор не подписан</t>
+        </is>
+      </c>
+      <c r="E6" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Зрелость рабочей документации</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>заморожена не менее чем на 90%</t>
+        </is>
+      </c>
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>от 60% до 90%</t>
+        </is>
+      </c>
+      <c r="D7" s="52" t="inlineStr">
+        <is>
+          <t>менее 60%</t>
+        </is>
+      </c>
+      <c r="E7" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Резерв против ожидаемой стоимости названных рисков</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>резерв покрывает не менее 100%</t>
+        </is>
+      </c>
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t>покрытие от 50% до 100%</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>покрытие менее 50%</t>
+        </is>
+      </c>
+      <c r="E8" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Срок</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>есть резерв времени</t>
+        </is>
+      </c>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>резерв выбран или задержка меньше 3 месяцев</t>
+        </is>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>задержка от 3 месяцев или вероятна претензия на срок</t>
+        </is>
+      </c>
+      <c r="E9" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Несогласованные изменения и претензии</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>менее 1% строки</t>
+        </is>
+      </c>
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>от 1% до 3%</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>более 3%</t>
+        </is>
+      </c>
+      <c r="E10" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Сумма баллов</t>
+        </is>
+      </c>
+      <c r="E11" s="54">
+        <f>SUM(E5:E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>Принудительное повышение: нет ТУ, отрицательная экспертиза, обременение или неизвестная плата за присоединение</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Оценка</t>
+        </is>
+      </c>
+      <c r="E13" s="56">
+        <f>IF(E12&gt;=2,"Высокий",IF(AND(E12=1,E11&lt;=3),"Средний",IF(E11&lt;=3,"Низкий",IF(E11&lt;=7,"Средний","Высокий"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>0–3 балла — низкий риск, 4–7 — средний, 8–12 — высокий. Одно блокирующее обстоятельство поднимает оценку не ниже средней, два — до высокой. Величина возможного удорожания в рублях вносится в колонку «Сумма риска» постатейной таблицы и в тождество факторов не входит.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A15:E15"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"0,1,2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"0,1,2"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1156,14 +1450,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Минимальный реестр документов для подтверждения факторов</t>
+          <t>Минимальный реестр документов для анализа увеличения бюджета</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Класс А не присваивается по объяснительной записке. Если документа из минимума нет, сумма не получает имя соответствующего фактора.</t>
+          <t>В запросе заказчику только документы, без которых фактор нельзя подтвердить. Объяснительная записка документ не заменяет. Проценты по кредиту не запрашиваются: в бюджет проекта они не входят.</t>
         </is>
       </c>
     </row>
@@ -1256,22 +1550,22 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Реестр промежуточных версий бюджета</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>Все</t>
+          <t>Письма Минстроя, выгрузка ФГИС ЦС или публикация Росстата</t>
+        </is>
+      </c>
+      <c r="C7" s="57" t="inlineStr">
+        <is>
+          <t>F1</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Что промежуточная версия не подменила T0</t>
+          <t>Отношение индексов, а не индекс к базе 2001 года</t>
         </is>
       </c>
       <c r="E7" s="55" t="inlineStr">
         <is>
-          <t>Риск подмены базы раскрывается как оговорка</t>
+          <t>Называть сумму инфляцией нельзя</t>
         </is>
       </c>
     </row>
@@ -1283,22 +1577,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Модели T0 и T1 с формулами</t>
-        </is>
-      </c>
-      <c r="C8" s="57" t="inlineStr">
-        <is>
-          <t>F1, проценты</t>
+          <t>Графики T0 и T1 и справка о причинах сдвига</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>F3 против F1</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Ряды дефляторов, график, ставка, НДС</t>
+          <t>Какие месяцы относятся к сроку, а не к индексу</t>
         </is>
       </c>
       <c r="E8" s="55" t="inlineStr">
         <is>
-          <t>F1 не выше класса В</t>
+          <t>Сдвиг сроков остается неразделенным</t>
         </is>
       </c>
     </row>
@@ -1310,22 +1604,22 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Письма Минстроя, выгрузка ФГИС ЦС, публикация Росстата на кварталы периода</t>
-        </is>
-      </c>
-      <c r="C9" s="57" t="inlineStr">
-        <is>
-          <t>F1</t>
+          <t>Справка о периметре: очереди, выбытия, затраты вне бюджета</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>До факторов</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Отношение индексов, а не индекс к базе 2001 года</t>
+          <t>Сопоставимость итогов</t>
         </is>
       </c>
       <c r="E9" s="55" t="inlineStr">
         <is>
-          <t>Называть сумму инфляцией нельзя</t>
+          <t>Факторы могут объяснять чужой объект</t>
         </is>
       </c>
     </row>
@@ -1337,142 +1631,142 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Графики T0 и T1, критический путь, справка о причинах сдвига</t>
-        </is>
-      </c>
-      <c r="C10" s="57" t="inlineStr">
-        <is>
-          <t>F1 против F3, реклассификация в F2</t>
+          <t>Регистр фактических затрат на дату T1 против бюджета</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Все</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Какие месяцы относятся к сроку, а не к индексу</t>
+          <t>Бюджет T1 связан с фактом</t>
         </is>
       </c>
       <c r="E10" s="55" t="inlineStr">
         <is>
-          <t>Сдвиг сроков остается неразделенным</t>
+          <t>Бюджет T1 может быть декларацией</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Сквозные</t>
+          <t>Ориентировочный бюджет</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Поквартальный поток затрат без процентов и отдельно проценты</t>
+          <t>Модель T0: удельная ставка, состав, дата цен, дефлятор, ТЭП и задание</t>
         </is>
       </c>
       <c r="C11" s="57" t="inlineStr">
         <is>
-          <t>F1, F3</t>
+          <t>F1, F2</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Веса кварталов и сценарии долга</t>
+          <t>Паспорт программы, от которого считаются инфляция и отступление</t>
         </is>
       </c>
       <c r="E11" s="55" t="inlineStr">
         <is>
-          <t>Допустим только средний индекс с оговоркой</t>
+          <t>Инфляцию и изменение проекта не от чего считать</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Сквозные</t>
+          <t>Ориентировочный бюджет</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Учетная политика по НДС, капитализации процентов и претензиям</t>
+          <t>Перечень исключений из ставки и резерв на недопроектированность</t>
         </is>
       </c>
       <c r="C12" s="55" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3d</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Чтобы одна сумма не попала в два режима</t>
+          <t>Что ставка не обещала</t>
         </is>
       </c>
       <c r="E12" s="55" t="inlineStr">
         <is>
-          <t>Оговорка о возможном двойном счете</t>
+          <t>Уточнение смешивается с пропуском периметра</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Сквозные</t>
+          <t>Ориентировочный бюджет</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Справка о периметре: очереди, выбытия, затраты вне бюджета</t>
+          <t>Рабочая документация и сметы T1 и таблица отступлений, исключенных из стоимости той же программы</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>До факторов</t>
+          <t>S и F3d</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Сопоставимость итогов</t>
+          <t>Стоимость той же программы в ценах T1</t>
         </is>
       </c>
       <c r="E13" s="55" t="inlineStr">
         <is>
-          <t>Факторы могут объяснять чужой объект</t>
+          <t>F3d не доказано</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Сквозные</t>
+          <t>СМР</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Регистр фактических затрат на дату T1 против бюджета</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>Все</t>
+          <t>Договоры, дополнительные соглашения и ведомости расценок обеих дат</t>
+        </is>
+      </c>
+      <c r="C14" s="57" t="inlineStr">
+        <is>
+          <t>F1, F3</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Связь бюджета с фактом</t>
+          <t>Исходная и новая цена, формула эскалации</t>
         </is>
       </c>
       <c r="E14" s="55" t="inlineStr">
         <is>
-          <t>Бюджет T1 может быть декларацией</t>
+          <t>Нет подтверждения цены</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Ориентировочный бюджет</t>
+          <t>СМР</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Модель T0 с формулой удельной ставки, составом включенных затрат, датой цен и дефлятором</t>
+          <t>Калькуляция существенных расценок или веса материалов, машин и оплаты труда</t>
         </is>
       </c>
       <c r="C15" s="57" t="inlineStr">
@@ -1482,24 +1776,24 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Ставка a0 и измеритель Q0, от которых считается инфляция</t>
+          <t>Из чего собран индекс статьи</t>
         </is>
       </c>
       <c r="E15" s="55" t="inlineStr">
         <is>
-          <t>Инфляцию начислять не на что</t>
+          <t>Индекс становится среднеотраслевым, класс не выше Б</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ориентировочный бюджет</t>
+          <t>СМР</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Лист ТЭП и задание на проектирование редакции T0</t>
+          <t>Проект и рабочая документация обеих ревизий, реестр измов и сопоставительная ведомость объемов</t>
         </is>
       </c>
       <c r="C16" s="58" t="inlineStr">
@@ -1509,1043 +1803,368 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Паспорт программы, от которой считается отступление</t>
+          <t>Что изменилось в решениях и количествах</t>
         </is>
       </c>
       <c r="E16" s="55" t="inlineStr">
         <is>
-          <t>Первый обсчет нельзя отделить от изменения проекта</t>
+          <t>F2 не подтверждается</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Ориентировочный бюджет</t>
+          <t>СМР</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Концепция или стадия П с пометкой, была ли она основанием бюджета</t>
+          <t>Спецификации оборудования и ведомости отделки обеих ревизий, если менялся класс</t>
         </is>
       </c>
       <c r="C17" s="58" t="inlineStr">
         <is>
-          <t>F2 против F3d</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Названные решения отделены от решений, которых в основании не было</t>
+          <t>Смена класса внутри того же шифра работы</t>
         </is>
       </c>
       <c r="E17" s="55" t="inlineStr">
         <is>
-          <t>Любая рабочая документация выглядит как изменение</t>
+          <t>Смена класса смешивается с инфляцией</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Ориентировочный бюджет</t>
+          <t>СМР</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Расчет аналога с долями конструктива, фасада и инженерных систем</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>U и F1</t>
+          <t>Технические условия и расчет платы за присоединение обеих редакций</t>
+        </is>
+      </c>
+      <c r="C18" s="57" t="inlineStr">
+        <is>
+          <t>F1, F2, F3</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Доля замененного решения и структура индекса, утвержденная до сметы T1</t>
+          <t>Мощность, тариф и навязанная трасса по отдельности</t>
         </is>
       </c>
       <c r="E18" s="55" t="inlineStr">
         <is>
-          <t>Доля замены назначается произвольно, класс В</t>
+          <t>Сети не раскладываются</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Ориентировочный бюджет</t>
+          <t>СМР</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Перечень исключений из удельной ставки и резерв на недопроектированность</t>
-        </is>
-      </c>
-      <c r="C19" s="55" t="inlineStr">
-        <is>
-          <t>F3d</t>
+          <t>Акты, справки о стоимости и накопительные ведомости по закрытому объему</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Все по закрытому объему</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Что ставка не обещала и какой резерв это покрывал</t>
+          <t>Факт объема и цены</t>
         </is>
       </c>
       <c r="E19" s="55" t="inlineStr">
         <is>
-          <t>Уточнение смешивается с пропуском периметра</t>
+          <t>Закрытый объем не отделен от прогноза</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Ориентировочный бюджет</t>
+          <t>СМР</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Рабочая документация и сметы T1 плюс таблица исключенных отступлений от паспорта</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>S и F3d</t>
+          <t>Реестр претензий, простоев и форс-мажора по существенным суммам иных причин</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>F3</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Стоимость той же программы в ценах T1</t>
+          <t>Иные причины по документу, а не остатком</t>
         </is>
       </c>
       <c r="E20" s="55" t="inlineStr">
         <is>
-          <t>F3d становится остатком без доказательства</t>
+          <t>Остаток F3 ограничивается классом В</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>СМР</t>
+          <t>СМР, без генподряда</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Договоры, дополнительные соглашения, протоколы цены и ведомости расценок</t>
-        </is>
-      </c>
-      <c r="C21" s="57" t="inlineStr">
-        <is>
-          <t>F1, F3</t>
+          <t>Реестр прямых договоров и матрица разграничения работ и поставок</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Запрет двойного счета</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Исходная и новая цена, формула эскалации</t>
+          <t>Сумма пакетов равна статьям СМР</t>
         </is>
       </c>
       <c r="E21" s="55" t="inlineStr">
         <is>
-          <t>Нет класса А по цене</t>
+          <t>Невязка блокирует вывод по статье</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>СМР</t>
+          <t>ПИР</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Калькуляция расценки или ресурсная ведомость</t>
+          <t>Договоры на изыскания, проект, рабочую документацию и авторский надзор и оба задания на проектирование</t>
         </is>
       </c>
       <c r="C22" s="57" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1, F2, F3</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Веса материалов, машин и оплаты труда</t>
+          <t>Цена этапа и какие разделы добавлены</t>
         </is>
       </c>
       <c r="E22" s="55" t="inlineStr">
         <is>
-          <t>Индекс статьи становится среднеотраслевым, класс Б</t>
+          <t>Переработку не отделить от индекса ставок</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>СМР</t>
+          <t>ПИР</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Локальные сметы и сводный сметный расчет с указанием базы и квартала цен</t>
-        </is>
-      </c>
-      <c r="C23" s="57" t="inlineStr">
-        <is>
-          <t>F1</t>
+          <t>Ведомость переработанных разделов с причиной</t>
+        </is>
+      </c>
+      <c r="C23" s="58" t="inlineStr">
+        <is>
+          <t>F2 против F3</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>К какой базе применяется отношение индексов</t>
+          <t>Смена ТЭП отделена от ошибки проектировщика</t>
         </is>
       </c>
       <c r="E23" s="55" t="inlineStr">
         <is>
-          <t>Индекс легко применить не к той базе</t>
+          <t>Вся переработка падает в один фактор</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>СМР</t>
+          <t>Управление</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Расчет скользящей цены подрядчика и его первичные индексы</t>
+          <t>Договоры заказчика, генподряда или управляющего, строительного контроля и охраны с базой процента</t>
         </is>
       </c>
       <c r="C24" s="57" t="inlineStr">
         <is>
-          <t>F1 и F3</t>
+          <t>F1, F2, F3</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Разница экономической инфляции и договорной эскалации</t>
+          <t>Процент, база процента и возмещаемые затраты</t>
         </is>
       </c>
       <c r="E24" s="55" t="inlineStr">
         <is>
-          <t>Договорная эскалация может быть принята за дефлятор</t>
+          <t>Процент может задвоить ФОТ</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>СМР</t>
+          <t>Управление</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Счета и УПД на основные материалы, спецификации поставки</t>
+          <t>Численность, месяцы и помесячная стоимость команды на исходный и новый срок</t>
         </is>
       </c>
       <c r="C25" s="57" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1, F3</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Фактическая цена освоенного объема</t>
+          <t>Индексация исходных месяцев и лишние месяцы</t>
         </is>
       </c>
       <c r="E25" s="55" t="inlineStr">
         <is>
-          <t>F1a не подтвержден</t>
+          <t>Рост содержания не раскладывается</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>СМР</t>
+          <t>Коммерция</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Не менее двух сопоставимых предложений на незакупленный остаток</t>
+          <t>Медиаплан, договоры брокеров и отчет о площади, цене и канале; смета шоурума, если он есть</t>
         </is>
       </c>
       <c r="C26" s="57" t="inlineStr">
         <is>
-          <t>F1b, pref</t>
+          <t>F1, F2, F3</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Прогноз и рыночная цена нового решения</t>
+          <t>Медиаинфляция, площадь из-за ТЭП, ставка комиссии, отсутствие двойного счета стройки</t>
         </is>
       </c>
       <c r="E26" s="55" t="inlineStr">
         <is>
-          <t>Остаток получает класс В</t>
+          <t>Коммерция не раскладывается</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>СМР</t>
+          <t>Финансы</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Проект и рабочая документация обеих ревизий, заключения экспертизы</t>
-        </is>
-      </c>
-      <c r="C27" s="58" t="inlineStr">
-        <is>
-          <t>F2</t>
+          <t>Полисы и расчеты страховых премий</t>
+        </is>
+      </c>
+      <c r="C27" s="57" t="inlineStr">
+        <is>
+          <t>F1, F2, F3</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Что именно изменилось в решениях</t>
+          <t>Тариф, страховая сумма и срок полиса</t>
         </is>
       </c>
       <c r="E27" s="55" t="inlineStr">
         <is>
-          <t>F2 не подтверждается</t>
+          <t>Страхование остается котловой суммой</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>СМР</t>
+          <t>Финансы</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Реестр измов с причиной и сопоставительная ведомость объемов</t>
-        </is>
-      </c>
-      <c r="C28" s="58" t="inlineStr">
-        <is>
-          <t>F2</t>
+          <t>Положение о резерве и регистр использования</t>
+        </is>
+      </c>
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t>F3 и перенос в статьи</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Дельта количества со ссылкой на лист</t>
+          <t>Куда ушел резерв и не снят ли он второй раз</t>
         </is>
       </c>
       <c r="E28" s="55" t="inlineStr">
         <is>
-          <t>Объемное отклонение остается классом В</t>
+          <t>Отрицательный резерв можно принять за экономию</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>СМР</t>
+          <t>Финансы</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Спецификации оборудования и ведомости отделки обеих ревизий</t>
-        </is>
-      </c>
-      <c r="C29" s="58" t="inlineStr">
-        <is>
-          <t>F2</t>
+          <t>Договоры гарантий и расчет обязательных платежей периода строительства</t>
+        </is>
+      </c>
+      <c r="C29" s="55" t="inlineStr">
+        <is>
+          <t>F3</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Смена класса внутри того же шифра работы</t>
+          <t>Пролонгация и новые платежи</t>
         </is>
       </c>
       <c r="E29" s="55" t="inlineStr">
         <is>
-          <t>Смена класса смешивается с инфляцией</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Технические условия и расчет платы за присоединение обеих редакций</t>
-        </is>
-      </c>
-      <c r="C30" s="57" t="inlineStr">
-        <is>
-          <t>F1, F2, F3</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Мощность, тариф и навязанная трасса по отдельности</t>
-        </is>
-      </c>
-      <c r="E30" s="55" t="inlineStr">
-        <is>
-          <t>Сети не раскладываются</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Акты выполненных работ, справки о стоимости, накопительные ведомости, исполнительные схемы</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>Все по закрытому объему</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Факт объема и цены</t>
-        </is>
-      </c>
-      <c r="E31" s="55" t="inlineStr">
-        <is>
-          <t>Закрытый объем не отделен от прогноза</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Журнал работ, акты простоя, подтверждение форс-мажора, реестр претензий</t>
-        </is>
-      </c>
-      <c r="C32" s="55" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Иные причины по существу, а не остатком</t>
-        </is>
-      </c>
-      <c r="E32" s="55" t="inlineStr">
-        <is>
-          <t>Остаток F3 ограничивается классом В</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>СМР</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Реестр давальческих материалов заказчика</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Запрет двойного счета</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Материал не сидит и у заказчика, и у подрядчика</t>
-        </is>
-      </c>
-      <c r="E33" s="55" t="inlineStr">
-        <is>
-          <t>Риск двойного счета в заключении</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>СМР, вариант Б</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Тендерная расшифровка твердой цены, допущения и протокол конкурса</t>
-        </is>
-      </c>
-      <c r="C34" s="57" t="inlineStr">
-        <is>
-          <t>F1, F3</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Структура твердой цены и коммерческий результат</t>
-        </is>
-      </c>
-      <c r="E34" s="55" t="inlineStr">
-        <is>
-          <t>Остается параметрический мост класса Б или В</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>СМР, вариант В</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Реестр пакетов, матрица разграничения, схема временных зданий</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Запрет двойного счета</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Сумма пакетов равна статьям СМР, стыки не задвоены</t>
-        </is>
-      </c>
-      <c r="E35" s="55" t="inlineStr">
-        <is>
-          <t>Невязка блокирует вывод по статье</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Договоры на изыскания, стадии П и Р, авторский надзор</t>
-        </is>
-      </c>
-      <c r="C36" s="57" t="inlineStr">
-        <is>
-          <t>F1, F2, F3</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Цена этапа и предмет</t>
-        </is>
-      </c>
-      <c r="E36" s="55" t="inlineStr">
-        <is>
-          <t>Нет базы для ставки</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Оба задания на проектирование</t>
-        </is>
-      </c>
-      <c r="C37" s="58" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Какие разделы добавлены</t>
-        </is>
-      </c>
-      <c r="E37" s="55" t="inlineStr">
-        <is>
-          <t>Переработка не отличима от инфляции ставок</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Акты сдачи комплектов и программа дополнительных изысканий</t>
-        </is>
-      </c>
-      <c r="C38" s="58" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Связь допизысканий с новым решением</t>
-        </is>
-      </c>
-      <c r="E38" s="55" t="inlineStr">
-        <is>
-          <t>Допизыскания остаются в F3</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Ведомость переработанных разделов с причиной</t>
-        </is>
-      </c>
-      <c r="C39" s="58" t="inlineStr">
-        <is>
-          <t>F2 против F3</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Смена ТЭП отделена от ошибки проектировщика</t>
-        </is>
-      </c>
-      <c r="E39" s="55" t="inlineStr">
-        <is>
-          <t>Вся переработка падает в один фактор</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>График выпуска рабочей документации и журнал авторского надзора</t>
-        </is>
-      </c>
-      <c r="C40" s="58" t="inlineStr">
-        <is>
-          <t>F2, F3</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Выезд привязан к разделу или к лишнему месяцу</t>
-        </is>
-      </c>
-      <c r="E40" s="55" t="inlineStr">
-        <is>
-          <t>Пролонгация надзора не доказывается</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>ПИР</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Платежные документы экспертизы с составом поданной документации</t>
-        </is>
-      </c>
-      <c r="C41" s="58" t="inlineStr">
-        <is>
-          <t>F2, F1</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Повторная экспертиза против тарифного индекса</t>
-        </is>
-      </c>
-      <c r="E41" s="55" t="inlineStr">
-        <is>
-          <t>Экспертиза не раскладывается</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Договоры заказчика, генподряда, управления, стройконтроля и охраны</t>
-        </is>
-      </c>
-      <c r="C42" s="57" t="inlineStr">
-        <is>
-          <t>F1, F2, F3</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Процент, база процента и возмещаемые затраты</t>
-        </is>
-      </c>
-      <c r="E42" s="55" t="inlineStr">
-        <is>
-          <t>Процент может задвоить ФОТ</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Калькуляция базы процента генподряда</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Наследование факторов</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>В базу не входят затраты, возмещаемые отдельно</t>
-        </is>
-      </c>
-      <c r="E43" s="55" t="inlineStr">
-        <is>
-          <t>Двойной счет управления</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Штатное расписание и помесячная стоимость команды без персональных данных в отчете</t>
-        </is>
-      </c>
-      <c r="C44" s="57" t="inlineStr">
-        <is>
-          <t>F1, F3</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Индексация исходных месяцев и лишние месяцы</t>
-        </is>
-      </c>
-      <c r="E44" s="55" t="inlineStr">
-        <is>
-          <t>Рост содержания не раскладывается</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Приказы об изменении численности с указанием функции</t>
-        </is>
-      </c>
-      <c r="C45" s="58" t="inlineStr">
-        <is>
-          <t>F2 против F3</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Новые разделы проекта против удержания срока</t>
-        </is>
-      </c>
-      <c r="E45" s="55" t="inlineStr">
-        <is>
-          <t>Прирост людей остается в F3</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Управление</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Счета общеплощадочных расходов по месяцам</t>
-        </is>
-      </c>
-      <c r="C46" s="55" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Месяц затраты совпадает с месяцем пролонгации</t>
-        </is>
-      </c>
-      <c r="E46" s="55" t="inlineStr">
-        <is>
-          <t>Справка о проценте роста недостаточна</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Коммерция</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Маркетинговые бюджеты, медиаплан и договоры размещений</t>
-        </is>
-      </c>
-      <c r="C47" s="57" t="inlineStr">
-        <is>
-          <t>F1, F3</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Цена исходного размещения и новые каналы</t>
-        </is>
-      </c>
-      <c r="E47" s="55" t="inlineStr">
-        <is>
-          <t>Медиаинфляция не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Коммерция</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Договоры брокеров и отчет о продажах: площадь, цена, канал</t>
-        </is>
-      </c>
-      <c r="C48" s="58" t="inlineStr">
-        <is>
-          <t>F2, F3</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Площадь из-за ТЭП отделена от цены прайса и ставки</t>
-        </is>
-      </c>
-      <c r="E48" s="55" t="inlineStr">
-        <is>
-          <t>Комиссия не раскладывается</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Коммерция</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Смета шоурума с указанием статьи, где сидит стройка</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>Запрет двойного счета</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Отделка не включена и в СМР, и в коммерцию</t>
-        </is>
-      </c>
-      <c r="E49" s="55" t="inlineStr">
-        <is>
-          <t>Двойной счет шоурума</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Кредитный договор, соглашения о ставке и сроке, модель банка T0 и T1</t>
-        </is>
-      </c>
-      <c r="C50" s="57" t="inlineStr">
-        <is>
-          <t>F1, F2, F3</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Сценарии тела, ставки и срока</t>
-        </is>
-      </c>
-      <c r="E50" s="55" t="inlineStr">
-        <is>
-          <t>Проценты нельзя наследовать от капитальных затрат reliable</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Регистр начисленных и капитализированных процентов</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Запрет двойного счета</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Проценты не капитализированы второй раз внутри СМР</t>
-        </is>
-      </c>
-      <c r="E51" s="55" t="inlineStr">
-        <is>
-          <t>Риск двойной капитализации</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Полисы и расчеты премий</t>
-        </is>
-      </c>
-      <c r="C52" s="57" t="inlineStr">
-        <is>
-          <t>F1, F2, F3</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Тариф, страховая сумма и срок полиса</t>
-        </is>
-      </c>
-      <c r="E52" s="55" t="inlineStr">
-        <is>
-          <t>Страхование остается котловой суммой</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Положение о резерве и регистр использования каждого существенного транша</t>
-        </is>
-      </c>
-      <c r="C53" s="55" t="inlineStr">
-        <is>
-          <t>F3 и перенос в статьи</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Куда ушел резерв и не снят ли он второй раз</t>
-        </is>
-      </c>
-      <c r="E53" s="55" t="inlineStr">
-        <is>
-          <t>Отрицательный резерв можно принять за экономию</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Договоры гарантий и расчет земельных платежей периода строительства</t>
-        </is>
-      </c>
-      <c r="C54" s="55" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Пролонгация и новые обязательные платежи</t>
-        </is>
-      </c>
-      <c r="E54" s="55" t="inlineStr">
-        <is>
-          <t>Строка 06.04 не раскрыта</t>
+          <t>Строка комиссий не раскрыта</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E54"/>
+  <autoFilter ref="A4:E29"/>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
@@ -2554,14 +2173,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -2612,12 +2231,12 @@
           <t>Базовый бюджет, руб.</t>
         </is>
       </c>
-      <c r="B5" s="37">
-        <f>'Условный пример'!C51</f>
+      <c r="B5" s="35">
+        <f>'Условный пример'!C50</f>
         <v/>
       </c>
       <c r="C5" s="60" t="n">
-        <v>8000000000</v>
+        <v>7020000000</v>
       </c>
       <c r="D5" s="61">
         <f>ABS(B5-C5)&lt;0.001</f>
@@ -2630,12 +2249,12 @@
           <t>Откорректированный бюджет, руб.</t>
         </is>
       </c>
-      <c r="B6" s="37">
-        <f>'Условный пример'!D51</f>
+      <c r="B6" s="35">
+        <f>'Условный пример'!D50</f>
         <v/>
       </c>
       <c r="C6" s="60" t="n">
-        <v>9200000000</v>
+        <v>8175000000</v>
       </c>
       <c r="D6" s="61">
         <f>ABS(B6-C6)&lt;0.001</f>
@@ -2648,12 +2267,12 @@
           <t>Отклонение, руб.</t>
         </is>
       </c>
-      <c r="B7" s="37">
-        <f>'Условный пример'!E51</f>
+      <c r="B7" s="35">
+        <f>'Условный пример'!E50</f>
         <v/>
       </c>
       <c r="C7" s="60" t="n">
-        <v>1200000000</v>
+        <v>1155000000</v>
       </c>
       <c r="D7" s="61">
         <f>ABS(B7-C7)&lt;0.001</f>
@@ -2666,12 +2285,12 @@
           <t>Фактор 1, руб.</t>
         </is>
       </c>
-      <c r="B8" s="37">
-        <f>'Условный пример'!G51</f>
+      <c r="B8" s="35">
+        <f>'Условный пример'!G50</f>
         <v/>
       </c>
       <c r="C8" s="60" t="n">
-        <v>550000000</v>
+        <v>535000000</v>
       </c>
       <c r="D8" s="61">
         <f>ABS(B8-C8)&lt;0.001</f>
@@ -2684,12 +2303,12 @@
           <t>Фактор 2, руб.</t>
         </is>
       </c>
-      <c r="B9" s="37">
-        <f>'Условный пример'!H51</f>
+      <c r="B9" s="35">
+        <f>'Условный пример'!H50</f>
         <v/>
       </c>
       <c r="C9" s="60" t="n">
-        <v>458000000</v>
+        <v>446000000</v>
       </c>
       <c r="D9" s="61">
         <f>ABS(B9-C9)&lt;0.001</f>
@@ -2702,12 +2321,12 @@
           <t>Фактор 3, руб.</t>
         </is>
       </c>
-      <c r="B10" s="37">
-        <f>'Условный пример'!I51</f>
+      <c r="B10" s="35">
+        <f>'Условный пример'!I50</f>
         <v/>
       </c>
       <c r="C10" s="60" t="n">
-        <v>192000000</v>
+        <v>174000000</v>
       </c>
       <c r="D10" s="61">
         <f>ABS(B10-C10)&lt;0.001</f>
@@ -2720,8 +2339,8 @@
           <t>Контроль тождества, руб.</t>
         </is>
       </c>
-      <c r="B11" s="37">
-        <f>'Условный пример'!J51</f>
+      <c r="B11" s="35">
+        <f>'Условный пример'!J50</f>
         <v/>
       </c>
       <c r="C11" s="60" t="n">
@@ -2743,7 +2362,7 @@
         <v/>
       </c>
       <c r="C12" s="63" t="n">
-        <v>0.15</v>
+        <v>0.1645299145299145</v>
       </c>
       <c r="D12" s="61">
         <f>ABS(B12-C12)&lt;0.001</f>
@@ -2761,7 +2380,7 @@
         <v/>
       </c>
       <c r="C13" s="63" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4632034632034632</v>
       </c>
       <c r="D13" s="61">
         <f>ABS(B13-C13)&lt;0.001</f>
@@ -2779,7 +2398,7 @@
         <v/>
       </c>
       <c r="C14" s="63" t="n">
-        <v>0.3816666666666667</v>
+        <v>0.3861471861471861</v>
       </c>
       <c r="D14" s="61">
         <f>ABS(B14-C14)&lt;0.001</f>
@@ -2797,75 +2416,154 @@
         <v/>
       </c>
       <c r="C15" s="63" t="n">
-        <v>0.16</v>
+        <v>0.1506493506493506</v>
       </c>
       <c r="D15" s="61">
         <f>ABS(B15-C15)&lt;0.001</f>
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Сумма риска, руб.</t>
+        </is>
+      </c>
+      <c r="B16" s="35">
+        <f>'Условный пример'!M50</f>
+        <v/>
+      </c>
+      <c r="C16" s="60" t="n">
+        <v>444000000</v>
+      </c>
+      <c r="D16" s="61">
+        <f>ABS(B16-C16)&lt;0.001</f>
+        <v/>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Позиция монолита, контроль калькулятора, руб.</t>
-        </is>
-      </c>
-      <c r="B17" s="50">
-        <f>'Калькулятор позиции'!B18</f>
+          <t>Контроль упрощенной суммы фактора 3, руб.</t>
+        </is>
+      </c>
+      <c r="B17" s="35">
+        <f>'Условный пример'!C58</f>
+        <v/>
+      </c>
+      <c r="C17" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="61">
+        <f>ABS(B17-C17)&lt;0.001</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Замена фасада, контроль калькулятора, руб.</t>
-        </is>
-      </c>
-      <c r="B18" s="50">
-        <f>'Калькулятор позиции'!B35</f>
+          <t>Укрупненный итог, базовый бюджет, руб.</t>
+        </is>
+      </c>
+      <c r="B18" s="35">
+        <f>'Укрупненный анализ'!C11</f>
+        <v/>
+      </c>
+      <c r="C18" s="60" t="n">
+        <v>7020000000</v>
+      </c>
+      <c r="D18" s="61">
+        <f>ABS(B18-C18)&lt;0.001</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Контроль производного вознаграждения, руб.</t>
-        </is>
-      </c>
-      <c r="B19" s="50">
-        <f>'Производные затраты'!B26</f>
+          <t>Укрупненный итог, контроль, руб.</t>
+        </is>
+      </c>
+      <c r="B19" s="35">
+        <f>'Укрупненный анализ'!J11</f>
+        <v/>
+      </c>
+      <c r="C19" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="61">
+        <f>ABS(B19-C19)&lt;0.001</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Контроль учебного графика процентов, млн руб.</t>
-        </is>
-      </c>
-      <c r="B20" s="50">
-        <f>'Производные затраты'!B51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Контроль ориентировочного бюджета, руб.</t>
-        </is>
-      </c>
-      <c r="B21" s="50">
-        <f>'Ориентировочный бюджет'!B28</f>
+          <t>Укрупненный итог, сумма риска, руб.</t>
+        </is>
+      </c>
+      <c r="B20" s="35">
+        <f>'Укрупненный анализ'!M11</f>
+        <v/>
+      </c>
+      <c r="C20" s="60" t="n">
+        <v>444000000</v>
+      </c>
+      <c r="D20" s="61">
+        <f>ABS(B20-C20)&lt;0.001</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
+          <t>Позиция монолита, контроль калькулятора, руб.</t>
+        </is>
+      </c>
+      <c r="B22" s="64">
+        <f>'Калькулятор позиции'!B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Замена фасада, контроль калькулятора, руб.</t>
+        </is>
+      </c>
+      <c r="B23" s="64">
+        <f>'Калькулятор позиции'!B35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Контроль производного вознаграждения, руб.</t>
+        </is>
+      </c>
+      <c r="B24" s="64">
+        <f>'Производные затраты'!B26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Контроль ориентировочного бюджета, руб.</t>
+        </is>
+      </c>
+      <c r="B25" s="64">
+        <f>'Ориентировочный бюджет'!B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
           <t>Контроль состава ориентировочного бюджета, руб.</t>
         </is>
       </c>
-      <c r="B22" s="50">
+      <c r="B26" s="64">
         <f>'Ориентировочный бюджет'!B29</f>
         <v/>
       </c>
@@ -2874,7 +2572,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D15">
+  <conditionalFormatting sqref="D5:D20">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>D5=TRUE</formula>
     </cfRule>
@@ -2894,7 +2592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3986,12 +3684,12 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Резерв инфляции в эту группу не прячется, если инфляция уже сидит в статьях.</t>
+          <t>Проценты по кредиту в группу не входят: бюджет проекта их не содержит. Резерв инфляции сюда не прячется, если инфляция уже сидит в статьях.</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Тело долга, ставка, срок, регистр резерва</t>
+          <t>Тариф страхования, регистр резерва, срок гарантий</t>
         </is>
       </c>
     </row>
@@ -4003,7 +3701,7 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Проценты на инвестиционной фазе</t>
+          <t>Страхование</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
@@ -4011,12 +3709,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Сценарии BASE, INF, PSD, ACT. Ставка кредита сама по себе в инфляцию СМР не входит.</t>
+          <t>Удорожание страховой суммы наследует факторы базы. Удлинение полиса и смена тарифа — иная причина.</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Тело долга, ставка, срок, регистр резерва</t>
+          <t>Тариф страхования, регистр резерва, срок гарантий</t>
         </is>
       </c>
     </row>
@@ -4028,7 +3726,7 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Страхование</t>
+          <t>Резерв непредвиденных расходов</t>
         </is>
       </c>
       <c r="C48" s="13" t="n">
@@ -4036,12 +3734,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Та же логика наследования базы плюс срок полиса.</t>
+          <t>Использование резерва — отрицательная сумма здесь и положительная сумма в профильной статье.</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Тело долга, ставка, срок, регистр резерва</t>
+          <t>Тариф страхования, регистр резерва, срок гарантий</t>
         </is>
       </c>
     </row>
@@ -4053,7 +3751,7 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Резерв непредвиденных расходов</t>
+          <t>Комиссии, гарантии, обязательные платежи и консультации</t>
         </is>
       </c>
       <c r="C49" s="13" t="n">
@@ -4061,42 +3759,17 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Использование резерва — отрицательная сумма здесь и положительная сумма в профильной статье.</t>
+          <t>В том числе земельные платежи периода строительства и эффект ставки НДС, если он не вынесен справочно.</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Тело долга, ставка, срок, регистр резерва</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>06.04</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>Комиссии, гарантии, обязательные платежи и консультации</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>В том числе земельные платежи периода строительства и эффект ставки НДС, если он не вынесен справочно.</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>Тело долга, ставка, срок, регистр резерва</t>
+          <t>Тариф страхования, регистр резерва, срок гарантий</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E50"/>
+  <autoFilter ref="A4:E49"/>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
@@ -4112,7 +3785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4127,8 +3800,9 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="72" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4141,7 +3815,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Единица измерения — рубль без НДС. Желтым отмечен ввод. Отклонение, процент, агрегаты и колонка «Контроль» считаются формулами. Контроль = инфляция + изменения ПСД + иные причины − отклонение и должен быть равен нулю. Агрегаты не вводятся вручную: они суммируют строки, которые стоят ниже до следующего агрегата того же или более высокого уровня.</t>
+          <t>Единица измерения — рубль без НДС. Желтым отмечен ввод. Отклонение, процент, агрегаты и колонка «Контроль» считаются формулами. Контроль = инфляция + изменения ПСД + иные причины − отклонение и должен быть равен нулю. Сумма риска — оценка возможного нового удорожания сверх откорректированного бюджета. В контроль факторов она не входит. Агрегаты не вводятся вручную: они суммируют строки, которые стоят ниже до следующего агрегата того же или более высокого уровня.</t>
         </is>
       </c>
     </row>
@@ -4208,10 +3882,15 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
+          <t>Сумма риска, руб.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
           <t>Комментарий к риску</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Класс надежности</t>
         </is>
@@ -4262,8 +3941,12 @@
       </c>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="10" t="n"/>
-      <c r="M5" s="6" t="n"/>
-      <c r="N5" s="10" t="n"/>
+      <c r="M5" s="18">
+        <f>SUM(M6,M7,M8,M9)</f>
+        <v/>
+      </c>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="10" t="n"/>
     </row>
     <row r="6" outlineLevel="1" ht="22" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
@@ -4295,8 +3978,9 @@
       </c>
       <c r="K6" s="23" t="n"/>
       <c r="L6" s="24" t="n"/>
-      <c r="M6" s="23" t="n"/>
-      <c r="N6" s="24" t="n"/>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="23" t="n"/>
+      <c r="O6" s="24" t="n"/>
     </row>
     <row r="7" outlineLevel="1" ht="22" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
@@ -4328,8 +4012,9 @@
       </c>
       <c r="K7" s="23" t="n"/>
       <c r="L7" s="24" t="n"/>
-      <c r="M7" s="23" t="n"/>
-      <c r="N7" s="24" t="n"/>
+      <c r="M7" s="20" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="24" t="n"/>
     </row>
     <row r="8" outlineLevel="1" ht="22" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
@@ -4361,8 +4046,9 @@
       </c>
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="24" t="n"/>
-      <c r="M8" s="23" t="n"/>
-      <c r="N8" s="24" t="n"/>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="23" t="n"/>
+      <c r="O8" s="24" t="n"/>
     </row>
     <row r="9" outlineLevel="1" ht="22" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
@@ -4394,8 +4080,9 @@
       </c>
       <c r="K9" s="23" t="n"/>
       <c r="L9" s="24" t="n"/>
-      <c r="M9" s="23" t="n"/>
-      <c r="N9" s="24" t="n"/>
+      <c r="M9" s="20" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="24" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
@@ -4442,8 +4129,12 @@
       </c>
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="10" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="10" t="n"/>
+      <c r="M10" s="18">
+        <f>SUM(M11,M12,M13,M14,M15)</f>
+        <v/>
+      </c>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="10" t="n"/>
     </row>
     <row r="11" outlineLevel="1" ht="22" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
@@ -4475,8 +4166,9 @@
       </c>
       <c r="K11" s="23" t="n"/>
       <c r="L11" s="24" t="n"/>
-      <c r="M11" s="23" t="n"/>
-      <c r="N11" s="24" t="n"/>
+      <c r="M11" s="20" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="24" t="n"/>
     </row>
     <row r="12" outlineLevel="1" ht="22" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
@@ -4508,8 +4200,9 @@
       </c>
       <c r="K12" s="23" t="n"/>
       <c r="L12" s="24" t="n"/>
-      <c r="M12" s="23" t="n"/>
-      <c r="N12" s="24" t="n"/>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="23" t="n"/>
+      <c r="O12" s="24" t="n"/>
     </row>
     <row r="13" outlineLevel="1" ht="22" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
@@ -4541,8 +4234,9 @@
       </c>
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="24" t="n"/>
-      <c r="M13" s="23" t="n"/>
-      <c r="N13" s="24" t="n"/>
+      <c r="M13" s="20" t="n"/>
+      <c r="N13" s="23" t="n"/>
+      <c r="O13" s="24" t="n"/>
     </row>
     <row r="14" outlineLevel="1" ht="22" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
@@ -4574,8 +4268,9 @@
       </c>
       <c r="K14" s="23" t="n"/>
       <c r="L14" s="24" t="n"/>
-      <c r="M14" s="23" t="n"/>
-      <c r="N14" s="24" t="n"/>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="23" t="n"/>
+      <c r="O14" s="24" t="n"/>
     </row>
     <row r="15" outlineLevel="1" ht="22" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
@@ -4607,8 +4302,9 @@
       </c>
       <c r="K15" s="23" t="n"/>
       <c r="L15" s="24" t="n"/>
-      <c r="M15" s="23" t="n"/>
-      <c r="N15" s="24" t="n"/>
+      <c r="M15" s="20" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="24" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
@@ -4655,8 +4351,12 @@
       </c>
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="10" t="n"/>
-      <c r="M16" s="6" t="n"/>
-      <c r="N16" s="10" t="n"/>
+      <c r="M16" s="18">
+        <f>SUM(M17,M25,M31,M37)</f>
+        <v/>
+      </c>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="10" t="n"/>
     </row>
     <row r="17" outlineLevel="1" ht="22" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -4703,8 +4403,12 @@
       </c>
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="10" t="n"/>
-      <c r="M17" s="6" t="n"/>
-      <c r="N17" s="10" t="n"/>
+      <c r="M17" s="18">
+        <f>SUM(M18,M19,M20,M21,M22,M23,M24)</f>
+        <v/>
+      </c>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="10" t="n"/>
     </row>
     <row r="18" outlineLevel="2" ht="22" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -4736,8 +4440,9 @@
       </c>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="24" t="n"/>
-      <c r="M18" s="23" t="n"/>
-      <c r="N18" s="24" t="n"/>
+      <c r="M18" s="20" t="n"/>
+      <c r="N18" s="23" t="n"/>
+      <c r="O18" s="24" t="n"/>
     </row>
     <row r="19" outlineLevel="2" ht="22" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
@@ -4769,8 +4474,9 @@
       </c>
       <c r="K19" s="23" t="n"/>
       <c r="L19" s="24" t="n"/>
-      <c r="M19" s="23" t="n"/>
-      <c r="N19" s="24" t="n"/>
+      <c r="M19" s="20" t="n"/>
+      <c r="N19" s="23" t="n"/>
+      <c r="O19" s="24" t="n"/>
     </row>
     <row r="20" outlineLevel="2" ht="22" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
@@ -4802,8 +4508,9 @@
       </c>
       <c r="K20" s="23" t="n"/>
       <c r="L20" s="24" t="n"/>
-      <c r="M20" s="23" t="n"/>
-      <c r="N20" s="24" t="n"/>
+      <c r="M20" s="20" t="n"/>
+      <c r="N20" s="23" t="n"/>
+      <c r="O20" s="24" t="n"/>
     </row>
     <row r="21" outlineLevel="2" ht="22" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
@@ -4835,8 +4542,9 @@
       </c>
       <c r="K21" s="23" t="n"/>
       <c r="L21" s="24" t="n"/>
-      <c r="M21" s="23" t="n"/>
-      <c r="N21" s="24" t="n"/>
+      <c r="M21" s="20" t="n"/>
+      <c r="N21" s="23" t="n"/>
+      <c r="O21" s="24" t="n"/>
     </row>
     <row r="22" outlineLevel="2" ht="22" customHeight="1">
       <c r="A22" s="13" t="inlineStr">
@@ -4868,8 +4576,9 @@
       </c>
       <c r="K22" s="23" t="n"/>
       <c r="L22" s="24" t="n"/>
-      <c r="M22" s="23" t="n"/>
-      <c r="N22" s="24" t="n"/>
+      <c r="M22" s="20" t="n"/>
+      <c r="N22" s="23" t="n"/>
+      <c r="O22" s="24" t="n"/>
     </row>
     <row r="23" outlineLevel="2" ht="22" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
@@ -4901,8 +4610,9 @@
       </c>
       <c r="K23" s="23" t="n"/>
       <c r="L23" s="24" t="n"/>
-      <c r="M23" s="23" t="n"/>
-      <c r="N23" s="24" t="n"/>
+      <c r="M23" s="20" t="n"/>
+      <c r="N23" s="23" t="n"/>
+      <c r="O23" s="24" t="n"/>
     </row>
     <row r="24" outlineLevel="2" ht="22" customHeight="1">
       <c r="A24" s="13" t="inlineStr">
@@ -4934,8 +4644,9 @@
       </c>
       <c r="K24" s="23" t="n"/>
       <c r="L24" s="24" t="n"/>
-      <c r="M24" s="23" t="n"/>
-      <c r="N24" s="24" t="n"/>
+      <c r="M24" s="20" t="n"/>
+      <c r="N24" s="23" t="n"/>
+      <c r="O24" s="24" t="n"/>
     </row>
     <row r="25" outlineLevel="1" ht="22" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -4982,8 +4693,12 @@
       </c>
       <c r="K25" s="6" t="n"/>
       <c r="L25" s="10" t="n"/>
-      <c r="M25" s="6" t="n"/>
-      <c r="N25" s="10" t="n"/>
+      <c r="M25" s="18">
+        <f>SUM(M26,M27,M28,M29,M30)</f>
+        <v/>
+      </c>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="10" t="n"/>
     </row>
     <row r="26" outlineLevel="2" ht="22" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
@@ -5015,8 +4730,9 @@
       </c>
       <c r="K26" s="23" t="n"/>
       <c r="L26" s="24" t="n"/>
-      <c r="M26" s="23" t="n"/>
-      <c r="N26" s="24" t="n"/>
+      <c r="M26" s="20" t="n"/>
+      <c r="N26" s="23" t="n"/>
+      <c r="O26" s="24" t="n"/>
     </row>
     <row r="27" outlineLevel="2" ht="22" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
@@ -5048,8 +4764,9 @@
       </c>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="24" t="n"/>
-      <c r="M27" s="23" t="n"/>
-      <c r="N27" s="24" t="n"/>
+      <c r="M27" s="20" t="n"/>
+      <c r="N27" s="23" t="n"/>
+      <c r="O27" s="24" t="n"/>
     </row>
     <row r="28" outlineLevel="2" ht="22" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
@@ -5081,8 +4798,9 @@
       </c>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="24" t="n"/>
-      <c r="M28" s="23" t="n"/>
-      <c r="N28" s="24" t="n"/>
+      <c r="M28" s="20" t="n"/>
+      <c r="N28" s="23" t="n"/>
+      <c r="O28" s="24" t="n"/>
     </row>
     <row r="29" outlineLevel="2" ht="22" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
@@ -5114,8 +4832,9 @@
       </c>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="24" t="n"/>
-      <c r="M29" s="23" t="n"/>
-      <c r="N29" s="24" t="n"/>
+      <c r="M29" s="20" t="n"/>
+      <c r="N29" s="23" t="n"/>
+      <c r="O29" s="24" t="n"/>
     </row>
     <row r="30" outlineLevel="2" ht="22" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
@@ -5147,8 +4866,9 @@
       </c>
       <c r="K30" s="23" t="n"/>
       <c r="L30" s="24" t="n"/>
-      <c r="M30" s="23" t="n"/>
-      <c r="N30" s="24" t="n"/>
+      <c r="M30" s="20" t="n"/>
+      <c r="N30" s="23" t="n"/>
+      <c r="O30" s="24" t="n"/>
     </row>
     <row r="31" outlineLevel="1" ht="22" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
@@ -5195,8 +4915,12 @@
       </c>
       <c r="K31" s="6" t="n"/>
       <c r="L31" s="10" t="n"/>
-      <c r="M31" s="6" t="n"/>
-      <c r="N31" s="10" t="n"/>
+      <c r="M31" s="18">
+        <f>SUM(M32,M33,M34,M35,M36)</f>
+        <v/>
+      </c>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="10" t="n"/>
     </row>
     <row r="32" outlineLevel="2" ht="22" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
@@ -5228,8 +4952,9 @@
       </c>
       <c r="K32" s="23" t="n"/>
       <c r="L32" s="24" t="n"/>
-      <c r="M32" s="23" t="n"/>
-      <c r="N32" s="24" t="n"/>
+      <c r="M32" s="20" t="n"/>
+      <c r="N32" s="23" t="n"/>
+      <c r="O32" s="24" t="n"/>
     </row>
     <row r="33" outlineLevel="2" ht="22" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
@@ -5261,8 +4986,9 @@
       </c>
       <c r="K33" s="23" t="n"/>
       <c r="L33" s="24" t="n"/>
-      <c r="M33" s="23" t="n"/>
-      <c r="N33" s="24" t="n"/>
+      <c r="M33" s="20" t="n"/>
+      <c r="N33" s="23" t="n"/>
+      <c r="O33" s="24" t="n"/>
     </row>
     <row r="34" outlineLevel="2" ht="22" customHeight="1">
       <c r="A34" s="13" t="inlineStr">
@@ -5294,8 +5020,9 @@
       </c>
       <c r="K34" s="23" t="n"/>
       <c r="L34" s="24" t="n"/>
-      <c r="M34" s="23" t="n"/>
-      <c r="N34" s="24" t="n"/>
+      <c r="M34" s="20" t="n"/>
+      <c r="N34" s="23" t="n"/>
+      <c r="O34" s="24" t="n"/>
     </row>
     <row r="35" outlineLevel="2" ht="22" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
@@ -5327,8 +5054,9 @@
       </c>
       <c r="K35" s="23" t="n"/>
       <c r="L35" s="24" t="n"/>
-      <c r="M35" s="23" t="n"/>
-      <c r="N35" s="24" t="n"/>
+      <c r="M35" s="20" t="n"/>
+      <c r="N35" s="23" t="n"/>
+      <c r="O35" s="24" t="n"/>
     </row>
     <row r="36" outlineLevel="2" ht="22" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
@@ -5360,8 +5088,9 @@
       </c>
       <c r="K36" s="23" t="n"/>
       <c r="L36" s="24" t="n"/>
-      <c r="M36" s="23" t="n"/>
-      <c r="N36" s="24" t="n"/>
+      <c r="M36" s="20" t="n"/>
+      <c r="N36" s="23" t="n"/>
+      <c r="O36" s="24" t="n"/>
     </row>
     <row r="37" outlineLevel="1" ht="22" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
@@ -5393,8 +5122,9 @@
       </c>
       <c r="K37" s="23" t="n"/>
       <c r="L37" s="24" t="n"/>
-      <c r="M37" s="23" t="n"/>
-      <c r="N37" s="24" t="n"/>
+      <c r="M37" s="20" t="n"/>
+      <c r="N37" s="23" t="n"/>
+      <c r="O37" s="24" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
@@ -5441,8 +5171,12 @@
       </c>
       <c r="K38" s="6" t="n"/>
       <c r="L38" s="10" t="n"/>
-      <c r="M38" s="6" t="n"/>
-      <c r="N38" s="10" t="n"/>
+      <c r="M38" s="18">
+        <f>SUM(M39,M40,M41)</f>
+        <v/>
+      </c>
+      <c r="N38" s="6" t="n"/>
+      <c r="O38" s="10" t="n"/>
     </row>
     <row r="39" outlineLevel="1" ht="22" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
@@ -5474,8 +5208,9 @@
       </c>
       <c r="K39" s="23" t="n"/>
       <c r="L39" s="24" t="n"/>
-      <c r="M39" s="23" t="n"/>
-      <c r="N39" s="24" t="n"/>
+      <c r="M39" s="20" t="n"/>
+      <c r="N39" s="23" t="n"/>
+      <c r="O39" s="24" t="n"/>
     </row>
     <row r="40" outlineLevel="1" ht="22" customHeight="1">
       <c r="A40" s="13" t="inlineStr">
@@ -5507,8 +5242,9 @@
       </c>
       <c r="K40" s="23" t="n"/>
       <c r="L40" s="24" t="n"/>
-      <c r="M40" s="23" t="n"/>
-      <c r="N40" s="24" t="n"/>
+      <c r="M40" s="20" t="n"/>
+      <c r="N40" s="23" t="n"/>
+      <c r="O40" s="24" t="n"/>
     </row>
     <row r="41" outlineLevel="1" ht="22" customHeight="1">
       <c r="A41" s="13" t="inlineStr">
@@ -5540,8 +5276,9 @@
       </c>
       <c r="K41" s="23" t="n"/>
       <c r="L41" s="24" t="n"/>
-      <c r="M41" s="23" t="n"/>
-      <c r="N41" s="24" t="n"/>
+      <c r="M41" s="20" t="n"/>
+      <c r="N41" s="23" t="n"/>
+      <c r="O41" s="24" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
@@ -5588,8 +5325,12 @@
       </c>
       <c r="K42" s="6" t="n"/>
       <c r="L42" s="10" t="n"/>
-      <c r="M42" s="6" t="n"/>
-      <c r="N42" s="10" t="n"/>
+      <c r="M42" s="18">
+        <f>SUM(M43,M44,M45)</f>
+        <v/>
+      </c>
+      <c r="N42" s="6" t="n"/>
+      <c r="O42" s="10" t="n"/>
     </row>
     <row r="43" outlineLevel="1" ht="22" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
@@ -5621,8 +5362,9 @@
       </c>
       <c r="K43" s="23" t="n"/>
       <c r="L43" s="24" t="n"/>
-      <c r="M43" s="23" t="n"/>
-      <c r="N43" s="24" t="n"/>
+      <c r="M43" s="20" t="n"/>
+      <c r="N43" s="23" t="n"/>
+      <c r="O43" s="24" t="n"/>
     </row>
     <row r="44" outlineLevel="1" ht="22" customHeight="1">
       <c r="A44" s="13" t="inlineStr">
@@ -5654,8 +5396,9 @@
       </c>
       <c r="K44" s="23" t="n"/>
       <c r="L44" s="24" t="n"/>
-      <c r="M44" s="23" t="n"/>
-      <c r="N44" s="24" t="n"/>
+      <c r="M44" s="20" t="n"/>
+      <c r="N44" s="23" t="n"/>
+      <c r="O44" s="24" t="n"/>
     </row>
     <row r="45" outlineLevel="1" ht="22" customHeight="1">
       <c r="A45" s="13" t="inlineStr">
@@ -5687,8 +5430,9 @@
       </c>
       <c r="K45" s="23" t="n"/>
       <c r="L45" s="24" t="n"/>
-      <c r="M45" s="23" t="n"/>
-      <c r="N45" s="24" t="n"/>
+      <c r="M45" s="20" t="n"/>
+      <c r="N45" s="23" t="n"/>
+      <c r="O45" s="24" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
@@ -5702,11 +5446,11 @@
         </is>
       </c>
       <c r="C46" s="18">
-        <f>SUM(C47,C48,C49,C50)</f>
+        <f>SUM(C47,C48,C49)</f>
         <v/>
       </c>
       <c r="D46" s="18">
-        <f>SUM(D47,D48,D49,D50)</f>
+        <f>SUM(D47,D48,D49)</f>
         <v/>
       </c>
       <c r="E46" s="18">
@@ -5718,15 +5462,15 @@
         <v/>
       </c>
       <c r="G46" s="18">
-        <f>SUM(G47,G48,G49,G50)</f>
+        <f>SUM(G47,G48,G49)</f>
         <v/>
       </c>
       <c r="H46" s="18">
-        <f>SUM(H47,H48,H49,H50)</f>
+        <f>SUM(H47,H48,H49)</f>
         <v/>
       </c>
       <c r="I46" s="18">
-        <f>SUM(I47,I48,I49,I50)</f>
+        <f>SUM(I47,I48,I49)</f>
         <v/>
       </c>
       <c r="J46" s="18">
@@ -5735,8 +5479,12 @@
       </c>
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="10" t="n"/>
-      <c r="M46" s="6" t="n"/>
-      <c r="N46" s="10" t="n"/>
+      <c r="M46" s="18">
+        <f>SUM(M47,M48,M49)</f>
+        <v/>
+      </c>
+      <c r="N46" s="6" t="n"/>
+      <c r="O46" s="10" t="n"/>
     </row>
     <row r="47" outlineLevel="1" ht="22" customHeight="1">
       <c r="A47" s="13" t="inlineStr">
@@ -5746,7 +5494,7 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Проценты на инвестиционной фазе</t>
+          <t>Страхование</t>
         </is>
       </c>
       <c r="C47" s="20" t="n"/>
@@ -5768,8 +5516,9 @@
       </c>
       <c r="K47" s="23" t="n"/>
       <c r="L47" s="24" t="n"/>
-      <c r="M47" s="23" t="n"/>
-      <c r="N47" s="24" t="n"/>
+      <c r="M47" s="20" t="n"/>
+      <c r="N47" s="23" t="n"/>
+      <c r="O47" s="24" t="n"/>
     </row>
     <row r="48" outlineLevel="1" ht="22" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
@@ -5779,7 +5528,7 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Страхование</t>
+          <t>Резерв непредвиденных расходов</t>
         </is>
       </c>
       <c r="C48" s="20" t="n"/>
@@ -5801,8 +5550,9 @@
       </c>
       <c r="K48" s="23" t="n"/>
       <c r="L48" s="24" t="n"/>
-      <c r="M48" s="23" t="n"/>
-      <c r="N48" s="24" t="n"/>
+      <c r="M48" s="20" t="n"/>
+      <c r="N48" s="23" t="n"/>
+      <c r="O48" s="24" t="n"/>
     </row>
     <row r="49" outlineLevel="1" ht="22" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
@@ -5812,7 +5562,7 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Резерв непредвиденных расходов</t>
+          <t>Комиссии, гарантии, обязательные платежи и консультации</t>
         </is>
       </c>
       <c r="C49" s="20" t="n"/>
@@ -5834,101 +5584,73 @@
       </c>
       <c r="K49" s="23" t="n"/>
       <c r="L49" s="24" t="n"/>
-      <c r="M49" s="23" t="n"/>
-      <c r="N49" s="24" t="n"/>
-    </row>
-    <row r="50" outlineLevel="1" ht="22" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>06.04</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>Комиссии, гарантии, обязательные платежи и консультации</t>
-        </is>
-      </c>
-      <c r="C50" s="20" t="n"/>
-      <c r="D50" s="20" t="n"/>
-      <c r="E50" s="21">
-        <f>D50-C50</f>
-        <v/>
-      </c>
-      <c r="F50" s="22">
-        <f>IF(AND(C50=0,D50=0),"—",IF(C50=0,"новая статья",E50/C50))</f>
-        <v/>
-      </c>
-      <c r="G50" s="20" t="n"/>
-      <c r="H50" s="20" t="n"/>
-      <c r="I50" s="20" t="n"/>
-      <c r="J50" s="21">
-        <f>G50+H50+I50-E50</f>
-        <v/>
-      </c>
-      <c r="K50" s="23" t="n"/>
-      <c r="L50" s="24" t="n"/>
-      <c r="M50" s="23" t="n"/>
-      <c r="N50" s="24" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="M49" s="20" t="n"/>
+      <c r="N49" s="23" t="n"/>
+      <c r="O49" s="24" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B51" s="25" t="inlineStr">
+      <c r="B50" s="25" t="inlineStr">
         <is>
           <t>Итого, сопоставимый периметр</t>
         </is>
       </c>
-      <c r="C51" s="26">
+      <c r="C50" s="26">
         <f>SUM(C5,C10,C16,C38,C42,C46)</f>
         <v/>
       </c>
-      <c r="D51" s="26">
+      <c r="D50" s="26">
         <f>SUM(D5,D10,D16,D38,D42,D46)</f>
         <v/>
       </c>
-      <c r="E51" s="26">
+      <c r="E50" s="26">
         <f>SUM(E5,E10,E16,E38,E42,E46)</f>
         <v/>
       </c>
-      <c r="F51" s="27">
-        <f>IF(C51=0,"—",E51/C51)</f>
-        <v/>
-      </c>
-      <c r="G51" s="26">
+      <c r="F50" s="27">
+        <f>IF(C50=0,"—",E50/C50)</f>
+        <v/>
+      </c>
+      <c r="G50" s="26">
         <f>SUM(G5,G10,G16,G38,G42,G46)</f>
         <v/>
       </c>
-      <c r="H51" s="26">
+      <c r="H50" s="26">
         <f>SUM(H5,H10,H16,H38,H42,H46)</f>
         <v/>
       </c>
-      <c r="I51" s="26">
+      <c r="I50" s="26">
         <f>SUM(I5,I10,I16,I38,I42,I46)</f>
         <v/>
       </c>
-      <c r="J51" s="26">
+      <c r="J50" s="26">
         <f>SUM(J5,J10,J16,J38,J42,J46)</f>
         <v/>
       </c>
-      <c r="K51" s="25" t="inlineStr">
-        <is>
-          <t>F1 + F2 + F3 = отклонение.</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="25" t="n"/>
-      <c r="N51" s="5" t="n"/>
+      <c r="K50" s="25" t="inlineStr">
+        <is>
+          <t>F1 + F2 + F3 = отклонение. Сумма риска в это тождество не входит.</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="26">
+        <f>SUM(M5,M10,M16,M38,M42,M46)</f>
+        <v/>
+      </c>
+      <c r="N50" s="25" t="n"/>
+      <c r="O50" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N51"/>
+  <autoFilter ref="A4:O50"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J51">
+  <conditionalFormatting sqref="J5:J50">
     <cfRule type="cellIs" priority="1" operator="between" dxfId="0">
       <formula>-1</formula>
       <formula>1</formula>
@@ -5938,7 +5660,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L51">
+  <conditionalFormatting sqref="L5:L50">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>L5="Высокий"</formula>
     </cfRule>
@@ -5950,10 +5672,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Низкий,Средний,Высокий"</formula1>
     </dataValidation>
-    <dataValidation sqref="N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"А,Б,В"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5977,7 +5699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5992,8 +5714,9 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="72" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -6006,7 +5729,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Единица измерения — рубль без НДС. Желтым отмечен ввод. Отклонение, процент, агрегаты и колонка «Контроль» считаются формулами. Контроль = инфляция + изменения ПСД + иные причины − отклонение и должен быть равен нулю. Цифры примера условные и показывают рост сопоставимого бюджета на 15%.</t>
+          <t>Единица измерения — рубль без НДС. Желтым отмечен ввод. Отклонение, процент, агрегаты и колонка «Контроль» считаются формулами. Контроль = инфляция + изменения ПСД + иные причины − отклонение и должен быть равен нулю. Сумма риска — оценка возможного нового удорожания сверх откорректированного бюджета. В контроль факторов она не входит. Цифры примера условные. Проценты по кредиту в бюджет не включены.</t>
         </is>
       </c>
     </row>
@@ -6073,10 +5796,15 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
+          <t>Сумма риска, руб.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
           <t>Комментарий к риску</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Класс надежности</t>
         </is>
@@ -6135,12 +5863,16 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="18">
+        <f>SUM(M6,M7,M8,M9)</f>
+        <v/>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>Оценка агрегата — наихудшая существенная вложенная строка.</t>
         </is>
       </c>
-      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
     </row>
     <row r="6" outlineLevel="1" ht="48" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
@@ -6190,12 +5922,15 @@
           <t>Низкий</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t>Градостроительная подготовка завершена, открытых предписаний нет.</t>
         </is>
       </c>
-      <c r="N6" s="24" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -6249,12 +5984,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="M7" s="20" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t>Часть переносов не законтрактована. Возможен новый объем по требованиям смежных собственников.</t>
         </is>
       </c>
-      <c r="N7" s="24" t="inlineStr">
+      <c r="O7" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -6308,12 +6046,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M8" s="23" t="inlineStr">
+      <c r="M8" s="20" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t>Котлован выполнен частично. Остается риск водопритока и зимнего удорожания незакрытого остатка.</t>
         </is>
       </c>
-      <c r="N8" s="24" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -6367,12 +6108,15 @@
           <t>Низкий</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t>Затраты в основном уже понесены.</t>
         </is>
       </c>
-      <c r="N9" s="24" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -6431,12 +6175,16 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="18">
+        <f>SUM(M11,M12,M13,M14,M15)</f>
+        <v/>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>Оценка агрегата — наихудшая существенная вложенная строка.</t>
         </is>
       </c>
-      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
     </row>
     <row r="11" outlineLevel="1" ht="48" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
@@ -6486,12 +6234,15 @@
           <t>Низкий</t>
         </is>
       </c>
-      <c r="M11" s="23" t="inlineStr">
+      <c r="M11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t>Полевые работы закрыты актами.</t>
         </is>
       </c>
-      <c r="N11" s="24" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -6545,12 +6296,15 @@
           <t>Низкий</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="M12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="23" t="inlineStr">
         <is>
           <t>Экспертиза стадии П пройдена.</t>
         </is>
       </c>
-      <c r="N12" s="24" t="inlineStr">
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -6604,12 +6358,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr">
+      <c r="M13" s="20" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t>Комплект рабочей документации не завершен. До окончания СМР вероятны дополнительные измы.</t>
         </is>
       </c>
-      <c r="N13" s="24" t="inlineStr">
+      <c r="O13" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -6663,12 +6420,15 @@
           <t>Низкий</t>
         </is>
       </c>
-      <c r="M14" s="23" t="inlineStr">
+      <c r="M14" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t>Повторное заключение получено.</t>
         </is>
       </c>
-      <c r="N14" s="24" t="inlineStr">
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -6722,12 +6482,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M15" s="23" t="inlineStr">
+      <c r="M15" s="20" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="N15" s="23" t="inlineStr">
         <is>
           <t>При следующем сдвиге ввода вероятно дополнительное соглашение. В бюджете T1 его еще нет.</t>
         </is>
       </c>
-      <c r="N15" s="24" t="inlineStr">
+      <c r="O15" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -6786,12 +6549,16 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M16" s="18">
+        <f>SUM(M17,M25,M31,M37)</f>
+        <v/>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
         <is>
           <t>Оценка агрегата — наихудшая существенная вложенная строка.</t>
         </is>
       </c>
-      <c r="N16" s="10" t="n"/>
+      <c r="O16" s="10" t="n"/>
     </row>
     <row r="17" outlineLevel="1" ht="48" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -6846,12 +6613,16 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M17" s="18">
+        <f>SUM(M18,M19,M20,M21,M22,M23,M24)</f>
+        <v/>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
         <is>
           <t>Оценка агрегата — наихудшая существенная вложенная строка.</t>
         </is>
       </c>
-      <c r="N17" s="10" t="n"/>
+      <c r="O17" s="10" t="n"/>
     </row>
     <row r="18" outlineLevel="2" ht="48" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -6901,12 +6672,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M18" s="23" t="inlineStr">
+      <c r="M18" s="20" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="N18" s="23" t="inlineStr">
         <is>
           <t>Подземная часть законтрактована по единичным расценкам примерно на 70%. Остаток зависит от исполнительной геологии.</t>
         </is>
       </c>
-      <c r="N18" s="24" t="inlineStr">
+      <c r="O18" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -6960,12 +6734,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M19" s="23" t="inlineStr">
+      <c r="M19" s="20" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="N19" s="23" t="inlineStr">
         <is>
           <t>Расценки зафиксированы до текущей отметки. Верхние этажи еще открыты.</t>
         </is>
       </c>
-      <c r="N19" s="24" t="inlineStr">
+      <c r="O19" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -7019,12 +6796,15 @@
           <t>Низкий</t>
         </is>
       </c>
-      <c r="M20" s="23" t="inlineStr">
+      <c r="M20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="23" t="inlineStr">
         <is>
           <t>Решения типовые, расценки законтрактованы.</t>
         </is>
       </c>
-      <c r="N20" s="24" t="inlineStr">
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -7078,12 +6858,15 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M21" s="23" t="inlineStr">
+      <c r="M21" s="20" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="N21" s="23" t="inlineStr">
         <is>
           <t>Фасадный договор не подписан, узлы рабочей документации не утверждены, валютная составляющая фурнитуры открыта.</t>
         </is>
       </c>
-      <c r="N21" s="24" t="inlineStr">
+      <c r="O21" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -7137,12 +6920,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M22" s="23" t="inlineStr">
+      <c r="M22" s="20" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="N22" s="23" t="inlineStr">
         <is>
           <t>Спецификация согласована не полностью. Металл и стекло верхних этажей не закуплены.</t>
         </is>
       </c>
-      <c r="N22" s="24" t="inlineStr">
+      <c r="O22" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -7196,12 +6982,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M23" s="23" t="inlineStr">
+      <c r="M23" s="20" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="N23" s="23" t="inlineStr">
         <is>
           <t>Отделка не законтрактована, объемы зависят от финальной рабочей документации.</t>
         </is>
       </c>
-      <c r="N23" s="24" t="inlineStr">
+      <c r="O23" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -7255,12 +7044,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M24" s="23" t="inlineStr">
+      <c r="M24" s="20" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="N24" s="23" t="inlineStr">
         <is>
           <t>Договор поставки не заключен. Срок изготовления лежит на критическом пути ввода.</t>
         </is>
       </c>
-      <c r="N24" s="24" t="inlineStr">
+      <c r="O24" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -7319,12 +7111,16 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr">
+      <c r="M25" s="18">
+        <f>SUM(M26,M27,M28,M29,M30)</f>
+        <v/>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
         <is>
           <t>Оценка агрегата — наихудшая существенная вложенная строка.</t>
         </is>
       </c>
-      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n"/>
     </row>
     <row r="26" outlineLevel="2" ht="48" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
@@ -7374,12 +7170,15 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M26" s="23" t="inlineStr">
+      <c r="M26" s="20" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="N26" s="23" t="inlineStr">
         <is>
           <t>Рабочая документация выпущена частично. Основное оборудование не законтрактовано.</t>
         </is>
       </c>
-      <c r="N26" s="24" t="inlineStr">
+      <c r="O26" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -7433,12 +7232,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M27" s="23" t="inlineStr">
+      <c r="M27" s="20" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="N27" s="23" t="inlineStr">
         <is>
           <t>Система в основном типовая, но спецификация приборов не закрыта полностью.</t>
         </is>
       </c>
-      <c r="N27" s="24" t="inlineStr">
+      <c r="O27" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -7492,12 +7294,15 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M28" s="23" t="inlineStr">
+      <c r="M28" s="20" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="N28" s="23" t="inlineStr">
         <is>
           <t>Нагрузка не подтверждена окончательными техническими условиями. Спецификация щитов открыта.</t>
         </is>
       </c>
-      <c r="N28" s="24" t="inlineStr">
+      <c r="O28" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -7551,12 +7356,15 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M29" s="23" t="inlineStr">
+      <c r="M29" s="20" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="N29" s="23" t="inlineStr">
         <is>
           <t>Задание на слаботочные системы пересматривается. Договоры не заключены.</t>
         </is>
       </c>
-      <c r="N29" s="24" t="inlineStr">
+      <c r="O29" s="24" t="inlineStr">
         <is>
           <t>В</t>
         </is>
@@ -7610,12 +7418,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M30" s="23" t="inlineStr">
+      <c r="M30" s="20" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="N30" s="23" t="inlineStr">
         <is>
           <t>Состав зависит от финальной редакции пожарного раздела.</t>
         </is>
       </c>
-      <c r="N30" s="24" t="inlineStr">
+      <c r="O30" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -7674,12 +7485,16 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="M31" s="18">
+        <f>SUM(M32,M33,M34,M35,M36)</f>
+        <v/>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
         <is>
           <t>Оценка агрегата — наихудшая существенная вложенная строка.</t>
         </is>
       </c>
-      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
     </row>
     <row r="32" outlineLevel="2" ht="48" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
@@ -7729,12 +7544,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M32" s="23" t="inlineStr">
+      <c r="M32" s="20" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="N32" s="23" t="inlineStr">
         <is>
           <t>Часть трасс не согласована с балансодержателями.</t>
         </is>
       </c>
-      <c r="N32" s="24" t="inlineStr">
+      <c r="O32" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -7788,12 +7606,15 @@
           <t>Низкий</t>
         </is>
       </c>
-      <c r="M33" s="23" t="inlineStr">
+      <c r="M33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="23" t="inlineStr">
         <is>
           <t>Технические условия получены, трасса согласована.</t>
         </is>
       </c>
-      <c r="N33" s="24" t="inlineStr">
+      <c r="O33" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -7847,12 +7668,15 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M34" s="23" t="inlineStr">
+      <c r="M34" s="20" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="N34" s="23" t="inlineStr">
         <is>
           <t>Договор технологического присоединения в редакции T1 не подписан. Тариф и трасса могут измениться до оплаты.</t>
         </is>
       </c>
-      <c r="N34" s="24" t="inlineStr">
+      <c r="O34" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -7906,12 +7730,15 @@
           <t>Низкий</t>
         </is>
       </c>
-      <c r="M35" s="23" t="inlineStr">
+      <c r="M35" s="20" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="N35" s="23" t="inlineStr">
         <is>
           <t>Объем небольшой и технически определен.</t>
         </is>
       </c>
-      <c r="N35" s="24" t="inlineStr">
+      <c r="O35" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -7965,12 +7792,15 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M36" s="23" t="inlineStr">
+      <c r="M36" s="20" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="N36" s="23" t="inlineStr">
         <is>
           <t>Проект благоустройства не заморожен. Работы стоят в конце графика и зависят от сезона.</t>
         </is>
       </c>
-      <c r="N36" s="24" t="inlineStr">
+      <c r="O36" s="24" t="inlineStr">
         <is>
           <t>В</t>
         </is>
@@ -8024,12 +7854,15 @@
           <t>Низкий</t>
         </is>
       </c>
-      <c r="M37" s="23" t="inlineStr">
+      <c r="M37" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="23" t="inlineStr">
         <is>
           <t>Строка не используется. При появлении технологии риск оценивается отдельно.</t>
         </is>
       </c>
-      <c r="N37" s="24" t="inlineStr">
+      <c r="O37" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -8088,12 +7921,16 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M38" s="6" t="inlineStr">
+      <c r="M38" s="18">
+        <f>SUM(M39,M40,M41)</f>
+        <v/>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
         <is>
           <t>Оценка агрегата — наихудшая существенная вложенная строка.</t>
         </is>
       </c>
-      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
     </row>
     <row r="39" outlineLevel="1" ht="48" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
@@ -8143,12 +7980,15 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M39" s="23" t="inlineStr">
+      <c r="M39" s="20" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="N39" s="23" t="inlineStr">
         <is>
           <t>Срок ввода в модели T1 уже сдвинут. Следующий сдвиг увеличивает помесячные затраты почти линейно. Резерв на этот сдвиг в строке не заложен.</t>
         </is>
       </c>
-      <c r="N39" s="24" t="inlineStr">
+      <c r="O39" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -8202,12 +8042,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M40" s="23" t="inlineStr">
+      <c r="M40" s="20" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="N40" s="23" t="inlineStr">
         <is>
           <t>Ставка процента зафиксирована. Возмещаемая часть при пролонгации остается открытой.</t>
         </is>
       </c>
-      <c r="N40" s="24" t="inlineStr">
+      <c r="O40" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -8261,12 +8104,15 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M41" s="23" t="inlineStr">
+      <c r="M41" s="20" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="N41" s="23" t="inlineStr">
         <is>
           <t>Затраты длятся до фактического ввода, а не до плановой даты T1.</t>
         </is>
       </c>
-      <c r="N41" s="24" t="inlineStr">
+      <c r="O41" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -8325,12 +8171,16 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M42" s="6" t="inlineStr">
+      <c r="M42" s="18">
+        <f>SUM(M43,M44,M45)</f>
+        <v/>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
         <is>
           <t>Оценка агрегата — наихудшая существенная вложенная строка.</t>
         </is>
       </c>
-      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="10" t="n"/>
     </row>
     <row r="43" outlineLevel="1" ht="48" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
@@ -8380,12 +8230,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M43" s="23" t="inlineStr">
+      <c r="M43" s="20" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="N43" s="23" t="inlineStr">
         <is>
           <t>Бюджет привязан к темпу продаж. Строительный дефлятор к этой строке не применяется.</t>
         </is>
       </c>
-      <c r="N43" s="24" t="inlineStr">
+      <c r="O43" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -8439,12 +8292,15 @@
           <t>Низкий</t>
         </is>
       </c>
-      <c r="M44" s="23" t="inlineStr">
+      <c r="M44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="23" t="inlineStr">
         <is>
           <t>Объект показа завершен.</t>
         </is>
       </c>
-      <c r="N44" s="24" t="inlineStr">
+      <c r="O44" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -8498,12 +8354,15 @@
           <t>Средний</t>
         </is>
       </c>
-      <c r="M45" s="23" t="inlineStr">
+      <c r="M45" s="20" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="N45" s="23" t="inlineStr">
         <is>
           <t>Комиссия платится с фактических регистраций до выбора остатка.</t>
         </is>
       </c>
-      <c r="N45" s="24" t="inlineStr">
+      <c r="O45" s="24" t="inlineStr">
         <is>
           <t>А</t>
         </is>
@@ -8521,11 +8380,11 @@
         </is>
       </c>
       <c r="C46" s="18">
-        <f>SUM(C47,C48,C49,C50)</f>
+        <f>SUM(C47,C48,C49)</f>
         <v/>
       </c>
       <c r="D46" s="18">
-        <f>SUM(D47,D48,D49,D50)</f>
+        <f>SUM(D47,D48,D49)</f>
         <v/>
       </c>
       <c r="E46" s="18">
@@ -8537,15 +8396,15 @@
         <v/>
       </c>
       <c r="G46" s="18">
-        <f>SUM(G47,G48,G49,G50)</f>
+        <f>SUM(G47,G48,G49)</f>
         <v/>
       </c>
       <c r="H46" s="18">
-        <f>SUM(H47,H48,H49,H50)</f>
+        <f>SUM(H47,H48,H49)</f>
         <v/>
       </c>
       <c r="I46" s="18">
-        <f>SUM(I47,I48,I49,I50)</f>
+        <f>SUM(I47,I48,I49)</f>
         <v/>
       </c>
       <c r="J46" s="18">
@@ -8562,12 +8421,16 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M46" s="6" t="inlineStr">
+      <c r="M46" s="18">
+        <f>SUM(M47,M48,M49)</f>
+        <v/>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
         <is>
           <t>Оценка агрегата — наихудшая существенная вложенная строка.</t>
         </is>
       </c>
-      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
     </row>
     <row r="47" outlineLevel="1" ht="48" customHeight="1">
       <c r="A47" s="13" t="inlineStr">
@@ -8577,14 +8440,14 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Проценты на инвестиционной фазе</t>
+          <t>Страхование</t>
         </is>
       </c>
       <c r="C47" s="20" t="n">
-        <v>980000000</v>
+        <v>70000000</v>
       </c>
       <c r="D47" s="20" t="n">
-        <v>1025000000</v>
+        <v>78000000</v>
       </c>
       <c r="E47" s="21">
         <f>D47-C47</f>
@@ -8595,13 +8458,13 @@
         <v/>
       </c>
       <c r="G47" s="20" t="n">
-        <v>15000000</v>
+        <v>3000000</v>
       </c>
       <c r="H47" s="20" t="n">
-        <v>12000000</v>
+        <v>2000000</v>
       </c>
       <c r="I47" s="20" t="n">
-        <v>18000000</v>
+        <v>3000000</v>
       </c>
       <c r="J47" s="21">
         <f>G47+H47+I47-E47</f>
@@ -8609,20 +8472,23 @@
       </c>
       <c r="K47" s="23" t="inlineStr">
         <is>
-          <t>Результат сценарного пересчета кредитной модели, а не процент от СМР. F1 — проценты на дополнительное тело долга из-за инфляции исходного объема. F2 — проценты на тело, вызванное изменениями ПСД. F3 — удлинение срока выборки и пересмотр ставки.</t>
+          <t>Страховая сумма выросла вместе с инфляционной и проектной частями стоимости по исходному тарифу. Удлинение полиса и расширение покрытия отнесены к иным причинам.</t>
         </is>
       </c>
       <c r="L47" s="24" t="inlineStr">
         <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="M47" s="23" t="inlineStr">
-        <is>
-          <t>Остаток долга не зафиксирован по ставке. Следующий сдвиг ввода увеличит строку сверх бюджета T1.</t>
-        </is>
-      </c>
-      <c r="N47" s="24" t="inlineStr">
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="M47" s="20" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="N47" s="23" t="inlineStr">
+        <is>
+          <t>При следующем сдвиге срока полис почти наверняка продлевается.</t>
+        </is>
+      </c>
+      <c r="O47" s="24" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
@@ -8636,14 +8502,14 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Страхование</t>
+          <t>Резерв непредвиденных расходов</t>
         </is>
       </c>
       <c r="C48" s="20" t="n">
-        <v>70000000</v>
+        <v>350000000</v>
       </c>
       <c r="D48" s="20" t="n">
-        <v>78000000</v>
+        <v>340000000</v>
       </c>
       <c r="E48" s="21">
         <f>D48-C48</f>
@@ -8654,13 +8520,13 @@
         <v/>
       </c>
       <c r="G48" s="20" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="H48" s="20" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="I48" s="20" t="n">
-        <v>3000000</v>
+        <v>-10000000</v>
       </c>
       <c r="J48" s="21">
         <f>G48+H48+I48-E48</f>
@@ -8668,22 +8534,25 @@
       </c>
       <c r="K48" s="23" t="inlineStr">
         <is>
-          <t>Страховая сумма выросла вместе с инфляционной и проектной частями стоимости по исходному тарифу. Удлинение полиса и расширение покрытия отнесены к иным причинам.</t>
+          <t>Резерв не индексируется и не является изменением ПСД. Снижение на 10 млн руб. — использование резерва на отклонения, уже показанные в профильных статьях. Это источник финансирования, а не экономия инфляции. Повторно из профильных статей сумма не исключается.</t>
         </is>
       </c>
       <c r="L48" s="24" t="inlineStr">
         <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="M48" s="23" t="inlineStr">
-        <is>
-          <t>При следующем сдвиге срока полис почти наверняка продлевается.</t>
-        </is>
-      </c>
-      <c r="N48" s="24" t="inlineStr">
-        <is>
-          <t>Б</t>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="M48" s="20" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="N48" s="23" t="inlineStr">
+        <is>
+          <t>Остаток резерва ниже ожидаемой стоимости уже названных открытых пакетов: фасад и наружные сети.</t>
+        </is>
+      </c>
+      <c r="O48" s="24" t="inlineStr">
+        <is>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -8695,14 +8564,14 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Резерв непредвиденных расходов</t>
+          <t>Комиссии, гарантии, обязательные платежи и консультации</t>
         </is>
       </c>
       <c r="C49" s="20" t="n">
-        <v>350000000</v>
+        <v>100000000</v>
       </c>
       <c r="D49" s="20" t="n">
-        <v>340000000</v>
+        <v>117000000</v>
       </c>
       <c r="E49" s="21">
         <f>D49-C49</f>
@@ -8713,13 +8582,13 @@
         <v/>
       </c>
       <c r="G49" s="20" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="H49" s="20" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="I49" s="20" t="n">
-        <v>-10000000</v>
+        <v>14000000</v>
       </c>
       <c r="J49" s="21">
         <f>G49+H49+I49-E49</f>
@@ -8727,151 +8596,218 @@
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
-          <t>Резерв не индексируется и не является изменением ПСД. Снижение на 10 млн руб. — использование резерва на отклонения, уже показанные в профильных статьях. Это источник финансирования, а не экономия инфляции. Повторно из профильных статей сумма не исключается.</t>
+          <t>Индекс комиссий и юридических услуг на исходный периметр. Дополнительные заключения в связи с повторной экспертизой. Пролонгация гарантий и обязательные платежи периода сверх исходного графика.</t>
         </is>
       </c>
       <c r="L49" s="24" t="inlineStr">
         <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="M49" s="20" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="N49" s="23" t="inlineStr">
+        <is>
+          <t>Платежи завязаны на срок гарантий и на дату ввода.</t>
+        </is>
+      </c>
+      <c r="O49" s="24" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>Итого, сопоставимый периметр</t>
+        </is>
+      </c>
+      <c r="C50" s="26">
+        <f>SUM(C5,C10,C16,C38,C42,C46)</f>
+        <v/>
+      </c>
+      <c r="D50" s="26">
+        <f>SUM(D5,D10,D16,D38,D42,D46)</f>
+        <v/>
+      </c>
+      <c r="E50" s="26">
+        <f>SUM(E5,E10,E16,E38,E42,E46)</f>
+        <v/>
+      </c>
+      <c r="F50" s="27">
+        <f>IF(C50=0,"—",E50/C50)</f>
+        <v/>
+      </c>
+      <c r="G50" s="26">
+        <f>SUM(G5,G10,G16,G38,G42,G46)</f>
+        <v/>
+      </c>
+      <c r="H50" s="26">
+        <f>SUM(H5,H10,H16,H38,H42,H46)</f>
+        <v/>
+      </c>
+      <c r="I50" s="26">
+        <f>SUM(I5,I10,I16,I38,I42,I46)</f>
+        <v/>
+      </c>
+      <c r="J50" s="26">
+        <f>SUM(J5,J10,J16,J38,J42,J46)</f>
+        <v/>
+      </c>
+      <c r="K50" s="25" t="inlineStr">
+        <is>
+          <t>F1 + F2 + F3 = отклонение. Сумма риска в это тождество не входит.</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="M49" s="23" t="inlineStr">
-        <is>
-          <t>Остаток резерва ниже ожидаемой стоимости уже названных открытых пакетов: фасад, сети, ставка кредита.</t>
-        </is>
-      </c>
-      <c r="N49" s="24" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" outlineLevel="1" ht="48" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>06.04</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>Комиссии, гарантии, обязательные платежи и консультации</t>
-        </is>
-      </c>
-      <c r="C50" s="20" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="D50" s="20" t="n">
-        <v>117000000</v>
-      </c>
-      <c r="E50" s="21">
-        <f>D50-C50</f>
-        <v/>
-      </c>
-      <c r="F50" s="22">
-        <f>IF(AND(C50=0,D50=0),"—",IF(C50=0,"новая статья",E50/C50))</f>
-        <v/>
-      </c>
-      <c r="G50" s="20" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="H50" s="20" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="I50" s="20" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="J50" s="21">
-        <f>G50+H50+I50-E50</f>
-        <v/>
-      </c>
-      <c r="K50" s="23" t="inlineStr">
-        <is>
-          <t>Индекс комиссий и юридических услуг на исходный периметр. Дополнительные заключения в связи с повторной экспертизой. Пролонгация гарантий и обязательные платежи периода сверх исходного графика.</t>
-        </is>
-      </c>
-      <c r="L50" s="24" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="M50" s="23" t="inlineStr">
-        <is>
-          <t>Платежи завязаны на срок кредита и на дату ввода.</t>
-        </is>
-      </c>
-      <c r="N50" s="24" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="inlineStr">
-        <is>
-          <t>Итого, сопоставимый периметр</t>
-        </is>
-      </c>
-      <c r="C51" s="26">
-        <f>SUM(C5,C10,C16,C38,C42,C46)</f>
-        <v/>
-      </c>
-      <c r="D51" s="26">
-        <f>SUM(D5,D10,D16,D38,D42,D46)</f>
-        <v/>
-      </c>
-      <c r="E51" s="26">
-        <f>SUM(E5,E10,E16,E38,E42,E46)</f>
-        <v/>
-      </c>
-      <c r="F51" s="27">
-        <f>IF(C51=0,"—",E51/C51)</f>
-        <v/>
-      </c>
-      <c r="G51" s="26">
-        <f>SUM(G5,G10,G16,G38,G42,G46)</f>
-        <v/>
-      </c>
-      <c r="H51" s="26">
-        <f>SUM(H5,H10,H16,H38,H42,H46)</f>
-        <v/>
-      </c>
-      <c r="I51" s="26">
-        <f>SUM(I5,I10,I16,I38,I42,I46)</f>
-        <v/>
-      </c>
-      <c r="J51" s="26">
-        <f>SUM(J5,J10,J16,J38,J42,J46)</f>
-        <v/>
-      </c>
-      <c r="K51" s="25" t="inlineStr">
-        <is>
-          <t>F1 + F2 + F3 = отклонение.</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="M51" s="25" t="inlineStr">
+      <c r="M50" s="26">
+        <f>SUM(M5,M10,M16,M38,M42,M46)</f>
+        <v/>
+      </c>
+      <c r="N50" s="25" t="inlineStr">
         <is>
           <t>Риск итога определяется открытыми строками с оценкой «Высокий».</t>
         </is>
       </c>
-      <c r="N51" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Упрощенный расчет суммы каждого фактора</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Сумма фактора 1 и сумма фактора 2 складываются по строкам. Сумма фактора 3 считается остатком: отклонение минус два первых фактора. Контроль обязан быть нулевым: остаток совпадает с суммой столбца иных причин.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Фактор</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Упрощенная формула</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Сумма, руб.</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Доля отклонения</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Фактор 1. Инфляция</t>
+        </is>
+      </c>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>Σ v0 × p0 × (Iex − 1) по конечным статьям</t>
+        </is>
+      </c>
+      <c r="C55" s="21">
+        <f>G50</f>
+        <v/>
+      </c>
+      <c r="D55" s="29">
+        <f>IF(E50=0,"—",C55/E50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Фактор 2. Изменения ПСД</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>Σ (v1 × pref − v0 × p0 × Iex) по конечным статьям</t>
+        </is>
+      </c>
+      <c r="C56" s="21">
+        <f>H50</f>
+        <v/>
+      </c>
+      <c r="D56" s="29">
+        <f>IF(E50=0,"—",C56/E50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Фактор 3. Иные причины</t>
+        </is>
+      </c>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>Отклонение − сумма фактора 1 − сумма фактора 2</t>
+        </is>
+      </c>
+      <c r="C57" s="21">
+        <f>E50-C55-C56</f>
+        <v/>
+      </c>
+      <c r="D57" s="29">
+        <f>IF(E50=0,"—",C57/E50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="30" t="inlineStr">
+        <is>
+          <t>Контроль упрощенной формулы</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>Сумма фактора 3 по строкам − упрощенная сумма фактора 3</t>
+        </is>
+      </c>
+      <c r="C58" s="32">
+        <f>I50-C57</f>
+        <v/>
+      </c>
+      <c r="D58" s="33" t="inlineStr">
+        <is>
+          <t>должно быть 0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N51"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+  <autoFilter ref="A4:O50"/>
+  <mergeCells count="4">
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J51">
+  <conditionalFormatting sqref="J5:J50">
     <cfRule type="cellIs" priority="1" operator="between" dxfId="0">
       <formula>-1</formula>
       <formula>1</formula>
@@ -8881,7 +8817,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L51">
+  <conditionalFormatting sqref="L5:L50">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>L5="Высокий"</formula>
     </cfRule>
@@ -8893,10 +8829,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Низкий,Средний,Высокий"</formula1>
     </dataValidation>
-    <dataValidation sqref="N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"А,Б,В"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8920,6 +8856,1033 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Укрупненный факторный анализ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Отдельная таблица поверх постатейного анализа. Пять групп: СМР, ПИР, наружные сети и ТУ, коммерческие и административные затраты. Наружные сети вынесены из СМР. Проценты по кредиту не включены. Суммы — формулы со ссылкой на постатейные строки, без повторного ввода.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Условный пример</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Состав</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Базовый бюджет, руб.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Откорректированный бюджет, руб.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Отклонение, руб.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Отклонение, %</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Фактор 1. Инфляция, руб.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Фактор 2. Изменения ПСД, руб.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Фактор 3. Иные причины, руб.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Контроль, руб.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Что входит в группу</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Риск до ввода</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Сумма риска, руб.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Класс надежности</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>Подготовка площадки, общестроительные работы, внутренние системы и технологическое оборудование. Коды 01, 03.01, 03.02, 03.04.</t>
+        </is>
+      </c>
+      <c r="C6" s="35">
+        <f>SUM('Условный пример'!C5,'Условный пример'!C17,'Условный пример'!C25,'Условный пример'!C37)</f>
+        <v/>
+      </c>
+      <c r="D6" s="35">
+        <f>SUM('Условный пример'!D5,'Условный пример'!D17,'Условный пример'!D25,'Условный пример'!D37)</f>
+        <v/>
+      </c>
+      <c r="E6" s="35">
+        <f>D6-C6</f>
+        <v/>
+      </c>
+      <c r="F6" s="36">
+        <f>IF(C6=0,"—",E6/C6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="35">
+        <f>SUM('Условный пример'!G5,'Условный пример'!G17,'Условный пример'!G25,'Условный пример'!G37)</f>
+        <v/>
+      </c>
+      <c r="H6" s="35">
+        <f>SUM('Условный пример'!H5,'Условный пример'!H17,'Условный пример'!H25,'Условный пример'!H37)</f>
+        <v/>
+      </c>
+      <c r="I6" s="35">
+        <f>SUM('Условный пример'!I5,'Условный пример'!I17,'Условный пример'!I25,'Условный пример'!I37)</f>
+        <v/>
+      </c>
+      <c r="J6" s="35">
+        <f>G6+H6+I6-E6</f>
+        <v/>
+      </c>
+      <c r="K6" s="28" t="inlineStr">
+        <is>
+          <t>Подготовка площадки, общестроительные работы, внутренние системы и технологическое оборудование. Коды 01, 03.01, 03.02, 03.04.</t>
+        </is>
+      </c>
+      <c r="L6" s="37">
+        <f>IF(OR('Условный пример'!L5="Высокий",'Условный пример'!L17="Высокий",'Условный пример'!L25="Высокий",'Условный пример'!L37="Высокий"),"Высокий",IF(OR('Условный пример'!L5="Средний",'Условный пример'!L17="Средний",'Условный пример'!L25="Средний",'Условный пример'!L37="Средний"),"Средний",IF(COUNTA('Условный пример'!L5,'Условный пример'!L17,'Условный пример'!L25,'Условный пример'!L37)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M6" s="35">
+        <f>SUM('Условный пример'!M5,'Условный пример'!M17,'Условный пример'!M25,'Условный пример'!M37)</f>
+        <v/>
+      </c>
+      <c r="N6" s="28" t="inlineStr">
+        <is>
+          <t>Свертка постатейных строк. Сумма риска в тождество факторов не входит.</t>
+        </is>
+      </c>
+      <c r="O6" s="38" t="inlineStr">
+        <is>
+          <t>свертка</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>ПИР</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>Изыскания, проект, рабочая документация, экспертиза и авторский надзор. Код 02.</t>
+        </is>
+      </c>
+      <c r="C7" s="35">
+        <f>SUM('Условный пример'!C10)</f>
+        <v/>
+      </c>
+      <c r="D7" s="35">
+        <f>SUM('Условный пример'!D10)</f>
+        <v/>
+      </c>
+      <c r="E7" s="35">
+        <f>D7-C7</f>
+        <v/>
+      </c>
+      <c r="F7" s="36">
+        <f>IF(C7=0,"—",E7/C7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="35">
+        <f>SUM('Условный пример'!G10)</f>
+        <v/>
+      </c>
+      <c r="H7" s="35">
+        <f>SUM('Условный пример'!H10)</f>
+        <v/>
+      </c>
+      <c r="I7" s="35">
+        <f>SUM('Условный пример'!I10)</f>
+        <v/>
+      </c>
+      <c r="J7" s="35">
+        <f>G7+H7+I7-E7</f>
+        <v/>
+      </c>
+      <c r="K7" s="28" t="inlineStr">
+        <is>
+          <t>Изыскания, проект, рабочая документация, экспертиза и авторский надзор. Код 02.</t>
+        </is>
+      </c>
+      <c r="L7" s="37">
+        <f>IF(OR('Условный пример'!L10="Высокий"),"Высокий",IF(OR('Условный пример'!L10="Средний"),"Средний",IF(COUNTA('Условный пример'!L10)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M7" s="35">
+        <f>SUM('Условный пример'!M10)</f>
+        <v/>
+      </c>
+      <c r="N7" s="28" t="inlineStr">
+        <is>
+          <t>Свертка постатейных строк. Сумма риска в тождество факторов не входит.</t>
+        </is>
+      </c>
+      <c r="O7" s="38" t="inlineStr">
+        <is>
+          <t>свертка</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Наружные сети и ТУ</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>Наружные сети, технологическое присоединение и благоустройство. Код 03.03.</t>
+        </is>
+      </c>
+      <c r="C8" s="35">
+        <f>SUM('Условный пример'!C31)</f>
+        <v/>
+      </c>
+      <c r="D8" s="35">
+        <f>SUM('Условный пример'!D31)</f>
+        <v/>
+      </c>
+      <c r="E8" s="35">
+        <f>D8-C8</f>
+        <v/>
+      </c>
+      <c r="F8" s="36">
+        <f>IF(C8=0,"—",E8/C8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="35">
+        <f>SUM('Условный пример'!G31)</f>
+        <v/>
+      </c>
+      <c r="H8" s="35">
+        <f>SUM('Условный пример'!H31)</f>
+        <v/>
+      </c>
+      <c r="I8" s="35">
+        <f>SUM('Условный пример'!I31)</f>
+        <v/>
+      </c>
+      <c r="J8" s="35">
+        <f>G8+H8+I8-E8</f>
+        <v/>
+      </c>
+      <c r="K8" s="28" t="inlineStr">
+        <is>
+          <t>Наружные сети, технологическое присоединение и благоустройство. Код 03.03.</t>
+        </is>
+      </c>
+      <c r="L8" s="37">
+        <f>IF(OR('Условный пример'!L31="Высокий"),"Высокий",IF(OR('Условный пример'!L31="Средний"),"Средний",IF(COUNTA('Условный пример'!L31)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M8" s="35">
+        <f>SUM('Условный пример'!M31)</f>
+        <v/>
+      </c>
+      <c r="N8" s="28" t="inlineStr">
+        <is>
+          <t>Свертка постатейных строк. Сумма риска в тождество факторов не входит.</t>
+        </is>
+      </c>
+      <c r="O8" s="38" t="inlineStr">
+        <is>
+          <t>свертка</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Продвижение, офис продаж и брокерские комиссии. Код 05.</t>
+        </is>
+      </c>
+      <c r="C9" s="35">
+        <f>SUM('Условный пример'!C42)</f>
+        <v/>
+      </c>
+      <c r="D9" s="35">
+        <f>SUM('Условный пример'!D42)</f>
+        <v/>
+      </c>
+      <c r="E9" s="35">
+        <f>D9-C9</f>
+        <v/>
+      </c>
+      <c r="F9" s="36">
+        <f>IF(C9=0,"—",E9/C9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="35">
+        <f>SUM('Условный пример'!G42)</f>
+        <v/>
+      </c>
+      <c r="H9" s="35">
+        <f>SUM('Условный пример'!H42)</f>
+        <v/>
+      </c>
+      <c r="I9" s="35">
+        <f>SUM('Условный пример'!I42)</f>
+        <v/>
+      </c>
+      <c r="J9" s="35">
+        <f>G9+H9+I9-E9</f>
+        <v/>
+      </c>
+      <c r="K9" s="28" t="inlineStr">
+        <is>
+          <t>Продвижение, офис продаж и брокерские комиссии. Код 05.</t>
+        </is>
+      </c>
+      <c r="L9" s="37">
+        <f>IF(OR('Условный пример'!L42="Высокий"),"Высокий",IF(OR('Условный пример'!L42="Средний"),"Средний",IF(COUNTA('Условный пример'!L42)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M9" s="35">
+        <f>SUM('Условный пример'!M42)</f>
+        <v/>
+      </c>
+      <c r="N9" s="28" t="inlineStr">
+        <is>
+          <t>Свертка постатейных строк. Сумма риска в тождество факторов не входит.</t>
+        </is>
+      </c>
+      <c r="O9" s="38" t="inlineStr">
+        <is>
+          <t>свертка</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Административные</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Управление, страхование, резерв, гарантии и обязательные платежи. Коды 04 и 06. Проценты по кредиту не входят.</t>
+        </is>
+      </c>
+      <c r="C10" s="35">
+        <f>SUM('Условный пример'!C38,'Условный пример'!C46)</f>
+        <v/>
+      </c>
+      <c r="D10" s="35">
+        <f>SUM('Условный пример'!D38,'Условный пример'!D46)</f>
+        <v/>
+      </c>
+      <c r="E10" s="35">
+        <f>D10-C10</f>
+        <v/>
+      </c>
+      <c r="F10" s="36">
+        <f>IF(C10=0,"—",E10/C10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="35">
+        <f>SUM('Условный пример'!G38,'Условный пример'!G46)</f>
+        <v/>
+      </c>
+      <c r="H10" s="35">
+        <f>SUM('Условный пример'!H38,'Условный пример'!H46)</f>
+        <v/>
+      </c>
+      <c r="I10" s="35">
+        <f>SUM('Условный пример'!I38,'Условный пример'!I46)</f>
+        <v/>
+      </c>
+      <c r="J10" s="35">
+        <f>G10+H10+I10-E10</f>
+        <v/>
+      </c>
+      <c r="K10" s="28" t="inlineStr">
+        <is>
+          <t>Управление, страхование, резерв, гарантии и обязательные платежи. Коды 04 и 06. Проценты по кредиту не входят.</t>
+        </is>
+      </c>
+      <c r="L10" s="37">
+        <f>IF(OR('Условный пример'!L38="Высокий",'Условный пример'!L46="Высокий"),"Высокий",IF(OR('Условный пример'!L38="Средний",'Условный пример'!L46="Средний"),"Средний",IF(COUNTA('Условный пример'!L38,'Условный пример'!L46)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M10" s="35">
+        <f>SUM('Условный пример'!M38,'Условный пример'!M46)</f>
+        <v/>
+      </c>
+      <c r="N10" s="28" t="inlineStr">
+        <is>
+          <t>Свертка постатейных строк. Сумма риска в тождество факторов не входит.</t>
+        </is>
+      </c>
+      <c r="O10" s="38" t="inlineStr">
+        <is>
+          <t>свертка</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Пять групп без повторного счета</t>
+        </is>
+      </c>
+      <c r="C11" s="26">
+        <f>SUM(C6:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="26">
+        <f>SUM(D6:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="26">
+        <f>SUM(E6:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="27">
+        <f>IF(C11=0,"—",E11/C11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="26">
+        <f>SUM(G6:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="26">
+        <f>SUM(H6:H10)</f>
+        <v/>
+      </c>
+      <c r="I11" s="26">
+        <f>SUM(I6:I10)</f>
+        <v/>
+      </c>
+      <c r="J11" s="26">
+        <f>SUM(J6:J10)</f>
+        <v/>
+      </c>
+      <c r="K11" s="25" t="inlineStr">
+        <is>
+          <t>Сумма групп равна постатейному итогу.</t>
+        </is>
+      </c>
+      <c r="L11" s="5">
+        <f>IF(OR('Условный пример'!L5="Высокий",'Условный пример'!L17="Высокий",'Условный пример'!L25="Высокий",'Условный пример'!L37="Высокий",'Условный пример'!L10="Высокий",'Условный пример'!L31="Высокий",'Условный пример'!L42="Высокий",'Условный пример'!L38="Высокий",'Условный пример'!L46="Высокий"),"Высокий",IF(OR('Условный пример'!L5="Средний",'Условный пример'!L17="Средний",'Условный пример'!L25="Средний",'Условный пример'!L37="Средний",'Условный пример'!L10="Средний",'Условный пример'!L31="Средний",'Условный пример'!L42="Средний",'Условный пример'!L38="Средний",'Условный пример'!L46="Средний"),"Средний",IF(COUNTA('Условный пример'!L5,'Условный пример'!L17,'Условный пример'!L25,'Условный пример'!L37,'Условный пример'!L10,'Условный пример'!L31,'Условный пример'!L42,'Условный пример'!L38,'Условный пример'!L46)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M11" s="26">
+        <f>SUM(M6:M10)</f>
+        <v/>
+      </c>
+      <c r="N11" s="25" t="inlineStr">
+        <is>
+          <t>Проценты по кредиту в свод не входят.</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Рабочая таблица по листу «Шаблон»</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Состав</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Базовый бюджет, руб.</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Откорректированный бюджет, руб.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Отклонение, руб.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Отклонение, %</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Фактор 1. Инфляция, руб.</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Фактор 2. Изменения ПСД, руб.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Фактор 3. Иные причины, руб.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Контроль, руб.</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Что входит в группу</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Риск до ввода</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Сумма риска, руб.</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>Класс надежности</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>СМР</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Подготовка площадки, общестроительные работы, внутренние системы и технологическое оборудование. Коды 01, 03.01, 03.02, 03.04.</t>
+        </is>
+      </c>
+      <c r="C15" s="35">
+        <f>SUM('Шаблон'!C5,'Шаблон'!C17,'Шаблон'!C25,'Шаблон'!C37)</f>
+        <v/>
+      </c>
+      <c r="D15" s="35">
+        <f>SUM('Шаблон'!D5,'Шаблон'!D17,'Шаблон'!D25,'Шаблон'!D37)</f>
+        <v/>
+      </c>
+      <c r="E15" s="35">
+        <f>D15-C15</f>
+        <v/>
+      </c>
+      <c r="F15" s="36">
+        <f>IF(C15=0,"—",E15/C15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="35">
+        <f>SUM('Шаблон'!G5,'Шаблон'!G17,'Шаблон'!G25,'Шаблон'!G37)</f>
+        <v/>
+      </c>
+      <c r="H15" s="35">
+        <f>SUM('Шаблон'!H5,'Шаблон'!H17,'Шаблон'!H25,'Шаблон'!H37)</f>
+        <v/>
+      </c>
+      <c r="I15" s="35">
+        <f>SUM('Шаблон'!I5,'Шаблон'!I17,'Шаблон'!I25,'Шаблон'!I37)</f>
+        <v/>
+      </c>
+      <c r="J15" s="35">
+        <f>G15+H15+I15-E15</f>
+        <v/>
+      </c>
+      <c r="K15" s="28" t="inlineStr">
+        <is>
+          <t>Подготовка площадки, общестроительные работы, внутренние системы и технологическое оборудование. Коды 01, 03.01, 03.02, 03.04.</t>
+        </is>
+      </c>
+      <c r="L15" s="37">
+        <f>IF(OR('Шаблон'!L5="Высокий",'Шаблон'!L17="Высокий",'Шаблон'!L25="Высокий",'Шаблон'!L37="Высокий"),"Высокий",IF(OR('Шаблон'!L5="Средний",'Шаблон'!L17="Средний",'Шаблон'!L25="Средний",'Шаблон'!L37="Средний"),"Средний",IF(COUNTA('Шаблон'!L5,'Шаблон'!L17,'Шаблон'!L25,'Шаблон'!L37)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M15" s="35">
+        <f>SUM('Шаблон'!M5,'Шаблон'!M17,'Шаблон'!M25,'Шаблон'!M37)</f>
+        <v/>
+      </c>
+      <c r="N15" s="28" t="inlineStr">
+        <is>
+          <t>Свертка постатейных строк. Сумма риска в тождество факторов не входит.</t>
+        </is>
+      </c>
+      <c r="O15" s="38" t="inlineStr">
+        <is>
+          <t>свертка</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>ПИР</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>Изыскания, проект, рабочая документация, экспертиза и авторский надзор. Код 02.</t>
+        </is>
+      </c>
+      <c r="C16" s="35">
+        <f>SUM('Шаблон'!C10)</f>
+        <v/>
+      </c>
+      <c r="D16" s="35">
+        <f>SUM('Шаблон'!D10)</f>
+        <v/>
+      </c>
+      <c r="E16" s="35">
+        <f>D16-C16</f>
+        <v/>
+      </c>
+      <c r="F16" s="36">
+        <f>IF(C16=0,"—",E16/C16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="35">
+        <f>SUM('Шаблон'!G10)</f>
+        <v/>
+      </c>
+      <c r="H16" s="35">
+        <f>SUM('Шаблон'!H10)</f>
+        <v/>
+      </c>
+      <c r="I16" s="35">
+        <f>SUM('Шаблон'!I10)</f>
+        <v/>
+      </c>
+      <c r="J16" s="35">
+        <f>G16+H16+I16-E16</f>
+        <v/>
+      </c>
+      <c r="K16" s="28" t="inlineStr">
+        <is>
+          <t>Изыскания, проект, рабочая документация, экспертиза и авторский надзор. Код 02.</t>
+        </is>
+      </c>
+      <c r="L16" s="37">
+        <f>IF(OR('Шаблон'!L10="Высокий"),"Высокий",IF(OR('Шаблон'!L10="Средний"),"Средний",IF(COUNTA('Шаблон'!L10)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M16" s="35">
+        <f>SUM('Шаблон'!M10)</f>
+        <v/>
+      </c>
+      <c r="N16" s="28" t="inlineStr">
+        <is>
+          <t>Свертка постатейных строк. Сумма риска в тождество факторов не входит.</t>
+        </is>
+      </c>
+      <c r="O16" s="38" t="inlineStr">
+        <is>
+          <t>свертка</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Наружные сети и ТУ</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>Наружные сети, технологическое присоединение и благоустройство. Код 03.03.</t>
+        </is>
+      </c>
+      <c r="C17" s="35">
+        <f>SUM('Шаблон'!C31)</f>
+        <v/>
+      </c>
+      <c r="D17" s="35">
+        <f>SUM('Шаблон'!D31)</f>
+        <v/>
+      </c>
+      <c r="E17" s="35">
+        <f>D17-C17</f>
+        <v/>
+      </c>
+      <c r="F17" s="36">
+        <f>IF(C17=0,"—",E17/C17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="35">
+        <f>SUM('Шаблон'!G31)</f>
+        <v/>
+      </c>
+      <c r="H17" s="35">
+        <f>SUM('Шаблон'!H31)</f>
+        <v/>
+      </c>
+      <c r="I17" s="35">
+        <f>SUM('Шаблон'!I31)</f>
+        <v/>
+      </c>
+      <c r="J17" s="35">
+        <f>G17+H17+I17-E17</f>
+        <v/>
+      </c>
+      <c r="K17" s="28" t="inlineStr">
+        <is>
+          <t>Наружные сети, технологическое присоединение и благоустройство. Код 03.03.</t>
+        </is>
+      </c>
+      <c r="L17" s="37">
+        <f>IF(OR('Шаблон'!L31="Высокий"),"Высокий",IF(OR('Шаблон'!L31="Средний"),"Средний",IF(COUNTA('Шаблон'!L31)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M17" s="35">
+        <f>SUM('Шаблон'!M31)</f>
+        <v/>
+      </c>
+      <c r="N17" s="28" t="inlineStr">
+        <is>
+          <t>Свертка постатейных строк. Сумма риска в тождество факторов не входит.</t>
+        </is>
+      </c>
+      <c r="O17" s="38" t="inlineStr">
+        <is>
+          <t>свертка</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>Продвижение, офис продаж и брокерские комиссии. Код 05.</t>
+        </is>
+      </c>
+      <c r="C18" s="35">
+        <f>SUM('Шаблон'!C42)</f>
+        <v/>
+      </c>
+      <c r="D18" s="35">
+        <f>SUM('Шаблон'!D42)</f>
+        <v/>
+      </c>
+      <c r="E18" s="35">
+        <f>D18-C18</f>
+        <v/>
+      </c>
+      <c r="F18" s="36">
+        <f>IF(C18=0,"—",E18/C18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="35">
+        <f>SUM('Шаблон'!G42)</f>
+        <v/>
+      </c>
+      <c r="H18" s="35">
+        <f>SUM('Шаблон'!H42)</f>
+        <v/>
+      </c>
+      <c r="I18" s="35">
+        <f>SUM('Шаблон'!I42)</f>
+        <v/>
+      </c>
+      <c r="J18" s="35">
+        <f>G18+H18+I18-E18</f>
+        <v/>
+      </c>
+      <c r="K18" s="28" t="inlineStr">
+        <is>
+          <t>Продвижение, офис продаж и брокерские комиссии. Код 05.</t>
+        </is>
+      </c>
+      <c r="L18" s="37">
+        <f>IF(OR('Шаблон'!L42="Высокий"),"Высокий",IF(OR('Шаблон'!L42="Средний"),"Средний",IF(COUNTA('Шаблон'!L42)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M18" s="35">
+        <f>SUM('Шаблон'!M42)</f>
+        <v/>
+      </c>
+      <c r="N18" s="28" t="inlineStr">
+        <is>
+          <t>Свертка постатейных строк. Сумма риска в тождество факторов не входит.</t>
+        </is>
+      </c>
+      <c r="O18" s="38" t="inlineStr">
+        <is>
+          <t>свертка</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Административные</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>Управление, страхование, резерв, гарантии и обязательные платежи. Коды 04 и 06. Проценты по кредиту не входят.</t>
+        </is>
+      </c>
+      <c r="C19" s="35">
+        <f>SUM('Шаблон'!C38,'Шаблон'!C46)</f>
+        <v/>
+      </c>
+      <c r="D19" s="35">
+        <f>SUM('Шаблон'!D38,'Шаблон'!D46)</f>
+        <v/>
+      </c>
+      <c r="E19" s="35">
+        <f>D19-C19</f>
+        <v/>
+      </c>
+      <c r="F19" s="36">
+        <f>IF(C19=0,"—",E19/C19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="35">
+        <f>SUM('Шаблон'!G38,'Шаблон'!G46)</f>
+        <v/>
+      </c>
+      <c r="H19" s="35">
+        <f>SUM('Шаблон'!H38,'Шаблон'!H46)</f>
+        <v/>
+      </c>
+      <c r="I19" s="35">
+        <f>SUM('Шаблон'!I38,'Шаблон'!I46)</f>
+        <v/>
+      </c>
+      <c r="J19" s="35">
+        <f>G19+H19+I19-E19</f>
+        <v/>
+      </c>
+      <c r="K19" s="28" t="inlineStr">
+        <is>
+          <t>Управление, страхование, резерв, гарантии и обязательные платежи. Коды 04 и 06. Проценты по кредиту не входят.</t>
+        </is>
+      </c>
+      <c r="L19" s="37">
+        <f>IF(OR('Шаблон'!L38="Высокий",'Шаблон'!L46="Высокий"),"Высокий",IF(OR('Шаблон'!L38="Средний",'Шаблон'!L46="Средний"),"Средний",IF(COUNTA('Шаблон'!L38,'Шаблон'!L46)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M19" s="35">
+        <f>SUM('Шаблон'!M38,'Шаблон'!M46)</f>
+        <v/>
+      </c>
+      <c r="N19" s="28" t="inlineStr">
+        <is>
+          <t>Свертка постатейных строк. Сумма риска в тождество факторов не входит.</t>
+        </is>
+      </c>
+      <c r="O19" s="38" t="inlineStr">
+        <is>
+          <t>свертка</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Пять групп без повторного счета</t>
+        </is>
+      </c>
+      <c r="C20" s="26">
+        <f>SUM(C15:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="26">
+        <f>SUM(D15:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="26">
+        <f>SUM(E15:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="27">
+        <f>IF(C20=0,"—",E20/C20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="26">
+        <f>SUM(G15:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="26">
+        <f>SUM(H15:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="26">
+        <f>SUM(I15:I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="26">
+        <f>SUM(J15:J19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="25" t="inlineStr">
+        <is>
+          <t>Сумма групп равна постатейному итогу.</t>
+        </is>
+      </c>
+      <c r="L20" s="5">
+        <f>IF(OR('Шаблон'!L5="Высокий",'Шаблон'!L17="Высокий",'Шаблон'!L25="Высокий",'Шаблон'!L37="Высокий",'Шаблон'!L10="Высокий",'Шаблон'!L31="Высокий",'Шаблон'!L42="Высокий",'Шаблон'!L38="Высокий",'Шаблон'!L46="Высокий"),"Высокий",IF(OR('Шаблон'!L5="Средний",'Шаблон'!L17="Средний",'Шаблон'!L25="Средний",'Шаблон'!L37="Средний",'Шаблон'!L10="Средний",'Шаблон'!L31="Средний",'Шаблон'!L42="Средний",'Шаблон'!L38="Средний",'Шаблон'!L46="Средний"),"Средний",IF(COUNTA('Шаблон'!L5,'Шаблон'!L17,'Шаблон'!L25,'Шаблон'!L37,'Шаблон'!L10,'Шаблон'!L31,'Шаблон'!L42,'Шаблон'!L38,'Шаблон'!L46)=0,"","Низкий")))</f>
+        <v/>
+      </c>
+      <c r="M20" s="26">
+        <f>SUM(M15:M19)</f>
+        <v/>
+      </c>
+      <c r="N20" s="25" t="inlineStr">
+        <is>
+          <t>Проценты по кредиту в свод не входят.</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="J6:J11">
+    <cfRule type="cellIs" priority="1" operator="between" dxfId="0">
+      <formula>-1</formula>
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J15:J20">
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="0">
+      <formula>-1</formula>
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C65911"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8947,7 +9910,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Пример 1. Решение не изменилось: монолит, 10 000 м³ → 11 200 м³</t>
         </is>
@@ -8959,10 +9922,10 @@
           <t>Исходный объем v0</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="40" t="n">
         <v>10000</v>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>м³</t>
         </is>
@@ -8974,10 +9937,10 @@
           <t>Новый объем v1</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="40" t="n">
         <v>11200</v>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>м³</t>
         </is>
@@ -8989,10 +9952,10 @@
           <t>Исходная цена p0</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="40" t="n">
         <v>18000</v>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>руб. за единицу</t>
         </is>
@@ -9004,10 +9967,10 @@
           <t>Новая цена p1</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="40" t="n">
         <v>22500</v>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>руб. за единицу</t>
         </is>
@@ -9019,11 +9982,11 @@
           <t>Коэффициент Iex</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="41">
         <f>Индекс!B10</f>
         <v/>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>из листа «Индекс», пример 1</t>
         </is>
@@ -9035,11 +9998,11 @@
           <t>Цена-ориентир pref</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="42">
         <f>B7*B9</f>
         <v/>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>p0 × Iex, решение не менялось</t>
         </is>
@@ -9117,7 +10080,7 @@
           <t>Контроль</t>
         </is>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="32">
         <f>B15+B16+B17-B14</f>
         <v/>
       </c>
@@ -9139,7 +10102,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Пример 2. Замена решения: кладка 5 000 м² заменена вентилируемым фасадом 5 300 м²</t>
         </is>
@@ -9151,7 +10114,7 @@
           <t>Исходный объем v0</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="40" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -9161,7 +10124,7 @@
           <t>Новый объем v1</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="40" t="n">
         <v>5300</v>
       </c>
     </row>
@@ -9171,7 +10134,7 @@
           <t>Исходная цена p0</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="40" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -9181,7 +10144,7 @@
           <t>Новая цена p1</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="40" t="n">
         <v>9600</v>
       </c>
     </row>
@@ -9191,7 +10154,7 @@
           <t>Iex исходного решения</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n">
+      <c r="B26" s="43" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -9201,7 +10164,7 @@
           <t>Рыночная цена нового решения pref</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="40" t="n">
         <v>9200</v>
       </c>
     </row>
@@ -9277,7 +10240,7 @@
           <t>Контроль</t>
         </is>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="44">
         <f>B32+B33+B34-B31</f>
         <v/>
       </c>
@@ -9299,7 +10262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -9329,7 +10292,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Паспорт и инфляция</t>
         </is>
@@ -9341,10 +10304,10 @@
           <t>Исходный измеритель Q0</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="40" t="n">
         <v>50000</v>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>м² общей площади, как в модели T0</t>
         </is>
@@ -9356,10 +10319,10 @@
           <t>Удельная ставка a0</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="40" t="n">
         <v>120000</v>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>руб. без НДС за единицу измерителя</t>
         </is>
@@ -9371,10 +10334,10 @@
           <t>Коэффициент Iex</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="41" t="n">
         <v>1.25</v>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>дефлятор паспорта, не веса новой сметы</t>
         </is>
@@ -9386,11 +10349,11 @@
           <t>Базовый бюджет B0</t>
         </is>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="35">
         <f>B5*B6</f>
         <v/>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>a0 × Q0</t>
         </is>
@@ -9402,11 +10365,11 @@
           <t>Фактор 1. Инфляция</t>
         </is>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="35">
         <f>B8*(B7-1)</f>
         <v/>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>только на сумму паспорта</t>
         </is>
@@ -9418,18 +10381,18 @@
           <t>Проиндексированный паспорт</t>
         </is>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="35">
         <f>B8*B7</f>
         <v/>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>B0 × Iex</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Отступление от паспорта</t>
         </is>
@@ -9441,10 +10404,10 @@
           <t>Измеритель T1, Q1</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="40" t="n">
         <v>52000</v>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>новый ТЭП той же единицы измерения</t>
         </is>
@@ -9459,7 +10422,7 @@
       <c r="B14" s="20" t="n">
         <v>7750000000</v>
       </c>
-      <c r="C14" s="30" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>рабочая документация и цены T1 без лишней площади и без замененного решения</t>
         </is>
@@ -9471,11 +10434,11 @@
           <t>Удельная стоимость той же программы</t>
         </is>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="45">
         <f>IF(B5=0,"",B14/B5)</f>
         <v/>
       </c>
-      <c r="C15" s="30" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>S / Q0, руб. за единицу</t>
         </is>
@@ -9491,7 +10454,7 @@
         <f>(B13-B5)*B15</f>
         <v/>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>приростная площадь в текущей полноте исходного стандарта</t>
         </is>
@@ -9506,7 +10469,7 @@
       <c r="B17" s="20" t="n">
         <v>1400000000</v>
       </c>
-      <c r="C17" s="30" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>замена решения, названного в паспорте</t>
         </is>
@@ -9521,7 +10484,7 @@
       <c r="B18" s="20" t="n">
         <v>800000000</v>
       </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>Allowance0 из паспорта или аналога</t>
         </is>
@@ -9533,11 +10496,11 @@
           <t>U, чистая замена</t>
         </is>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="35">
         <f>B17-B18*B7</f>
         <v/>
       </c>
-      <c r="C19" s="33" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>Cost1 − Allowance0 × Iex</t>
         </is>
@@ -9549,18 +10512,18 @@
           <t>Фактор 2. Изменения ПСД</t>
         </is>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="35">
         <f>B16+B19</f>
         <v/>
       </c>
-      <c r="C20" s="33" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>площадь и замена; детализация сюда не входит</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>Факт, уточнение и прочие иные причины</t>
         </is>
@@ -9575,7 +10538,7 @@
       <c r="B23" s="20" t="n">
         <v>8560000000</v>
       </c>
-      <c r="C23" s="30" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>статья T1, тот же периметр</t>
         </is>
@@ -9587,27 +10550,27 @@
           <t>Фактор 3. Иные причины</t>
         </is>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="35">
         <f>B23-B8-B9-B20</f>
         <v/>
       </c>
-      <c r="C24" s="33" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>остаток после инфляции и отступлений от паспорта</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>В том числе F3d, уточнение по РД</t>
         </is>
       </c>
-      <c r="B25" s="34">
+      <c r="B25" s="32">
         <f>B14-B10</f>
         <v/>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
         <is>
           <t>S − проиндексированный паспорт; это не изменение проекта</t>
         </is>
@@ -9623,7 +10586,7 @@
         <f>B24-B25</f>
         <v/>
       </c>
-      <c r="C26" s="30" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>срок, закупка, форс-мажор и налог</t>
         </is>
@@ -9635,38 +10598,38 @@
           <t>Отклонение</t>
         </is>
       </c>
-      <c r="B27" s="37">
+      <c r="B27" s="35">
         <f>B23-B8</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>Контроль тождества</t>
         </is>
       </c>
-      <c r="B28" s="34">
+      <c r="B28" s="32">
         <f>B9+B20+B24-B27</f>
         <v/>
       </c>
-      <c r="C28" s="40" t="inlineStr">
+      <c r="C28" s="31" t="inlineStr">
         <is>
           <t>F1 + F2 + F3 − отклонение, должно быть 0</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Контроль состава B1</t>
         </is>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="32">
         <f>B14+B20+B26-B23</f>
         <v/>
       </c>
-      <c r="C29" s="40" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>S + F2 + прочие иные − B1, должно быть 0</t>
         </is>
@@ -9689,7 +10652,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008064A2"/>
@@ -9747,13 +10710,13 @@
           <t>Материалы</t>
         </is>
       </c>
-      <c r="B5" s="41" t="n">
+      <c r="B5" s="46" t="n">
         <v>0.62</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="41" t="n">
         <v>1.19</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="47">
         <f>B5*C5</f>
         <v/>
       </c>
@@ -9764,13 +10727,13 @@
           <t>Машины и механизмы</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="46" t="n">
         <v>0.11</v>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="41" t="n">
         <v>1.14</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="47">
         <f>B6*C6</f>
         <v/>
       </c>
@@ -9781,13 +10744,13 @@
           <t>Оплата труда</t>
         </is>
       </c>
-      <c r="B7" s="41" t="n">
+      <c r="B7" s="46" t="n">
         <v>0.27</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="41" t="n">
         <v>1.16</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="47">
         <f>B7*C7</f>
         <v/>
       </c>
@@ -9798,13 +10761,13 @@
           <t>Перевозка, если выделена отдельно</t>
         </is>
       </c>
-      <c r="B8" s="41" t="n">
+      <c r="B8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="47">
         <f>B8*C8</f>
         <v/>
       </c>
@@ -9815,23 +10778,23 @@
           <t>Сумма весов</t>
         </is>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="48">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>Должна быть равна 100%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>Iex позиции</t>
         </is>
       </c>
-      <c r="B10" s="44">
+      <c r="B10" s="49">
         <f>IF(ABS(B9-1)&gt;0.000001,"проверьте веса",SUM(D5:D8))</f>
         <v/>
       </c>
@@ -9866,41 +10829,41 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C0C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Процент, содержание команды и проценты по кредиту</t>
+          <t>Процент генподряда и содержание команды</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Эти статьи считаются после разложения базы. Процент не индексируется вторым кругом. Ставка кредита не объявляется инфляцией СМР.</t>
+          <t>Эти статьи считаются после разложения базы. Процент не индексируется вторым кругом. Проценты по кредиту в бюджет проекта не входят и на этом листе не считаются.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Вознаграждение: процент от базы плюс помесячное содержание</t>
         </is>
@@ -9912,7 +10875,7 @@
           <t>База T0, руб.</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="50" t="n">
         <v>3100000000</v>
       </c>
     </row>
@@ -9922,7 +10885,7 @@
           <t>Фактор 1 базы, руб.</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="50" t="n">
         <v>280000000</v>
       </c>
     </row>
@@ -9932,7 +10895,7 @@
           <t>Фактор 2 базы, руб.</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="50" t="n">
         <v>190000000</v>
       </c>
     </row>
@@ -9942,7 +10905,7 @@
           <t>Фактор 3 базы, руб.</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="50" t="n">
         <v>30000000</v>
       </c>
     </row>
@@ -9952,7 +10915,7 @@
           <t>Ставка процента T0</t>
         </is>
       </c>
-      <c r="B9" s="41" t="n">
+      <c r="B9" s="46" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -9962,7 +10925,7 @@
           <t>Ставка процента T1</t>
         </is>
       </c>
-      <c r="B10" s="41" t="n">
+      <c r="B10" s="46" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -9972,7 +10935,7 @@
           <t>Исходная численность, чел.</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="50" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9982,7 +10945,7 @@
           <t>Дополнительная численность из-за ПСД, чел.</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n">
+      <c r="B12" s="50" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9992,7 +10955,7 @@
           <t>Исходный срок, мес.</t>
         </is>
       </c>
-      <c r="B13" s="45" t="n">
+      <c r="B13" s="50" t="n">
         <v>36</v>
       </c>
     </row>
@@ -10002,7 +10965,7 @@
           <t>Срок T1, мес.</t>
         </is>
       </c>
-      <c r="B14" s="45" t="n">
+      <c r="B14" s="50" t="n">
         <v>43</v>
       </c>
     </row>
@@ -10012,7 +10975,7 @@
           <t>Стоимость человека в месяц T0, руб.</t>
         </is>
       </c>
-      <c r="B15" s="45" t="n">
+      <c r="B15" s="50" t="n">
         <v>350000</v>
       </c>
     </row>
@@ -10022,7 +10985,7 @@
           <t>Iex оплаты труда</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="43" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -10032,7 +10995,7 @@
           <t>Фактическая стоимость человека в месяц T1, руб.</t>
         </is>
       </c>
-      <c r="B17" s="45" t="n">
+      <c r="B17" s="50" t="n">
         <v>410000</v>
       </c>
     </row>
@@ -10075,7 +11038,7 @@
           <t>Отклонение</t>
         </is>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="35">
         <f>B21-B20</f>
         <v/>
       </c>
@@ -10119,736 +11082,24 @@
           <t>Контроль</t>
         </is>
       </c>
-      <c r="B26" s="34">
+      <c r="B26" s="32">
         <f>B23+B24+B25-B22</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>Учебный график процентов, млн руб. Процент начисляется на долг на начало квартала.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Сценарии BASE, INF и PSD идут по исходной ставке и исходному числу кварталов. ACT добавляет квартал и новую ставку. Это проверка логики, а не замена помесячной модели банка.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Квартал 1</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Квартал 2</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Квартал 3</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Квартал 4</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Квартал 5</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Выборка BASE</t>
-        </is>
-      </c>
-      <c r="B32" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="C32" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="D32" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="E32" s="46" t="n">
-        <v>100</v>
-      </c>
-      <c r="F32" s="46" t="n"/>
-      <c r="G32" s="47">
-        <f>SUM(B32:F32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Выборка INF</t>
-        </is>
-      </c>
-      <c r="B33" s="46" t="n">
-        <v>110</v>
-      </c>
-      <c r="C33" s="46" t="n">
-        <v>110</v>
-      </c>
-      <c r="D33" s="46" t="n">
-        <v>110</v>
-      </c>
-      <c r="E33" s="46" t="n">
-        <v>110</v>
-      </c>
-      <c r="F33" s="46" t="n"/>
-      <c r="G33" s="47">
-        <f>SUM(B33:F33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Выборка PSD</t>
-        </is>
-      </c>
-      <c r="B34" s="46" t="n">
-        <v>110</v>
-      </c>
-      <c r="C34" s="46" t="n">
-        <v>110</v>
-      </c>
-      <c r="D34" s="46" t="n">
-        <v>150</v>
-      </c>
-      <c r="E34" s="46" t="n">
-        <v>110</v>
-      </c>
-      <c r="F34" s="46" t="n"/>
-      <c r="G34" s="47">
-        <f>SUM(B34:F34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Выборка ACT</t>
-        </is>
-      </c>
-      <c r="B35" s="46" t="n">
-        <v>110</v>
-      </c>
-      <c r="C35" s="46" t="n">
-        <v>110</v>
-      </c>
-      <c r="D35" s="46" t="n">
-        <v>150</v>
-      </c>
-      <c r="E35" s="46" t="n">
-        <v>110</v>
-      </c>
-      <c r="F35" s="46" t="n">
-        <v>40</v>
-      </c>
-      <c r="G35" s="47">
-        <f>SUM(B35:F35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Ставка за квартал BASE / INF / PSD</t>
-        </is>
-      </c>
-      <c r="B36" s="41" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Ставка за квартал ACT</t>
-        </is>
-      </c>
-      <c r="B37" s="41" t="n">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Долг на начало, BASE</t>
-        </is>
-      </c>
-      <c r="B39" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="47">
-        <f>IF(C32="","",B39+B32)</f>
-        <v/>
-      </c>
-      <c r="D39" s="47">
-        <f>IF(D32="","",C39+C32)</f>
-        <v/>
-      </c>
-      <c r="E39" s="47">
-        <f>IF(E32="","",D39+D32)</f>
-        <v/>
-      </c>
-      <c r="F39" s="47">
-        <f>IF(F32="","",E39+E32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Проценты, BASE</t>
-        </is>
-      </c>
-      <c r="B40" s="48">
-        <f>IF(OR(B32="",B39=""),"",B39*$B$36)</f>
-        <v/>
-      </c>
-      <c r="C40" s="48">
-        <f>IF(OR(C32="",C39=""),"",C39*$B$36)</f>
-        <v/>
-      </c>
-      <c r="D40" s="48">
-        <f>IF(OR(D32="",D39=""),"",D39*$B$36)</f>
-        <v/>
-      </c>
-      <c r="E40" s="48">
-        <f>IF(OR(E32="",E39=""),"",E39*$B$36)</f>
-        <v/>
-      </c>
-      <c r="F40" s="48">
-        <f>IF(OR(F32="",F39=""),"",F39*$B$36)</f>
-        <v/>
-      </c>
-      <c r="G40" s="49">
-        <f>SUM(B40:F40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Долг на начало, INF</t>
-        </is>
-      </c>
-      <c r="B41" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="47">
-        <f>IF(C33="","",B41+B33)</f>
-        <v/>
-      </c>
-      <c r="D41" s="47">
-        <f>IF(D33="","",C41+C33)</f>
-        <v/>
-      </c>
-      <c r="E41" s="47">
-        <f>IF(E33="","",D41+D33)</f>
-        <v/>
-      </c>
-      <c r="F41" s="47">
-        <f>IF(F33="","",E41+E33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>Проценты, INF</t>
-        </is>
-      </c>
-      <c r="B42" s="48">
-        <f>IF(OR(B33="",B41=""),"",B41*$B$36)</f>
-        <v/>
-      </c>
-      <c r="C42" s="48">
-        <f>IF(OR(C33="",C41=""),"",C41*$B$36)</f>
-        <v/>
-      </c>
-      <c r="D42" s="48">
-        <f>IF(OR(D33="",D41=""),"",D41*$B$36)</f>
-        <v/>
-      </c>
-      <c r="E42" s="48">
-        <f>IF(OR(E33="",E41=""),"",E41*$B$36)</f>
-        <v/>
-      </c>
-      <c r="F42" s="48">
-        <f>IF(OR(F33="",F41=""),"",F41*$B$36)</f>
-        <v/>
-      </c>
-      <c r="G42" s="49">
-        <f>SUM(B42:F42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Долг на начало, PSD</t>
-        </is>
-      </c>
-      <c r="B43" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="47">
-        <f>IF(C34="","",B43+B34)</f>
-        <v/>
-      </c>
-      <c r="D43" s="47">
-        <f>IF(D34="","",C43+C34)</f>
-        <v/>
-      </c>
-      <c r="E43" s="47">
-        <f>IF(E34="","",D43+D34)</f>
-        <v/>
-      </c>
-      <c r="F43" s="47">
-        <f>IF(F34="","",E43+E34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>Проценты, PSD</t>
-        </is>
-      </c>
-      <c r="B44" s="48">
-        <f>IF(OR(B34="",B43=""),"",B43*$B$36)</f>
-        <v/>
-      </c>
-      <c r="C44" s="48">
-        <f>IF(OR(C34="",C43=""),"",C43*$B$36)</f>
-        <v/>
-      </c>
-      <c r="D44" s="48">
-        <f>IF(OR(D34="",D43=""),"",D43*$B$36)</f>
-        <v/>
-      </c>
-      <c r="E44" s="48">
-        <f>IF(OR(E34="",E43=""),"",E43*$B$36)</f>
-        <v/>
-      </c>
-      <c r="F44" s="48">
-        <f>IF(OR(F34="",F43=""),"",F43*$B$36)</f>
-        <v/>
-      </c>
-      <c r="G44" s="49">
-        <f>SUM(B44:F44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>Долг на начало, ACT</t>
-        </is>
-      </c>
-      <c r="B45" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="47">
-        <f>IF(C35="","",B45+B35)</f>
-        <v/>
-      </c>
-      <c r="D45" s="47">
-        <f>IF(D35="","",C45+C35)</f>
-        <v/>
-      </c>
-      <c r="E45" s="47">
-        <f>IF(E35="","",D45+D35)</f>
-        <v/>
-      </c>
-      <c r="F45" s="47">
-        <f>IF(F35="","",E45+E35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>Проценты, ACT</t>
-        </is>
-      </c>
-      <c r="B46" s="48">
-        <f>IF(OR(B35="",B45=""),"",B45*$B$37)</f>
-        <v/>
-      </c>
-      <c r="C46" s="48">
-        <f>IF(OR(C35="",C45=""),"",C45*$B$37)</f>
-        <v/>
-      </c>
-      <c r="D46" s="48">
-        <f>IF(OR(D35="",D45=""),"",D45*$B$37)</f>
-        <v/>
-      </c>
-      <c r="E46" s="48">
-        <f>IF(OR(E35="",E45=""),"",E45*$B$37)</f>
-        <v/>
-      </c>
-      <c r="F46" s="48">
-        <f>IF(OR(F35="",F45=""),"",F45*$B$37)</f>
-        <v/>
-      </c>
-      <c r="G46" s="49">
-        <f>SUM(B46:F46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Фактор 1 процентов</t>
-        </is>
-      </c>
-      <c r="B48" s="50">
-        <f>G42-G40</f>
-        <v/>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>млн руб.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Фактор 2 процентов</t>
-        </is>
-      </c>
-      <c r="B49" s="50">
-        <f>G44-G42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Фактор 3 процентов</t>
-        </is>
-      </c>
-      <c r="B50" s="50">
-        <f>G46-G44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="39" t="inlineStr">
-        <is>
-          <t>Контроль процентов</t>
-        </is>
-      </c>
-      <c r="B51" s="49">
-        <f>B48+B49+B50-(G46-G40)</f>
-        <v/>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Проценты по кредиту в расчет не включаются: бюджеты проектов эти затраты не содержат.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C00000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Оценка риска дальнейшего роста бюджета до ввода</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Шкала оценивает новое отклонение сверх откорректированного бюджета. Она не переразлагает уже учтенные факторы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Признак</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>0 баллов</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>1 балл</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2 балла</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Балл строки</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Доля строки без подписанного договора</t>
-        </is>
-      </c>
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t>менее 15%</t>
-        </is>
-      </c>
-      <c r="C5" s="51" t="inlineStr">
-        <is>
-          <t>от 15% до 40%</t>
-        </is>
-      </c>
-      <c r="D5" s="52" t="inlineStr">
-        <is>
-          <t>более 40%</t>
-        </is>
-      </c>
-      <c r="E5" s="53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Тип цены подписанного объема</t>
-        </is>
-      </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>твердая цена без эскалации</t>
-        </is>
-      </c>
-      <c r="C6" s="51" t="inlineStr">
-        <is>
-          <t>единичные расценки</t>
-        </is>
-      </c>
-      <c r="D6" s="52" t="inlineStr">
-        <is>
-          <t>открытая цена или договор не подписан</t>
-        </is>
-      </c>
-      <c r="E6" s="53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Зрелость рабочей документации</t>
-        </is>
-      </c>
-      <c r="B7" s="40" t="inlineStr">
-        <is>
-          <t>заморожена не менее чем на 90%</t>
-        </is>
-      </c>
-      <c r="C7" s="51" t="inlineStr">
-        <is>
-          <t>от 60% до 90%</t>
-        </is>
-      </c>
-      <c r="D7" s="52" t="inlineStr">
-        <is>
-          <t>менее 60%</t>
-        </is>
-      </c>
-      <c r="E7" s="53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Резерв против ожидаемой стоимости названных рисков</t>
-        </is>
-      </c>
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>резерв покрывает не менее 100%</t>
-        </is>
-      </c>
-      <c r="C8" s="51" t="inlineStr">
-        <is>
-          <t>покрытие от 50% до 100%</t>
-        </is>
-      </c>
-      <c r="D8" s="52" t="inlineStr">
-        <is>
-          <t>покрытие менее 50%</t>
-        </is>
-      </c>
-      <c r="E8" s="53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Срок</t>
-        </is>
-      </c>
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>есть резерв времени</t>
-        </is>
-      </c>
-      <c r="C9" s="51" t="inlineStr">
-        <is>
-          <t>резерв выбран или задержка меньше 3 месяцев</t>
-        </is>
-      </c>
-      <c r="D9" s="52" t="inlineStr">
-        <is>
-          <t>задержка от 3 месяцев или вероятна претензия на срок</t>
-        </is>
-      </c>
-      <c r="E9" s="53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Несогласованные изменения и претензии</t>
-        </is>
-      </c>
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>менее 1% строки</t>
-        </is>
-      </c>
-      <c r="C10" s="51" t="inlineStr">
-        <is>
-          <t>от 1% до 3%</t>
-        </is>
-      </c>
-      <c r="D10" s="52" t="inlineStr">
-        <is>
-          <t>более 3%</t>
-        </is>
-      </c>
-      <c r="E10" s="53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Сумма баллов</t>
-        </is>
-      </c>
-      <c r="E11" s="54">
-        <f>SUM(E5:E10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="55" t="inlineStr">
-        <is>
-          <t>Принудительное повышение: нет ТУ, отрицательная экспертиза, обременение или неизвестная плата за присоединение</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Оценка</t>
-        </is>
-      </c>
-      <c r="E13" s="56">
-        <f>IF(E12&gt;=2,"Высокий",IF(AND(E12=1,E11&lt;=3),"Средний",IF(E11&lt;=3,"Низкий",IF(E11&lt;=7,"Средний","Высокий"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>0–3 балла — низкий риск, 4–7 — средний, 8–12 — высокий. Одно блокирующее обстоятельство поднимает оценку не ниже средней, два — до высокой. В комментарии указываются причина следующего удорожания, порядок величины и событие, которое снимет оценку.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:E15"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="E5 E6 E7 E8 E9 E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"0,1,2"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"0,1,2"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>